--- a/tests/eindhoven-500/reference/resultaten/werk/alle groepen/herkomsten/restdag/Pot_totaalproduct_Auto_Fiets.xlsx
+++ b/tests/eindhoven-500/reference/resultaten/werk/alle groepen/herkomsten/restdag/Pot_totaalproduct_Auto_Fiets.xlsx
@@ -388,13 +388,13 @@
         <v>2669906.822588462</v>
       </c>
       <c r="C2">
-        <v>3620213.208426756</v>
+        <v>3622412.168235496</v>
       </c>
       <c r="D2">
-        <v>5853105.573501623</v>
+        <v>5871393.875759445</v>
       </c>
       <c r="E2">
-        <v>7473670.026431233</v>
+        <v>7503510.231001171</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -405,13 +405,13 @@
         <v>1096439.322529429</v>
       </c>
       <c r="C3">
-        <v>1511704.912233991</v>
+        <v>1515485.750219394</v>
       </c>
       <c r="D3">
-        <v>2451447.172852638</v>
+        <v>2459725.785113472</v>
       </c>
       <c r="E3">
-        <v>3209783.514090162</v>
+        <v>3222965.237656336</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -422,13 +422,13 @@
         <v>195234.4955952457</v>
       </c>
       <c r="C4">
-        <v>337489.3026577411</v>
+        <v>338066.0514801582</v>
       </c>
       <c r="D4">
-        <v>705749.9270765944</v>
+        <v>707750.1928073741</v>
       </c>
       <c r="E4">
-        <v>1194532.046817181</v>
+        <v>1198129.408989331</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -439,13 +439,13 @@
         <v>273328.293833344</v>
       </c>
       <c r="C5">
-        <v>379675.4654899587</v>
+        <v>380324.307915178</v>
       </c>
       <c r="D5">
-        <v>664235.2254838536</v>
+        <v>666117.8285245873</v>
       </c>
       <c r="E5">
-        <v>817311.4004538608</v>
+        <v>819772.7535190159</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -456,13 +456,13 @@
         <v>286343.926873027</v>
       </c>
       <c r="C6">
-        <v>379675.4654899587</v>
+        <v>380324.307915178</v>
       </c>
       <c r="D6">
-        <v>664235.2254838536</v>
+        <v>666117.8285245873</v>
       </c>
       <c r="E6">
-        <v>754441.2927266407</v>
+        <v>756713.31094063</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -473,13 +473,13 @@
         <v>1072648.718100314</v>
       </c>
       <c r="C7">
-        <v>1467176.265437067</v>
+        <v>1471135.529176104</v>
       </c>
       <c r="D7">
-        <v>2383057.711583073</v>
+        <v>2392045.28413961</v>
       </c>
       <c r="E7">
-        <v>3126825.705296701</v>
+        <v>3140758.950287857</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -490,13 +490,13 @@
         <v>899132.0137017339</v>
       </c>
       <c r="C8">
-        <v>1393817.452165214</v>
+        <v>1397578.752717299</v>
       </c>
       <c r="D8">
-        <v>2517947.770729284</v>
+        <v>2527444.07380789</v>
       </c>
       <c r="E8">
-        <v>3659051.357262097</v>
+        <v>3675356.21842196</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -507,13 +507,13 @@
         <v>879701.1414710328</v>
       </c>
       <c r="C9">
-        <v>1352724.511567751</v>
+        <v>1356596.013961787</v>
       </c>
       <c r="D9">
-        <v>2446455.300323929</v>
+        <v>2456656.043180354</v>
       </c>
       <c r="E9">
-        <v>3561105.932607829</v>
+        <v>3578213.638467912</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -524,13 +524,13 @@
         <v>820260.7844296519</v>
       </c>
       <c r="C10">
-        <v>1320458.638893361</v>
+        <v>1324021.976258493</v>
       </c>
       <c r="D10">
-        <v>2562911.123778021</v>
+        <v>2572577.003697317</v>
       </c>
       <c r="E10">
-        <v>4124748.802731818</v>
+        <v>4143128.8280393</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -541,13 +541,13 @@
         <v>899132.0137017339</v>
       </c>
       <c r="C11">
-        <v>1393817.452165214</v>
+        <v>1397578.752717299</v>
       </c>
       <c r="D11">
-        <v>2517947.770729284</v>
+        <v>2527444.07380789</v>
       </c>
       <c r="E11">
-        <v>3659051.357262097</v>
+        <v>3675356.21842196</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -558,13 +558,13 @@
         <v>195234.4955952457</v>
       </c>
       <c r="C12">
-        <v>337489.3026577411</v>
+        <v>338066.0514801582</v>
       </c>
       <c r="D12">
-        <v>705749.9270765944</v>
+        <v>707750.1928073741</v>
       </c>
       <c r="E12">
-        <v>1194532.046817181</v>
+        <v>1198129.408989331</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -575,13 +575,13 @@
         <v>838453.5995813282</v>
       </c>
       <c r="C13">
-        <v>1360534.421010592</v>
+        <v>1363937.175197454</v>
       </c>
       <c r="D13">
-        <v>2636462.053822648</v>
+        <v>2645365.467008828</v>
       </c>
       <c r="E13">
-        <v>4234182.507948725</v>
+        <v>4251571.164567933</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -592,13 +592,13 @@
         <v>195234.4955952457</v>
       </c>
       <c r="C14">
-        <v>337489.3026577411</v>
+        <v>338066.0514801582</v>
       </c>
       <c r="D14">
-        <v>705749.9270765944</v>
+        <v>707750.1928073741</v>
       </c>
       <c r="E14">
-        <v>1194532.046817181</v>
+        <v>1198129.408989331</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -609,13 +609,13 @@
         <v>899132.0137017339</v>
       </c>
       <c r="C15">
-        <v>1393817.452165214</v>
+        <v>1397578.752717299</v>
       </c>
       <c r="D15">
-        <v>2517947.770729284</v>
+        <v>2527444.07380789</v>
       </c>
       <c r="E15">
-        <v>3659051.357262097</v>
+        <v>3675356.21842196</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -626,13 +626,13 @@
         <v>2200471.39144387</v>
       </c>
       <c r="C16">
-        <v>3365760.111620627</v>
+        <v>3367926.563307574</v>
       </c>
       <c r="D16">
-        <v>5986178.391211861</v>
+        <v>6006981.07237721</v>
       </c>
       <c r="E16">
-        <v>8606048.505651264</v>
+        <v>8643372.232179193</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -643,13 +643,13 @@
         <v>195234.4955952457</v>
       </c>
       <c r="C17">
-        <v>337489.3026577411</v>
+        <v>338066.0514801582</v>
       </c>
       <c r="D17">
-        <v>705749.9270765944</v>
+        <v>707750.1928073741</v>
       </c>
       <c r="E17">
-        <v>1194532.046817181</v>
+        <v>1198129.408989331</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -660,13 +660,13 @@
         <v>919074.1380026098</v>
       </c>
       <c r="C18">
-        <v>1436119.666622292</v>
+        <v>1439711.462708424</v>
       </c>
       <c r="D18">
-        <v>2590208.333580146</v>
+        <v>2598955.546534989</v>
       </c>
       <c r="E18">
-        <v>3756129.644148062</v>
+        <v>3771555.065342521</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -677,13 +677,13 @@
         <v>2200471.39144387</v>
       </c>
       <c r="C19">
-        <v>3365760.111620627</v>
+        <v>3367926.563307574</v>
       </c>
       <c r="D19">
-        <v>5986178.391211861</v>
+        <v>6006981.07237721</v>
       </c>
       <c r="E19">
-        <v>8606048.505651264</v>
+        <v>8643372.232179193</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -694,13 +694,13 @@
         <v>2200471.39144387</v>
       </c>
       <c r="C20">
-        <v>3365760.111620627</v>
+        <v>3367926.563307574</v>
       </c>
       <c r="D20">
-        <v>5986178.391211861</v>
+        <v>6006981.07237721</v>
       </c>
       <c r="E20">
-        <v>8606048.505651264</v>
+        <v>8643372.232179193</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -711,13 +711,13 @@
         <v>2200471.39144387</v>
       </c>
       <c r="C21">
-        <v>3365760.111620627</v>
+        <v>3367926.563307574</v>
       </c>
       <c r="D21">
-        <v>5986178.391211861</v>
+        <v>6006981.07237721</v>
       </c>
       <c r="E21">
-        <v>8606048.505651264</v>
+        <v>8643372.232179193</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -725,16 +725,16 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>563608.5329930863</v>
+        <v>563609.5268254629</v>
       </c>
       <c r="C22">
-        <v>751302.1807369696</v>
+        <v>753349.7683435007</v>
       </c>
       <c r="D22">
-        <v>1114421.620864094</v>
+        <v>1119701.53684254</v>
       </c>
       <c r="E22">
-        <v>1427475.360823974</v>
+        <v>1436417.810460362</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -745,13 +745,13 @@
         <v>2251728.645556535</v>
       </c>
       <c r="C23">
-        <v>3472449.404001174</v>
+        <v>3474558.610348333</v>
       </c>
       <c r="D23">
-        <v>6165866.940024611</v>
+        <v>6185132.47980766</v>
       </c>
       <c r="E23">
-        <v>8850398.71551067</v>
+        <v>8885735.799869807</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -762,13 +762,13 @@
         <v>1405158.536529705</v>
       </c>
       <c r="C24">
-        <v>2066677.546283767</v>
+        <v>2066945.79052467</v>
       </c>
       <c r="D24">
-        <v>3859587.089677576</v>
+        <v>3864228.731234427</v>
       </c>
       <c r="E24">
-        <v>5059072.951806335</v>
+        <v>5066580.55313955</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -779,13 +779,13 @@
         <v>1654300.121020787</v>
       </c>
       <c r="C25">
-        <v>2197895.168270038</v>
+        <v>2198180.443891316</v>
       </c>
       <c r="D25">
-        <v>3650960.760505816</v>
+        <v>3655351.502519052</v>
       </c>
       <c r="E25">
-        <v>3887498.162966973</v>
+        <v>3893267.16188618</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -796,13 +796,13 @@
         <v>1654300.121020787</v>
       </c>
       <c r="C26">
-        <v>2197895.168270038</v>
+        <v>2198180.443891316</v>
       </c>
       <c r="D26">
-        <v>3650960.760505816</v>
+        <v>3655351.502519052</v>
       </c>
       <c r="E26">
-        <v>3887498.162966973</v>
+        <v>3893267.16188618</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -813,13 +813,13 @@
         <v>943540.7371439812</v>
       </c>
       <c r="C27">
-        <v>1296620.835564928</v>
+        <v>1296640.019365398</v>
       </c>
       <c r="D27">
-        <v>2216431.443771083</v>
+        <v>2221404.083015178</v>
       </c>
       <c r="E27">
-        <v>3146829.478810903</v>
+        <v>3156808.619572191</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -830,13 +830,13 @@
         <v>1145728.037960549</v>
       </c>
       <c r="C28">
-        <v>1394479.01183398</v>
+        <v>1394499.643468447</v>
       </c>
       <c r="D28">
-        <v>2086053.123549255</v>
+        <v>2090733.254602521</v>
       </c>
       <c r="E28">
-        <v>2440398.371322741</v>
+        <v>2448137.296811088</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -847,13 +847,13 @@
         <v>1145728.037960549</v>
       </c>
       <c r="C29">
-        <v>1394479.01183398</v>
+        <v>1394499.643468447</v>
       </c>
       <c r="D29">
-        <v>2086053.123549255</v>
+        <v>2090733.254602521</v>
       </c>
       <c r="E29">
-        <v>2440398.371322741</v>
+        <v>2448137.296811088</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -864,13 +864,13 @@
         <v>4639669.847489828</v>
       </c>
       <c r="C30">
-        <v>6292103.596576019</v>
+        <v>6321252.095335207</v>
       </c>
       <c r="D30">
-        <v>9754028.554325642</v>
+        <v>9886426.511897897</v>
       </c>
       <c r="E30">
-        <v>13272138.70445629</v>
+        <v>13377617.09302677</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -881,13 +881,13 @@
         <v>3946385.847290198</v>
       </c>
       <c r="C31">
-        <v>5738951.632041864</v>
+        <v>5765537.625415629</v>
       </c>
       <c r="D31">
-        <v>10082816.03368493</v>
+        <v>10219676.84375962</v>
       </c>
       <c r="E31">
-        <v>15678198.9374279</v>
+        <v>15802799.13913104</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -898,13 +898,13 @@
         <v>3090435.225095135</v>
       </c>
       <c r="C32">
-        <v>5105336.080415857</v>
+        <v>5128346.285577849</v>
       </c>
       <c r="D32">
-        <v>10659754.88025932</v>
+        <v>10794686.81804218</v>
       </c>
       <c r="E32">
-        <v>19371028.69710715</v>
+        <v>19511347.26475471</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -915,13 +915,13 @@
         <v>4293027.847390013</v>
       </c>
       <c r="C33">
-        <v>5980955.616525557</v>
+        <v>6008662.706005444</v>
       </c>
       <c r="D33">
-        <v>9863624.380778739</v>
+        <v>9997509.955851806</v>
       </c>
       <c r="E33">
-        <v>14513976.24405454</v>
+        <v>14629323.9555322</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -929,16 +929,16 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>2868864.517987219</v>
+        <v>2870439.246903104</v>
       </c>
       <c r="C34">
-        <v>4569814.074972125</v>
+        <v>4594670.849537585</v>
       </c>
       <c r="D34">
-        <v>8286189.42570718</v>
+        <v>8367771.360973991</v>
       </c>
       <c r="E34">
-        <v>13590966.58363199</v>
+        <v>13653678.76771634</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -949,13 +949,13 @@
         <v>16517477.64186718</v>
       </c>
       <c r="C35">
-        <v>22447162.24234073</v>
+        <v>22501575.71717425</v>
       </c>
       <c r="D35">
-        <v>37825009.24978029</v>
+        <v>38184171.14457833</v>
       </c>
       <c r="E35">
-        <v>58962878.75221926</v>
+        <v>59232603.20892847</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -966,13 +966,13 @@
         <v>2854074.936816617</v>
       </c>
       <c r="C36">
-        <v>4388985.814350867</v>
+        <v>4405400.465454344</v>
       </c>
       <c r="D36">
-        <v>7894462.366445839</v>
+        <v>7981665.280402457</v>
       </c>
       <c r="E36">
-        <v>12086085.40523157</v>
+        <v>12183281.35193017</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -983,13 +983,13 @@
         <v>3164373.901391268</v>
       </c>
       <c r="C37">
-        <v>4075148.433890575</v>
+        <v>4089909.597882339</v>
       </c>
       <c r="D37">
-        <v>6035252.800809962</v>
+        <v>6122640.934496854</v>
       </c>
       <c r="E37">
-        <v>8029757.649746962</v>
+        <v>8090857.740272147</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1000,13 +1000,13 @@
         <v>2173787.288781827</v>
       </c>
       <c r="C38">
-        <v>3260118.74711246</v>
+        <v>3271927.678305871</v>
       </c>
       <c r="D38">
-        <v>6478207.134814363</v>
+        <v>6572009.076478275</v>
       </c>
       <c r="E38">
-        <v>11381986.57148599</v>
+        <v>11468594.46679353</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1014,16 +1014,16 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>4661237.217781901</v>
+        <v>4663831.941563756</v>
       </c>
       <c r="C39">
-        <v>5396405.516791594</v>
+        <v>5426415.08951323</v>
       </c>
       <c r="D39">
-        <v>7283455.25453206</v>
+        <v>7361123.699597943</v>
       </c>
       <c r="E39">
-        <v>8781364.024072748</v>
+        <v>8827004.490385117</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1034,13 +1034,13 @@
         <v>21489749.26189318</v>
       </c>
       <c r="C40">
-        <v>25110384.88126251</v>
+        <v>25171254.19209323</v>
       </c>
       <c r="D40">
-        <v>35706310.2143725</v>
+        <v>36045354.30946191</v>
       </c>
       <c r="E40">
-        <v>46714143.19480981</v>
+        <v>46927836.06667255</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1051,13 +1051,13 @@
         <v>25610604.50862705</v>
       </c>
       <c r="C41">
-        <v>26336312.76267095</v>
+        <v>26400153.80753213</v>
       </c>
       <c r="D41">
-        <v>33774555.21150069</v>
+        <v>34095256.60685577</v>
       </c>
       <c r="E41">
-        <v>38858057.63040238</v>
+        <v>39035813.00301876</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1068,13 +1068,13 @@
         <v>2000341.415907979</v>
       </c>
       <c r="C42">
-        <v>3327840.544782382</v>
+        <v>3336552.931859041</v>
       </c>
       <c r="D42">
-        <v>6568983.034069482</v>
+        <v>6655887.075271232</v>
       </c>
       <c r="E42">
-        <v>11265087.45088184</v>
+        <v>11349422.14286889</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1085,13 +1085,13 @@
         <v>2340637.349906901</v>
       </c>
       <c r="C43">
-        <v>3553613.788587423</v>
+        <v>3562629.181817317</v>
       </c>
       <c r="D43">
-        <v>6564326.941931941</v>
+        <v>6644712.65125926</v>
       </c>
       <c r="E43">
-        <v>10691444.51465091</v>
+        <v>10763702.92781113</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1102,13 +1102,13 @@
         <v>7893556.217524201</v>
       </c>
       <c r="C44">
-        <v>9705917.068532195</v>
+        <v>9755012.305998022</v>
       </c>
       <c r="D44">
-        <v>14266575.86470409</v>
+        <v>14439380.29994212</v>
       </c>
       <c r="E44">
-        <v>17468343.3023025</v>
+        <v>17599390.10399219</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1119,13 +1119,13 @@
         <v>1124148.692758323</v>
       </c>
       <c r="C45">
-        <v>1673046.581845774</v>
+        <v>1674593.8672912</v>
       </c>
       <c r="D45">
-        <v>3100153.41804818</v>
+        <v>3133892.608028861</v>
       </c>
       <c r="E45">
-        <v>4824780.079002594</v>
+        <v>4860079.596032055</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1136,13 +1136,13 @@
         <v>2491020.32544697</v>
       </c>
       <c r="C46">
-        <v>3705867.812163482</v>
+        <v>3718911.452777667</v>
       </c>
       <c r="D46">
-        <v>6572557.532852385</v>
+        <v>6661057.741677734</v>
       </c>
       <c r="E46">
-        <v>10401151.42722332</v>
+        <v>10472797.98608475</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1153,13 +1153,13 @@
         <v>4061430.436880509</v>
       </c>
       <c r="C47">
-        <v>4913871.207677618</v>
+        <v>4931665.610164179</v>
       </c>
       <c r="D47">
-        <v>7413821.614221204</v>
+        <v>7489460.40664469</v>
       </c>
       <c r="E47">
-        <v>9266110.832844336</v>
+        <v>9334330.74840009</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1170,13 +1170,13 @@
         <v>1595439.954741534</v>
       </c>
       <c r="C48">
-        <v>1967750.103938571</v>
+        <v>1969503.284152237</v>
       </c>
       <c r="D48">
-        <v>2919999.53830009</v>
+        <v>2949640.559244667</v>
       </c>
       <c r="E48">
-        <v>3636022.005186967</v>
+        <v>3660237.589750136</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1187,13 +1187,13 @@
         <v>14344128.64392016</v>
       </c>
       <c r="C49">
-        <v>21907402.5071959</v>
+        <v>21938419.93912045</v>
       </c>
       <c r="D49">
-        <v>35120574.32812688</v>
+        <v>35242062.73957169</v>
       </c>
       <c r="E49">
-        <v>48326544.64545599</v>
+        <v>48469187.85308439</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1204,13 +1204,13 @@
         <v>4204451.648457175</v>
       </c>
       <c r="C50">
-        <v>6442703.564980717</v>
+        <v>6442714.483393762</v>
       </c>
       <c r="D50">
-        <v>12612663.14032256</v>
+        <v>12637178.2567492</v>
       </c>
       <c r="E50">
-        <v>21339566.69828805</v>
+        <v>21374202.80112969</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -1221,13 +1221,13 @@
         <v>2024044.102717556</v>
       </c>
       <c r="C51">
-        <v>2945529.555675043</v>
+        <v>2948383.803652209</v>
       </c>
       <c r="D51">
-        <v>4776293.560463959</v>
+        <v>4790618.575558867</v>
       </c>
       <c r="E51">
-        <v>6274046.001742887</v>
+        <v>6285293.1212527</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1238,13 +1238,13 @@
         <v>1814986.067672352</v>
       </c>
       <c r="C52">
-        <v>2803455.560274784</v>
+        <v>2812230.476397509</v>
       </c>
       <c r="D52">
-        <v>4813910.934101139</v>
+        <v>4829387.693080183</v>
       </c>
       <c r="E52">
-        <v>6853891.528464119</v>
+        <v>6868884.326164941</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -1255,13 +1255,13 @@
         <v>1806835.490144952</v>
       </c>
       <c r="C53">
-        <v>2906976.486886751</v>
+        <v>2908456.64208781</v>
       </c>
       <c r="D53">
-        <v>5392872.180088926</v>
+        <v>5410231.49245037</v>
       </c>
       <c r="E53">
-        <v>8239970.263817521</v>
+        <v>8255606.483572594</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1272,13 +1272,13 @@
         <v>1551508.499788411</v>
       </c>
       <c r="C54">
-        <v>2488740.448486364</v>
+        <v>2491245.20267866</v>
       </c>
       <c r="D54">
-        <v>4929502.40792226</v>
+        <v>4946010.138614981</v>
       </c>
       <c r="E54">
-        <v>7928052.617122171</v>
+        <v>7943777.258728998</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -1289,13 +1289,13 @@
         <v>6426316.340731291</v>
       </c>
       <c r="C55">
-        <v>7968607.040897204</v>
+        <v>7968620.545250179</v>
       </c>
       <c r="D55">
-        <v>11455171.90276131</v>
+        <v>11477437.21419943</v>
       </c>
       <c r="E55">
-        <v>13605385.11716249</v>
+        <v>13627467.92347157</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -1306,13 +1306,13 @@
         <v>6772121.252207522</v>
       </c>
       <c r="C56">
-        <v>12179141.16888438</v>
+        <v>12203507.4731863</v>
       </c>
       <c r="D56">
-        <v>21393791.79825231</v>
+        <v>21453484.19377922</v>
       </c>
       <c r="E56">
-        <v>32705294.57164634</v>
+        <v>32814774.19160548</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -1323,13 +1323,13 @@
         <v>5231217.326221793</v>
       </c>
       <c r="C57">
-        <v>8620455.243313195</v>
+        <v>8626755.97881919</v>
       </c>
       <c r="D57">
-        <v>17572879.82661736</v>
+        <v>17618042.28851031</v>
       </c>
       <c r="E57">
-        <v>29167319.47202309</v>
+        <v>29210448.78517813</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -1340,13 +1340,13 @@
         <v>991270.2158064945</v>
       </c>
       <c r="C58">
-        <v>1344104.185066116</v>
+        <v>1344117.986951136</v>
       </c>
       <c r="D58">
-        <v>2189332.193819528</v>
+        <v>2190985.230297333</v>
       </c>
       <c r="E58">
-        <v>3145082.47396321</v>
+        <v>3152027.665489087</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -1357,13 +1357,13 @@
         <v>991270.2158064945</v>
       </c>
       <c r="C59">
-        <v>1344104.185066116</v>
+        <v>1344117.986951136</v>
       </c>
       <c r="D59">
-        <v>2189332.193819528</v>
+        <v>2190985.230297333</v>
       </c>
       <c r="E59">
-        <v>3145082.47396321</v>
+        <v>3152027.665489087</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -1374,13 +1374,13 @@
         <v>2051543.436262619</v>
       </c>
       <c r="C60">
-        <v>2868704.42224883</v>
+        <v>2868781.438668471</v>
       </c>
       <c r="D60">
-        <v>5184988.391105251</v>
+        <v>5191776.990429716</v>
       </c>
       <c r="E60">
-        <v>7068463.549418587</v>
+        <v>7077476.329678638</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -1391,13 +1391,13 @@
         <v>2363734.828737365</v>
       </c>
       <c r="C61">
-        <v>3004501.081290194</v>
+        <v>3004581.743457512</v>
       </c>
       <c r="D61">
-        <v>4949307.100600467</v>
+        <v>4955787.127228366</v>
       </c>
       <c r="E61">
-        <v>5898861.667140692</v>
+        <v>5906383.12404836</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -1408,13 +1408,13 @@
         <v>331494.3450434253</v>
       </c>
       <c r="C62">
-        <v>612342.8628711026</v>
+        <v>612371.9279876745</v>
       </c>
       <c r="D62">
-        <v>1628040.323736556</v>
+        <v>1629021.471560536</v>
       </c>
       <c r="E62">
-        <v>2632097.830502131</v>
+        <v>2634281.557433697</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -1425,13 +1425,13 @@
         <v>408843.0255535579</v>
       </c>
       <c r="C63">
-        <v>675688.6762715615</v>
+        <v>675720.7481243304</v>
       </c>
       <c r="D63">
-        <v>1513791.879965569</v>
+        <v>1514704.175310674</v>
       </c>
       <c r="E63">
-        <v>1974073.372876598</v>
+        <v>1975711.168075273</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -1442,13 +1442,13 @@
         <v>409418.1831013901</v>
       </c>
       <c r="C64">
-        <v>759186.9048824609</v>
+        <v>759496.891446764</v>
       </c>
       <c r="D64">
-        <v>1917602.262174998</v>
+        <v>1918592.752756232</v>
       </c>
       <c r="E64">
-        <v>2506670.859001315</v>
+        <v>2508415.703265276</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -1459,13 +1459,13 @@
         <v>377924.4767089754</v>
       </c>
       <c r="C65">
-        <v>741734.3323564274</v>
+        <v>742037.1927928155</v>
       </c>
       <c r="D65">
-        <v>1943870.786314382</v>
+        <v>1944874.845259743</v>
       </c>
       <c r="E65">
-        <v>2770530.949422506</v>
+        <v>2772459.461503726</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -1476,13 +1476,13 @@
         <v>1334894.454666344</v>
       </c>
       <c r="C66">
-        <v>2108646.820423805</v>
+        <v>2114173.640488138</v>
       </c>
       <c r="D66">
-        <v>3993299.076419252</v>
+        <v>4025430.125502721</v>
       </c>
       <c r="E66">
-        <v>6099860.51345841</v>
+        <v>6156889.793277642</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -1493,13 +1493,13 @@
         <v>874816.0140530537</v>
       </c>
       <c r="C67">
-        <v>1704419.900662284</v>
+        <v>1708597.069873504</v>
       </c>
       <c r="D67">
-        <v>4399680.821908828</v>
+        <v>4432318.406678279</v>
       </c>
       <c r="E67">
-        <v>8881129.264596635</v>
+        <v>8957151.695417643</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -1510,13 +1510,13 @@
         <v>1078183.982615124</v>
       </c>
       <c r="C68">
-        <v>1829187.603259204</v>
+        <v>1833981.953194529</v>
       </c>
       <c r="D68">
-        <v>4135916.900577083</v>
+        <v>4169195.487127818</v>
       </c>
       <c r="E68">
-        <v>7606884.875606959</v>
+        <v>7678003.742205059</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -1527,13 +1527,13 @@
         <v>1259735.060236397</v>
       </c>
       <c r="C69">
-        <v>2019082.036169167</v>
+        <v>2024030.37508092</v>
       </c>
       <c r="D69">
-        <v>4155254.10958056</v>
+        <v>4186078.495196152</v>
       </c>
       <c r="E69">
-        <v>7046185.201663446</v>
+        <v>7106500.51867846</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -1544,13 +1544,13 @@
         <v>997290.2560204812</v>
       </c>
       <c r="C70">
-        <v>1861750.968415726</v>
+        <v>1866313.722477212</v>
       </c>
       <c r="D70">
-        <v>4350795.479443175</v>
+        <v>4383070.424381853</v>
       </c>
       <c r="E70">
-        <v>8000356.114388704</v>
+        <v>8068839.130582836</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -1561,13 +1561,13 @@
         <v>5315037.654530353</v>
       </c>
       <c r="C71">
-        <v>7148809.562600881</v>
+        <v>7168866.546309436</v>
       </c>
       <c r="D71">
-        <v>12200200.83236189</v>
+        <v>12308635.88377027</v>
       </c>
       <c r="E71">
-        <v>16913949.56082598</v>
+        <v>17064554.98387653</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -1578,13 +1578,13 @@
         <v>1539676.184733375</v>
       </c>
       <c r="C72">
-        <v>2255078.63779933</v>
+        <v>2260605.353986482</v>
       </c>
       <c r="D72">
-        <v>4008598.082183599</v>
+        <v>4038334.548306876</v>
       </c>
       <c r="E72">
-        <v>5651627.713834222</v>
+        <v>5700005.624356682</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -1595,13 +1595,13 @@
         <v>1609661.465857619</v>
       </c>
       <c r="C73">
-        <v>2228856.793173756</v>
+        <v>2234319.245219198</v>
       </c>
       <c r="D73">
-        <v>3959712.739717945</v>
+        <v>3989086.566010451</v>
       </c>
       <c r="E73">
-        <v>5504832.188799567</v>
+        <v>5551953.530217548</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -1612,13 +1612,13 @@
         <v>1679646.746981863</v>
       </c>
       <c r="C74">
-        <v>2386187.860927198</v>
+        <v>2392035.897822906</v>
       </c>
       <c r="D74">
-        <v>3910827.397252291</v>
+        <v>3939838.583714026</v>
       </c>
       <c r="E74">
-        <v>4917650.088660946</v>
+        <v>4959745.153661009</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -1629,13 +1629,13 @@
         <v>1822899.051957235</v>
       </c>
       <c r="C75">
-        <v>2432842.893761189</v>
+        <v>2433718.556576926</v>
       </c>
       <c r="D75">
-        <v>4033960.50120692</v>
+        <v>4046593.046042328</v>
       </c>
       <c r="E75">
-        <v>4626442.529933055</v>
+        <v>4654511.066708672</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -1646,13 +1646,13 @@
         <v>1364712.981922764</v>
       </c>
       <c r="C76">
-        <v>2176413.103922609</v>
+        <v>2181747.027684628</v>
       </c>
       <c r="D76">
-        <v>4106368.767114906</v>
+        <v>4136830.512899727</v>
       </c>
       <c r="E76">
-        <v>6238809.813972843</v>
+        <v>6292214.00091322</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -1663,13 +1663,13 @@
         <v>3249306.505666658</v>
       </c>
       <c r="C77">
-        <v>4741734.739953597</v>
+        <v>4748308.636097455</v>
       </c>
       <c r="D77">
-        <v>8733717.077185402</v>
+        <v>8790951.593227087</v>
       </c>
       <c r="E77">
-        <v>12879048.93062018</v>
+        <v>12984836.22118209</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -1680,13 +1680,13 @@
         <v>2160621.336242262</v>
       </c>
       <c r="C78">
-        <v>4489514.806977342</v>
+        <v>4495739.027794399</v>
       </c>
       <c r="D78">
-        <v>9597491.293610331</v>
+        <v>9660386.366183612</v>
       </c>
       <c r="E78">
-        <v>16007857.42788949</v>
+        <v>16139344.45570656</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -1697,13 +1697,13 @@
         <v>4019760.625566999</v>
       </c>
       <c r="C79">
-        <v>5019176.666227478</v>
+        <v>5026135.205230817</v>
       </c>
       <c r="D79">
-        <v>8157867.599568781</v>
+        <v>8211328.41125607</v>
       </c>
       <c r="E79">
-        <v>10259581.35151099</v>
+        <v>10343852.58297557</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -1714,13 +1714,13 @@
         <v>3785274.589075591</v>
       </c>
       <c r="C80">
-        <v>4893066.69973935</v>
+        <v>4899850.401079289</v>
       </c>
       <c r="D80">
-        <v>8349817.425440989</v>
+        <v>8404536.138579743</v>
       </c>
       <c r="E80">
-        <v>11059974.22290546</v>
+        <v>11150819.80576089</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -1731,13 +1731,13 @@
         <v>853935.0074429346</v>
       </c>
       <c r="C81">
-        <v>1113735.330747656</v>
+        <v>1117112.182395427</v>
       </c>
       <c r="D81">
-        <v>1858009.092164721</v>
+        <v>1878028.160410056</v>
       </c>
       <c r="E81">
-        <v>2701240.472636871</v>
+        <v>2721947.50231659</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -1748,13 +1748,13 @@
         <v>954397.9494950445</v>
       </c>
       <c r="C82">
-        <v>1248733.552656463</v>
+        <v>1252519.719655479</v>
       </c>
       <c r="D82">
-        <v>1803361.765924582</v>
+        <v>1822792.038045054</v>
       </c>
       <c r="E82">
-        <v>2160992.378109497</v>
+        <v>2177558.001853272</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -1765,13 +1765,13 @@
         <v>2122032.355006795</v>
       </c>
       <c r="C83">
-        <v>3590658.552409123</v>
+        <v>3590719.605113259</v>
       </c>
       <c r="D83">
-        <v>7594278.706664633</v>
+        <v>7618969.462624854</v>
       </c>
       <c r="E83">
-        <v>12993026.59647819</v>
+        <v>13056654.15284051</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -1782,13 +1782,13 @@
         <v>3642543.727491979</v>
       </c>
       <c r="C84">
-        <v>4375372.01088264</v>
+        <v>4375446.406230725</v>
       </c>
       <c r="D84">
-        <v>6628532.281539651</v>
+        <v>6650083.172580075</v>
       </c>
       <c r="E84">
-        <v>7490877.578581814</v>
+        <v>7527560.812607029</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -1799,13 +1799,13 @@
         <v>2424207.199588601</v>
       </c>
       <c r="C85">
-        <v>2827881.340775832</v>
+        <v>2828434.018162626</v>
       </c>
       <c r="D85">
-        <v>4044089.067364762</v>
+        <v>4084079.500080615</v>
       </c>
       <c r="E85">
-        <v>4869296.269836106</v>
+        <v>4902009.477040051</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -1816,13 +1816,13 @@
         <v>2477486.478700439</v>
       </c>
       <c r="C86">
-        <v>2933926.891054925</v>
+        <v>2934500.293843725</v>
       </c>
       <c r="D86">
-        <v>3988690.586989902</v>
+        <v>4028133.205558963</v>
       </c>
       <c r="E86">
-        <v>4560134.601910004</v>
+        <v>4590770.780085127</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -1833,13 +1833,13 @@
         <v>742314.5930747868</v>
       </c>
       <c r="C87">
-        <v>1010564.717342376</v>
+        <v>1013224.296139993</v>
       </c>
       <c r="D87">
-        <v>1573885.536901175</v>
+        <v>1590821.765321835</v>
       </c>
       <c r="E87">
-        <v>2279429.004238571</v>
+        <v>2295490.44295749</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -1850,13 +1850,13 @@
         <v>691120.4832075601</v>
       </c>
       <c r="C88">
-        <v>975717.6581236734</v>
+        <v>978285.5273075793</v>
       </c>
       <c r="D88">
-        <v>1630095.734647646</v>
+        <v>1647636.828369044</v>
       </c>
       <c r="E88">
-        <v>2436631.004530886</v>
+        <v>2453800.128678696</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -1867,13 +1867,13 @@
         <v>793508.7029420135</v>
       </c>
       <c r="C89">
-        <v>1045411.776561079</v>
+        <v>1048163.064972406</v>
       </c>
       <c r="D89">
-        <v>1573885.536901175</v>
+        <v>1590821.765321835</v>
       </c>
       <c r="E89">
-        <v>2043626.003800098</v>
+        <v>2058025.91437568</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -1881,16 +1881,16 @@
         <v>89</v>
       </c>
       <c r="B90">
-        <v>150488331.2396595</v>
+        <v>150489419.3507757</v>
       </c>
       <c r="C90">
-        <v>183548105.295291</v>
+        <v>183766380.8617029</v>
       </c>
       <c r="D90">
-        <v>234661023.4965205</v>
+        <v>235349084.2321411</v>
       </c>
       <c r="E90">
-        <v>284412418.6463632</v>
+        <v>284699587.7025704</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -1898,16 +1898,16 @@
         <v>90</v>
       </c>
       <c r="B91">
-        <v>34716260.14987721</v>
+        <v>34716511.16700441</v>
       </c>
       <c r="C91">
-        <v>47066679.78284716</v>
+        <v>47122651.5193693</v>
       </c>
       <c r="D91">
-        <v>65124166.78144479</v>
+        <v>65315120.44488086</v>
       </c>
       <c r="E91">
-        <v>85314360.68055215</v>
+        <v>85400501.94173253</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -1915,16 +1915,16 @@
         <v>91</v>
       </c>
       <c r="B92">
-        <v>30978373.73256004</v>
+        <v>30978597.72276942</v>
       </c>
       <c r="C92">
-        <v>44438591.06400798</v>
+        <v>44491437.47514056</v>
       </c>
       <c r="D92">
-        <v>67493708.06105135</v>
+        <v>67691609.56904906</v>
       </c>
       <c r="E92">
-        <v>97114151.51013455</v>
+        <v>97212206.93038049</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -1932,16 +1932,16 @@
         <v>92</v>
       </c>
       <c r="B93">
-        <v>62519990.62389391</v>
+        <v>62520442.67686192</v>
       </c>
       <c r="C93">
-        <v>84636402.60443455</v>
+        <v>84737052.28800292</v>
       </c>
       <c r="D93">
-        <v>126502929.6048018</v>
+        <v>126873854.8547862</v>
       </c>
       <c r="E93">
-        <v>180930126.0535969</v>
+        <v>181112809.8259355</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -1949,16 +1949,16 @@
         <v>93</v>
       </c>
       <c r="B94">
-        <v>39989937.96921921</v>
+        <v>39995749.88104557</v>
       </c>
       <c r="C94">
-        <v>67468312.07676394</v>
+        <v>67588755.40567623</v>
       </c>
       <c r="D94">
-        <v>140868354.7292616</v>
+        <v>141306733.5578713</v>
       </c>
       <c r="E94">
-        <v>253844264.3285323</v>
+        <v>254068076.4572394</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -1966,16 +1966,16 @@
         <v>94</v>
       </c>
       <c r="B95">
-        <v>18177392.85133689</v>
+        <v>18177524.2836085</v>
       </c>
       <c r="C95">
-        <v>24608467.09458506</v>
+        <v>24637731.50505095</v>
       </c>
       <c r="D95">
-        <v>34473003.77750188</v>
+        <v>34574083.70967285</v>
       </c>
       <c r="E95">
-        <v>45981724.58194413</v>
+        <v>46028151.97957264</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -1983,16 +1983,16 @@
         <v>95</v>
       </c>
       <c r="B96">
-        <v>5581227.664213297</v>
+        <v>5581268.01947416</v>
       </c>
       <c r="C96">
-        <v>7943995.445582071</v>
+        <v>7953442.451873246</v>
       </c>
       <c r="D96">
-        <v>12306327.29085987</v>
+        <v>12342411.25777678</v>
       </c>
       <c r="E96">
-        <v>17980633.64507795</v>
+        <v>17998788.55413024</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2000,16 +2000,16 @@
         <v>96</v>
       </c>
       <c r="B97">
-        <v>5837247.28183776</v>
+        <v>5837289.488257378</v>
       </c>
       <c r="C97">
-        <v>8362100.469033759</v>
+        <v>8372044.686182363</v>
       </c>
       <c r="D97">
-        <v>12459200.92180223</v>
+        <v>12495733.13675538</v>
       </c>
       <c r="E97">
-        <v>17793335.37794172</v>
+        <v>17811301.17335805</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2017,16 +2017,16 @@
         <v>97</v>
       </c>
       <c r="B98">
-        <v>6710257.815394146</v>
+        <v>6710295.315612996</v>
       </c>
       <c r="C98">
-        <v>10529947.08163605</v>
+        <v>10548573.52511335</v>
       </c>
       <c r="D98">
-        <v>16944145.88767318</v>
+        <v>17010505.95716884</v>
       </c>
       <c r="E98">
-        <v>25443469.57767718</v>
+        <v>25475919.40819523</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2034,16 +2034,16 @@
         <v>98</v>
       </c>
       <c r="B99">
-        <v>3479392.941315483</v>
+        <v>3479412.385873405</v>
       </c>
       <c r="C99">
-        <v>4318461.443592314</v>
+        <v>4326100.378276825</v>
       </c>
       <c r="D99">
-        <v>5930451.060685614</v>
+        <v>5953677.085009092</v>
       </c>
       <c r="E99">
-        <v>7538805.800793238</v>
+        <v>7548420.565391178</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2051,16 +2051,16 @@
         <v>99</v>
       </c>
       <c r="B100">
-        <v>9117303.168081446</v>
+        <v>9117306.228509678</v>
       </c>
       <c r="C100">
-        <v>11018192.16953246</v>
+        <v>11027220.18017333</v>
       </c>
       <c r="D100">
-        <v>14681492.61283479</v>
+        <v>14725192.17546085</v>
       </c>
       <c r="E100">
-        <v>18797278.58368233</v>
+        <v>18817570.4801988</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2068,16 +2068,16 @@
         <v>100</v>
       </c>
       <c r="B101">
-        <v>4331978.300856378</v>
+        <v>4331979.754982499</v>
       </c>
       <c r="C101">
-        <v>5892081.374081532</v>
+        <v>5896909.187258462</v>
       </c>
       <c r="D101">
-        <v>8748039.639772026</v>
+        <v>8774078.23926424</v>
       </c>
       <c r="E101">
-        <v>12344481.45794063</v>
+        <v>12357807.47953354</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2085,16 +2085,16 @@
         <v>101</v>
       </c>
       <c r="B102">
-        <v>906693.1327373814</v>
+        <v>906693.4370893602</v>
       </c>
       <c r="C102">
-        <v>1060574.647334676</v>
+        <v>1061443.653706523</v>
       </c>
       <c r="D102">
-        <v>1369258.3783991</v>
+        <v>1373333.985276142</v>
       </c>
       <c r="E102">
-        <v>1683338.380628268</v>
+        <v>1685155.565390937</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2102,16 +2102,16 @@
         <v>102</v>
       </c>
       <c r="B103">
-        <v>4597319.600323708</v>
+        <v>4597330.929663979</v>
       </c>
       <c r="C103">
-        <v>5834155.99361275</v>
+        <v>5852707.255909893</v>
       </c>
       <c r="D103">
-        <v>7962375.846478515</v>
+        <v>8002139.03988087</v>
       </c>
       <c r="E103">
-        <v>9905933.406396288</v>
+        <v>9922323.818262648</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -2119,16 +2119,16 @@
         <v>103</v>
       </c>
       <c r="B104">
-        <v>10806070.81313201</v>
+        <v>10806097.44292152</v>
       </c>
       <c r="C104">
-        <v>14413797.16069032</v>
+        <v>14459629.6910715</v>
       </c>
       <c r="D104">
-        <v>20626345.0499253</v>
+        <v>20729350.6556914</v>
       </c>
       <c r="E104">
-        <v>27474947.37245763</v>
+        <v>27520407.57140772</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -2139,13 +2139,13 @@
         <v>1148086.576293358</v>
       </c>
       <c r="C105">
-        <v>1888284.916378578</v>
+        <v>1889022.595143988</v>
       </c>
       <c r="D105">
-        <v>2883625.599050695</v>
+        <v>2892220.13975289</v>
       </c>
       <c r="E105">
-        <v>3936599.140673195</v>
+        <v>3941574.848463994</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -2153,16 +2153,16 @@
         <v>105</v>
       </c>
       <c r="B106">
-        <v>1216718.537594818</v>
+        <v>1216720.701539854</v>
       </c>
       <c r="C106">
-        <v>1843454.577963492</v>
+        <v>1848826.639186701</v>
       </c>
       <c r="D106">
-        <v>2977309.212397879</v>
+        <v>2990080.827038481</v>
       </c>
       <c r="E106">
-        <v>4197421.762742564</v>
+        <v>4203007.687999449</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -2170,16 +2170,16 @@
         <v>106</v>
       </c>
       <c r="B107">
-        <v>5256224.082409615</v>
+        <v>5256233.430652169</v>
       </c>
       <c r="C107">
-        <v>8027947.355647467</v>
+        <v>8051341.815813053</v>
       </c>
       <c r="D107">
-        <v>13946343.15281112</v>
+        <v>14006168.08454867</v>
       </c>
       <c r="E107">
-        <v>22131860.2035517</v>
+        <v>22161313.26399709</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -2190,13 +2190,13 @@
         <v>11082070.03850278</v>
       </c>
       <c r="C108">
-        <v>14559790.67799711</v>
+        <v>14564641.14165993</v>
       </c>
       <c r="D108">
-        <v>20689206.2000137</v>
+        <v>20741726.98949262</v>
       </c>
       <c r="E108">
-        <v>27254505.57239825</v>
+        <v>27281331.13800905</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -2207,13 +2207,13 @@
         <v>1639265.314421703</v>
       </c>
       <c r="C109">
-        <v>2431756.157690702</v>
+        <v>2438561.264584122</v>
       </c>
       <c r="D109">
-        <v>3907095.054722896</v>
+        <v>3925211.030453685</v>
       </c>
       <c r="E109">
-        <v>5852117.250533628</v>
+        <v>5861381.368729084</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -2224,13 +2224,13 @@
         <v>83602531.03550684</v>
       </c>
       <c r="C110">
-        <v>81887974.7985148</v>
+        <v>82117132.81669322</v>
       </c>
       <c r="D110">
-        <v>93620008.42662939</v>
+        <v>94054095.07587099</v>
       </c>
       <c r="E110">
-        <v>93819657.508555</v>
+        <v>93968177.49867262</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -2241,13 +2241,13 @@
         <v>14331862.46322974</v>
       </c>
       <c r="C111">
-        <v>18322999.88585552</v>
+        <v>18374275.57500594</v>
       </c>
       <c r="D111">
-        <v>26973983.16625999</v>
+        <v>27099053.07563217</v>
       </c>
       <c r="E111">
-        <v>38270989.00348976</v>
+        <v>38331573.39549813</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -2255,16 +2255,16 @@
         <v>111</v>
       </c>
       <c r="B112">
-        <v>2877320.170376125</v>
+        <v>2877443.115439584</v>
       </c>
       <c r="C112">
-        <v>4289150.211119502</v>
+        <v>4306874.702453329</v>
       </c>
       <c r="D112">
-        <v>7336192.967479452</v>
+        <v>7373158.333775787</v>
       </c>
       <c r="E112">
-        <v>11442164.68493483</v>
+        <v>11459775.14333591</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -2275,13 +2275,13 @@
         <v>1366621.151332422</v>
       </c>
       <c r="C113">
-        <v>1545776.243689775</v>
+        <v>1549095.386711885</v>
       </c>
       <c r="D113">
-        <v>2078775.474543818</v>
+        <v>2088855.050889579</v>
       </c>
       <c r="E113">
-        <v>2401676.582568931</v>
+        <v>2405853.343142598</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -2292,13 +2292,13 @@
         <v>2309245.895211886</v>
       </c>
       <c r="C114">
-        <v>3436594.054614981</v>
+        <v>3443717.950718408</v>
       </c>
       <c r="D114">
-        <v>6271123.206225658</v>
+        <v>6299388.317441188</v>
       </c>
       <c r="E114">
-        <v>9809525.414544623</v>
+        <v>9824876.120645797</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -2306,16 +2306,16 @@
         <v>114</v>
       </c>
       <c r="B115">
-        <v>6186238.36630867</v>
+        <v>6186502.698195105</v>
       </c>
       <c r="C115">
-        <v>8056647.018183929</v>
+        <v>8089940.319473145</v>
       </c>
       <c r="D115">
-        <v>11386382.83494207</v>
+        <v>11443756.16388117</v>
       </c>
       <c r="E115">
-        <v>15099905.85470908</v>
+        <v>15123145.88587772</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -2323,16 +2323,16 @@
         <v>115</v>
       </c>
       <c r="B116">
-        <v>4651667.608774736</v>
+        <v>4651866.369960661</v>
       </c>
       <c r="C116">
-        <v>6201879.359321442</v>
+        <v>6227508.015709544</v>
       </c>
       <c r="D116">
-        <v>9170241.209349316</v>
+        <v>9216447.917219732</v>
       </c>
       <c r="E116">
-        <v>12755199.97664866</v>
+        <v>12774831.30732528</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -2343,13 +2343,13 @@
         <v>774418.652421706</v>
       </c>
       <c r="C117">
-        <v>1104125.888349839</v>
+        <v>1106496.704794203</v>
       </c>
       <c r="D117">
-        <v>1633323.587141571</v>
+        <v>1641243.254270384</v>
       </c>
       <c r="E117">
-        <v>2309304.40631628</v>
+        <v>2313320.522252498</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -2360,13 +2360,13 @@
         <v>655666.3201716493</v>
       </c>
       <c r="C118">
-        <v>632217.7962873267</v>
+        <v>633474.9547189182</v>
       </c>
       <c r="D118">
-        <v>845255.7048433771</v>
+        <v>848728.3873133846</v>
       </c>
       <c r="E118">
-        <v>1132997.091181556</v>
+        <v>1134572.554599854</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -2377,13 +2377,13 @@
         <v>262255.7476331354</v>
       </c>
       <c r="C119">
-        <v>318470.0914070475</v>
+        <v>318779.430966848</v>
       </c>
       <c r="D119">
-        <v>433472.9548923846</v>
+        <v>435351.5895093408</v>
       </c>
       <c r="E119">
-        <v>546115.0257792354</v>
+        <v>547006.6487563979</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -2391,16 +2391,16 @@
         <v>119</v>
       </c>
       <c r="B120">
-        <v>18192743.24331593</v>
+        <v>18193031.52394382</v>
       </c>
       <c r="C120">
-        <v>27670531.69053792</v>
+        <v>27722204.0764513</v>
       </c>
       <c r="D120">
-        <v>42195917.68998375</v>
+        <v>42353430.59746315</v>
       </c>
       <c r="E120">
-        <v>60231152.79158749</v>
+        <v>60302170.78477574</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -2408,16 +2408,16 @@
         <v>120</v>
       </c>
       <c r="B121">
-        <v>21509652.23242878</v>
+        <v>21509993.07250816</v>
       </c>
       <c r="C121">
-        <v>23038983.46765818</v>
+        <v>23082006.82760323</v>
       </c>
       <c r="D121">
-        <v>26803214.50361944</v>
+        <v>26903268.07461362</v>
       </c>
       <c r="E121">
-        <v>29038347.38008106</v>
+        <v>29072586.22594165</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -2428,13 +2428,13 @@
         <v>15296003.97811855</v>
       </c>
       <c r="C122">
-        <v>18055562.14140044</v>
+        <v>18090696.47238314</v>
       </c>
       <c r="D122">
-        <v>24217757.67968421</v>
+        <v>24306498.17893496</v>
       </c>
       <c r="E122">
-        <v>30807820.31661708</v>
+        <v>30848880.91684932</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -2445,13 +2445,13 @@
         <v>6275283.683330687</v>
       </c>
       <c r="C123">
-        <v>8180513.591573015</v>
+        <v>8196432.058684918</v>
       </c>
       <c r="D123">
-        <v>11387660.35094869</v>
+        <v>11429387.85843337</v>
       </c>
       <c r="E123">
-        <v>14985072.72197991</v>
+        <v>15005044.79641311</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -2462,13 +2462,13 @@
         <v>3529847.071873511</v>
       </c>
       <c r="C124">
-        <v>4148689.035726315</v>
+        <v>4156761.97261878</v>
       </c>
       <c r="D124">
-        <v>5010570.554417424</v>
+        <v>5028930.657710682</v>
       </c>
       <c r="E124">
-        <v>5677574.136899219</v>
+        <v>5685141.196156521</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -2476,16 +2476,16 @@
         <v>124</v>
       </c>
       <c r="B125">
-        <v>7502220.349834859</v>
+        <v>7502550.902010841</v>
       </c>
       <c r="C125">
-        <v>8880843.867809592</v>
+        <v>8903202.474665577</v>
       </c>
       <c r="D125">
-        <v>12185164.06752179</v>
+        <v>12236406.72607666</v>
       </c>
       <c r="E125">
-        <v>15810972.99427298</v>
+        <v>15836131.00601899</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -2493,16 +2493,16 @@
         <v>125</v>
       </c>
       <c r="B126">
-        <v>7104350.290928474</v>
+        <v>7104659.378677444</v>
       </c>
       <c r="C126">
-        <v>8038587.071101896</v>
+        <v>8057568.325556455</v>
       </c>
       <c r="D126">
-        <v>9080368.756518442</v>
+        <v>9115446.273555893</v>
       </c>
       <c r="E126">
-        <v>9164164.407888539</v>
+        <v>9177379.34089802</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -2510,16 +2510,16 @@
         <v>126</v>
       </c>
       <c r="B127">
-        <v>10141870.13919533</v>
+        <v>10146046.23329221</v>
       </c>
       <c r="C127">
-        <v>13445186.7205831</v>
+        <v>13491938.49521889</v>
       </c>
       <c r="D127">
-        <v>19002094.58790898</v>
+        <v>19072905.19492172</v>
       </c>
       <c r="E127">
-        <v>25534485.76262899</v>
+        <v>25565015.4502699</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -2530,13 +2530,13 @@
         <v>1825205.506967242</v>
       </c>
       <c r="C128">
-        <v>2405491.36063779</v>
+        <v>2409844.170824423</v>
       </c>
       <c r="D128">
-        <v>3388314.076952206</v>
+        <v>3398003.257001105</v>
       </c>
       <c r="E128">
-        <v>4507889.602500559</v>
+        <v>4512671.055235111</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -2547,13 +2547,13 @@
         <v>11813135.64231576</v>
       </c>
       <c r="C129">
-        <v>14493085.44784269</v>
+        <v>14519311.12921714</v>
       </c>
       <c r="D129">
-        <v>19251784.52813753</v>
+        <v>19306836.68750628</v>
       </c>
       <c r="E129">
-        <v>24417735.34687803</v>
+        <v>24443634.88252352</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -2561,16 +2561,16 @@
         <v>129</v>
       </c>
       <c r="B130">
-        <v>3372840.696873519</v>
+        <v>3372995.837571415</v>
       </c>
       <c r="C130">
-        <v>5166450.135597482</v>
+        <v>5172313.657730713</v>
       </c>
       <c r="D130">
-        <v>8249672.01873983</v>
+        <v>8272611.398445164</v>
       </c>
       <c r="E130">
-        <v>12457818.39389835</v>
+        <v>12469753.18320611</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -2578,16 +2578,16 @@
         <v>130</v>
       </c>
       <c r="B131">
-        <v>10833973.14753312</v>
+        <v>10834471.4782597</v>
       </c>
       <c r="C131">
-        <v>12114434.80071134</v>
+        <v>12128183.74916167</v>
       </c>
       <c r="D131">
-        <v>14228792.1057164</v>
+        <v>14268357.27438249</v>
       </c>
       <c r="E131">
-        <v>15804694.97733372</v>
+        <v>15819836.12794806</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -2595,16 +2595,16 @@
         <v>131</v>
       </c>
       <c r="B132">
-        <v>23456573.93734765</v>
+        <v>23457652.87038302</v>
       </c>
       <c r="C132">
-        <v>30820547.36063326</v>
+        <v>30855526.30301426</v>
       </c>
       <c r="D132">
-        <v>41172675.02930704</v>
+        <v>41287161.47480889</v>
       </c>
       <c r="E132">
-        <v>52713306.18910719</v>
+        <v>52763806.37968557</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -2612,16 +2612,16 @@
         <v>132</v>
       </c>
       <c r="B133">
-        <v>11140595.02906708</v>
+        <v>11141107.46349346</v>
       </c>
       <c r="C133">
-        <v>13302124.48705559</v>
+        <v>13317221.3716285</v>
       </c>
       <c r="D133">
-        <v>16877769.3594402</v>
+        <v>16924700.38397497</v>
       </c>
       <c r="E133">
-        <v>20360165.88256521</v>
+        <v>20379671.24718014</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -2629,16 +2629,16 @@
         <v>133</v>
       </c>
       <c r="B134">
-        <v>7310519.674068897</v>
+        <v>7311593.697093166</v>
       </c>
       <c r="C134">
-        <v>13761319.93994083</v>
+        <v>13787331.61258147</v>
       </c>
       <c r="D134">
-        <v>33045761.44549131</v>
+        <v>33157369.22480923</v>
       </c>
       <c r="E134">
-        <v>64056592.32777459</v>
+        <v>64120359.42036068</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -2646,16 +2646,16 @@
         <v>134</v>
       </c>
       <c r="B135">
-        <v>11798608.73510737</v>
+        <v>11799019.23920403</v>
       </c>
       <c r="C135">
-        <v>13184524.61524504</v>
+        <v>13202918.72359691</v>
       </c>
       <c r="D135">
-        <v>17488008.75199287</v>
+        <v>17541915.51176436</v>
       </c>
       <c r="E135">
-        <v>22799448.56886022</v>
+        <v>22823874.82239392</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -2663,16 +2663,16 @@
         <v>135</v>
       </c>
       <c r="B136">
-        <v>14508829.96320861</v>
+        <v>14509533.85760882</v>
       </c>
       <c r="C136">
-        <v>21184299.8701001</v>
+        <v>21224568.01601344</v>
       </c>
       <c r="D136">
-        <v>33296540.91905734</v>
+        <v>33405125.71511629</v>
       </c>
       <c r="E136">
-        <v>49646156.10424899</v>
+        <v>49705180.94160601</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -2680,16 +2680,16 @@
         <v>136</v>
       </c>
       <c r="B137">
-        <v>3839106.210196092</v>
+        <v>3839292.464040821</v>
       </c>
       <c r="C137">
-        <v>4804089.861252208</v>
+        <v>4813221.708549495</v>
       </c>
       <c r="D137">
-        <v>6466069.330263368</v>
+        <v>6487156.109855172</v>
       </c>
       <c r="E137">
-        <v>8458234.002946125</v>
+        <v>8468290.086347692</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -2697,16 +2697,16 @@
         <v>137</v>
       </c>
       <c r="B138">
-        <v>9622694.786595399</v>
+        <v>9623161.630647773</v>
       </c>
       <c r="C138">
-        <v>11460358.94611973</v>
+        <v>11482143.3529253</v>
       </c>
       <c r="D138">
-        <v>14938849.83198778</v>
+        <v>14987567.56414816</v>
       </c>
       <c r="E138">
-        <v>18755214.52827184</v>
+        <v>18777512.80016227</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -2717,13 +2717,13 @@
         <v>48849900.46614627</v>
       </c>
       <c r="C139">
-        <v>74859066.0856557</v>
+        <v>75015943.7466839</v>
       </c>
       <c r="D139">
-        <v>106655464.3818232</v>
+        <v>107023184.1895752</v>
       </c>
       <c r="E139">
-        <v>142870181.5654415</v>
+        <v>143047944.6367794</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -2731,16 +2731,16 @@
         <v>139</v>
       </c>
       <c r="B140">
-        <v>15213988.42981686</v>
+        <v>15215063.50862265</v>
       </c>
       <c r="C140">
-        <v>24737370.60694013</v>
+        <v>24784449.82519073</v>
       </c>
       <c r="D140">
-        <v>36336718.99775623</v>
+        <v>36458401.72064592</v>
       </c>
       <c r="E140">
-        <v>49898431.82960653</v>
+        <v>49970857.72797479</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -2751,13 +2751,13 @@
         <v>17287629.08306491</v>
       </c>
       <c r="C141">
-        <v>25432518.9929745</v>
+        <v>25485816.39971889</v>
       </c>
       <c r="D141">
-        <v>36465940.56696108</v>
+        <v>36591665.47690827</v>
       </c>
       <c r="E141">
-        <v>49578427.34246557</v>
+        <v>49640114.20686188</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -2768,13 +2768,13 @@
         <v>2766020.653290385</v>
       </c>
       <c r="C142">
-        <v>4027774.501149807</v>
+        <v>4036215.266923807</v>
       </c>
       <c r="D142">
-        <v>6892952.180340204</v>
+        <v>6916717.25478144</v>
       </c>
       <c r="E142">
-        <v>10997063.36616611</v>
+        <v>11010746.21963665</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -2785,13 +2785,13 @@
         <v>13242925.94989722</v>
       </c>
       <c r="C143">
-        <v>21579959.34997349</v>
+        <v>21621945.954974</v>
       </c>
       <c r="D143">
-        <v>36290809.99425524</v>
+        <v>36415278.96672139</v>
       </c>
       <c r="E143">
-        <v>56524174.9391074</v>
+        <v>56598421.17930981</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -2802,13 +2802,13 @@
         <v>4959897.359512068</v>
       </c>
       <c r="C144">
-        <v>6980040.760099242</v>
+        <v>6993621.333145229</v>
       </c>
       <c r="D144">
-        <v>11798246.87056035</v>
+        <v>11838712.09206169</v>
       </c>
       <c r="E144">
-        <v>18841391.64636914</v>
+        <v>18866140.39310327</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -2819,13 +2819,13 @@
         <v>6100673.752199844</v>
       </c>
       <c r="C145">
-        <v>10528228.14648302</v>
+        <v>10548712.17749405</v>
       </c>
       <c r="D145">
-        <v>22476407.01290294</v>
+        <v>22553495.82095296</v>
       </c>
       <c r="E145">
-        <v>41267243.16692557</v>
+        <v>41321448.95855302</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -2836,13 +2836,13 @@
         <v>9835829.67643458</v>
       </c>
       <c r="C146">
-        <v>16116792.11627319</v>
+        <v>16145955.94452363</v>
       </c>
       <c r="D146">
-        <v>23256155.70999014</v>
+        <v>23322658.71850758</v>
       </c>
       <c r="E146">
-        <v>31179569.75062886</v>
+        <v>31212641.46537619</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -2853,13 +2853,13 @@
         <v>9276588.207670514</v>
       </c>
       <c r="C147">
-        <v>12664049.50583484</v>
+        <v>12680154.69958696</v>
       </c>
       <c r="D147">
-        <v>21311832.13059213</v>
+        <v>21382089.16613622</v>
       </c>
       <c r="E147">
-        <v>34389020.76267499</v>
+        <v>34439410.70140707</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -2870,13 +2870,13 @@
         <v>8047885.070016755</v>
       </c>
       <c r="C148">
-        <v>10224404.30116032</v>
+        <v>10237661.14951293</v>
       </c>
       <c r="D148">
-        <v>14146368.21765955</v>
+        <v>14196768.99924026</v>
       </c>
       <c r="E148">
-        <v>19043569.65802746</v>
+        <v>19074173.05334436</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -2887,13 +2887,13 @@
         <v>5004463.720811648</v>
       </c>
       <c r="C149">
-        <v>5663690.82766612</v>
+        <v>5667473.336618471</v>
       </c>
       <c r="D149">
-        <v>7438807.705947097</v>
+        <v>7468857.035179182</v>
       </c>
       <c r="E149">
-        <v>9662275.426536478</v>
+        <v>9683856.425670806</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -2904,13 +2904,13 @@
         <v>2680962.707577669</v>
       </c>
       <c r="C150">
-        <v>3295238.299733015</v>
+        <v>3297439.032214383</v>
       </c>
       <c r="D150">
-        <v>4530910.148167777</v>
+        <v>4549212.92142732</v>
       </c>
       <c r="E150">
-        <v>6125192.457893659</v>
+        <v>6138873.269844886</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -2921,13 +2921,13 @@
         <v>21090239.96627766</v>
       </c>
       <c r="C151">
-        <v>22963691.90126445</v>
+        <v>22979028.25574398</v>
       </c>
       <c r="D151">
-        <v>25968201.44621532</v>
+        <v>26073100.92280732</v>
       </c>
       <c r="E151">
-        <v>26571257.42297531</v>
+        <v>26630605.17059472</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -2938,13 +2938,13 @@
         <v>5361925.415155337</v>
       </c>
       <c r="C152">
-        <v>6950893.288499329</v>
+        <v>6955535.458577215</v>
       </c>
       <c r="D152">
-        <v>9670450.017731227</v>
+        <v>9709514.145732936</v>
       </c>
       <c r="E152">
-        <v>13026817.76256257</v>
+        <v>13055913.57389546</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -2955,13 +2955,13 @@
         <v>34676472.85706288</v>
       </c>
       <c r="C153">
-        <v>38736581.27703659</v>
+        <v>38853431.29299535</v>
       </c>
       <c r="D153">
-        <v>49387286.79790337</v>
+        <v>49656984.87955813</v>
       </c>
       <c r="E153">
-        <v>59326512.20638508</v>
+        <v>59461032.88571883</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -2972,13 +2972,13 @@
         <v>6952568.032362546</v>
       </c>
       <c r="C154">
-        <v>9144710.168849487</v>
+        <v>9172295.451131528</v>
       </c>
       <c r="D154">
-        <v>13073105.32885678</v>
+        <v>13144495.9975301</v>
       </c>
       <c r="E154">
-        <v>17709406.62877167</v>
+        <v>17749562.05543846</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -2989,13 +2989,13 @@
         <v>17631257.85996554</v>
       </c>
       <c r="C155">
-        <v>19870168.18569447</v>
+        <v>19892304.80026738</v>
       </c>
       <c r="D155">
-        <v>26361738.22333463</v>
+        <v>26524113.2644249</v>
       </c>
       <c r="E155">
-        <v>33874600.04577429</v>
+        <v>33986161.44464172</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -3006,13 +3006,13 @@
         <v>5863418.311569934</v>
       </c>
       <c r="C156">
-        <v>7338143.646515463</v>
+        <v>7346318.799139512</v>
       </c>
       <c r="D156">
-        <v>10237568.2420717</v>
+        <v>10300626.51045627</v>
       </c>
       <c r="E156">
-        <v>13850205.93004565</v>
+        <v>13895819.70396681</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -3023,13 +3023,13 @@
         <v>6007472.845731005</v>
       </c>
       <c r="C157">
-        <v>7167129.228471961</v>
+        <v>7174964.167928196</v>
       </c>
       <c r="D157">
-        <v>9895059.386567978</v>
+        <v>9952449.665616779</v>
       </c>
       <c r="E157">
-        <v>13373013.35459654</v>
+        <v>13412222.64153223</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -3040,13 +3040,13 @@
         <v>16956132.81197058</v>
       </c>
       <c r="C158">
-        <v>20831873.79345092</v>
+        <v>20873673.30533168</v>
       </c>
       <c r="D158">
-        <v>28200835.87578495</v>
+        <v>28356970.47943366</v>
       </c>
       <c r="E158">
-        <v>36292799.8480261</v>
+        <v>36396026.31001374</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -3057,13 +3057,13 @@
         <v>15127379.02097822</v>
       </c>
       <c r="C159">
-        <v>19634043.06852608</v>
+        <v>19674228.20814756</v>
       </c>
       <c r="D159">
-        <v>30395712.580328</v>
+        <v>30573164.62191952</v>
       </c>
       <c r="E159">
-        <v>46050579.61810965</v>
+        <v>46195710.84972942</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -3074,13 +3074,13 @@
         <v>2636846.756125342</v>
       </c>
       <c r="C160">
-        <v>3412002.506927245</v>
+        <v>3415377.823394781</v>
       </c>
       <c r="D160">
-        <v>5115995.062753817</v>
+        <v>5149544.862132208</v>
       </c>
       <c r="E160">
-        <v>7445800.75049753</v>
+        <v>7473590.11113331</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -3088,16 +3088,16 @@
         <v>160</v>
       </c>
       <c r="B161">
-        <v>12074096.32109722</v>
+        <v>12077089.81870198</v>
       </c>
       <c r="C161">
-        <v>16231737.51501989</v>
+        <v>16317035.71853512</v>
       </c>
       <c r="D161">
-        <v>24633351.56741619</v>
+        <v>24812537.20718762</v>
       </c>
       <c r="E161">
-        <v>35544406.20497066</v>
+        <v>35655272.04111715</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -3108,13 +3108,13 @@
         <v>7357636.360588194</v>
       </c>
       <c r="C162">
-        <v>12183149.48750987</v>
+        <v>12194721.99180768</v>
       </c>
       <c r="D162">
-        <v>21259831.8562928</v>
+        <v>21382823.46269968</v>
       </c>
       <c r="E162">
-        <v>34657875.61143675</v>
+        <v>34760963.50270698</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -3125,13 +3125,13 @@
         <v>9013631.015348047</v>
       </c>
       <c r="C163">
-        <v>11337036.37501963</v>
+        <v>11352898.02340416</v>
       </c>
       <c r="D163">
-        <v>15566217.47586013</v>
+        <v>15635114.5293103</v>
       </c>
       <c r="E163">
-        <v>21667824.1788256</v>
+        <v>21716791.80147868</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -3142,13 +3142,13 @@
         <v>1149967.395118152</v>
       </c>
       <c r="C164">
-        <v>1875380.144211522</v>
+        <v>1877947.644931946</v>
       </c>
       <c r="D164">
-        <v>3151658.624814766</v>
+        <v>3164809.616915436</v>
       </c>
       <c r="E164">
-        <v>4957799.542067179</v>
+        <v>4968245.817083246</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -3159,13 +3159,13 @@
         <v>9630685.242269602</v>
       </c>
       <c r="C165">
-        <v>11410751.131884</v>
+        <v>11424598.56283938</v>
       </c>
       <c r="D165">
-        <v>15146573.60041885</v>
+        <v>15231468.49737011</v>
       </c>
       <c r="E165">
-        <v>19134050.84042131</v>
+        <v>19195804.18550413</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -3176,13 +3176,13 @@
         <v>3632626.889628008</v>
       </c>
       <c r="C166">
-        <v>5209255.951512261</v>
+        <v>5215577.604774499</v>
       </c>
       <c r="D166">
-        <v>8968365.947616426</v>
+        <v>9018632.662916511</v>
       </c>
       <c r="E166">
-        <v>14692217.60960922</v>
+        <v>14739635.35672638</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -3193,13 +3193,13 @@
         <v>16803034.52856103</v>
       </c>
       <c r="C167">
-        <v>21711457.51499207</v>
+        <v>21827445.88783506</v>
       </c>
       <c r="D167">
-        <v>33240675.08832612</v>
+        <v>33491646.69529875</v>
       </c>
       <c r="E167">
-        <v>49685090.16042669</v>
+        <v>49829165.24482287</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -3210,13 +3210,13 @@
         <v>978335.8829956541</v>
       </c>
       <c r="C168">
-        <v>983807.4123255635</v>
+        <v>988927.1432991829</v>
       </c>
       <c r="D168">
-        <v>1127758.715056429</v>
+        <v>1135434.117969417</v>
       </c>
       <c r="E168">
-        <v>1078270.111037174</v>
+        <v>1080983.394398647</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -3224,16 +3224,16 @@
         <v>168</v>
       </c>
       <c r="B169">
-        <v>7568168.223774613</v>
+        <v>7568343.62274555</v>
       </c>
       <c r="C169">
-        <v>10437742.63042339</v>
+        <v>10446722.75979002</v>
       </c>
       <c r="D169">
-        <v>15155907.07677313</v>
+        <v>15199196.18299422</v>
       </c>
       <c r="E169">
-        <v>21193734.86960574</v>
+        <v>21214528.4273541</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -3244,13 +3244,13 @@
         <v>17270619.60079974</v>
       </c>
       <c r="C170">
-        <v>24570983.13389632</v>
+        <v>24578666.46611782</v>
       </c>
       <c r="D170">
-        <v>36903995.8222095</v>
+        <v>36983137.64306378</v>
       </c>
       <c r="E170">
-        <v>52931289.47236523</v>
+        <v>52981093.57268373</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -3258,16 +3258,16 @@
         <v>170</v>
       </c>
       <c r="B171">
-        <v>6538485.472240652</v>
+        <v>6538637.00740602</v>
       </c>
       <c r="C171">
-        <v>8338196.699016383</v>
+        <v>8345370.480521911</v>
       </c>
       <c r="D171">
-        <v>13012647.49015875</v>
+        <v>13049814.90459099</v>
       </c>
       <c r="E171">
-        <v>19505738.28707077</v>
+        <v>19524875.72075067</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -3278,13 +3278,13 @@
         <v>6257470.869854978</v>
       </c>
       <c r="C172">
-        <v>7284573.823225734</v>
+        <v>7286851.705249048</v>
       </c>
       <c r="D172">
-        <v>9002789.303401913</v>
+        <v>9022096.078247415</v>
       </c>
       <c r="E172">
-        <v>10530832.46047057</v>
+        <v>10540741.12964388</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -3295,13 +3295,13 @@
         <v>15568587.52419919</v>
       </c>
       <c r="C173">
-        <v>20119299.13081393</v>
+        <v>20125590.42402118</v>
       </c>
       <c r="D173">
-        <v>30728528.77938008</v>
+        <v>30794427.11005109</v>
       </c>
       <c r="E173">
-        <v>45541231.60536834</v>
+        <v>45584082.25363539</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -3309,16 +3309,16 @@
         <v>173</v>
       </c>
       <c r="B174">
-        <v>30521442.02814815</v>
+        <v>30522279.0817388</v>
       </c>
       <c r="C174">
-        <v>40922320.35773607</v>
+        <v>40945385.9079128</v>
       </c>
       <c r="D174">
-        <v>62740057.56214901</v>
+        <v>62887571.00851851</v>
       </c>
       <c r="E174">
-        <v>92804268.33289748</v>
+        <v>92893848.32873529</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -3326,16 +3326,16 @@
         <v>174</v>
       </c>
       <c r="B175">
-        <v>152387161.1293942</v>
+        <v>152394222.7917317</v>
       </c>
       <c r="C175">
-        <v>162880872.9002307</v>
+        <v>163052731.5642912</v>
       </c>
       <c r="D175">
-        <v>193478192.2113907</v>
+        <v>193969104.430287</v>
       </c>
       <c r="E175">
-        <v>215901596.3755507</v>
+        <v>216097220.3616063</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -3343,16 +3343,16 @@
         <v>175</v>
       </c>
       <c r="B176">
-        <v>16004621.10489178</v>
+        <v>16005370.85006364</v>
       </c>
       <c r="C176">
-        <v>19863478.28076815</v>
+        <v>19885417.14510667</v>
       </c>
       <c r="D176">
-        <v>27254669.15717748</v>
+        <v>27329831.77590397</v>
       </c>
       <c r="E176">
-        <v>36013245.93007484</v>
+        <v>36049902.06512639</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -3360,16 +3360,16 @@
         <v>176</v>
       </c>
       <c r="B177">
-        <v>11053191.45056588</v>
+        <v>11053709.2433252</v>
       </c>
       <c r="C177">
-        <v>17226733.3762414</v>
+        <v>17245760.00195092</v>
       </c>
       <c r="D177">
-        <v>28920232.27233832</v>
+        <v>28999988.16220921</v>
       </c>
       <c r="E177">
-        <v>45086713.08648331</v>
+        <v>45132604.66335303</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -3377,16 +3377,16 @@
         <v>177</v>
       </c>
       <c r="B178">
-        <v>4547637.721676978</v>
+        <v>4547686.415381356</v>
       </c>
       <c r="C178">
-        <v>6600358.397171698</v>
+        <v>6605638.613611085</v>
       </c>
       <c r="D178">
-        <v>10345731.08932942</v>
+        <v>10370638.87462224</v>
       </c>
       <c r="E178">
-        <v>15501879.47076096</v>
+        <v>15517613.94616004</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -3394,16 +3394,16 @@
         <v>178</v>
       </c>
       <c r="B179">
-        <v>18273131.69372571</v>
+        <v>18273170.94979443</v>
       </c>
       <c r="C179">
-        <v>22409865.56615963</v>
+        <v>22435660.42305929</v>
       </c>
       <c r="D179">
-        <v>33520676.33380525</v>
+        <v>33598589.30150186</v>
       </c>
       <c r="E179">
-        <v>47221325.13500515</v>
+        <v>47268994.87454622</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -3411,16 +3411,16 @@
         <v>179</v>
       </c>
       <c r="B180">
-        <v>708014.1317938169</v>
+        <v>708015.6211839581</v>
       </c>
       <c r="C180">
-        <v>832484.7014650574</v>
+        <v>833339.9613199885</v>
       </c>
       <c r="D180">
-        <v>2144678.79852226</v>
+        <v>2148883.865258536</v>
       </c>
       <c r="E180">
-        <v>2637410.246634694</v>
+        <v>2639480.33275402</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -3428,16 +3428,16 @@
         <v>180</v>
       </c>
       <c r="B181">
-        <v>101144.8759705453</v>
+        <v>101145.0887405655</v>
       </c>
       <c r="C181">
-        <v>118926.3859235796</v>
+        <v>119048.5659028555</v>
       </c>
       <c r="D181">
-        <v>76595.67137579499</v>
+        <v>76745.85233066202</v>
       </c>
       <c r="E181">
-        <v>94193.22309409622</v>
+        <v>94267.15474121498</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -3445,16 +3445,16 @@
         <v>181</v>
       </c>
       <c r="B182">
-        <v>71407625.45707759</v>
+        <v>71410554.58883999</v>
       </c>
       <c r="C182">
-        <v>74612048.65158674</v>
+        <v>74786935.84755372</v>
       </c>
       <c r="D182">
-        <v>93444140.33938657</v>
+        <v>93890810.39852338</v>
       </c>
       <c r="E182">
-        <v>110449092.6283944</v>
+        <v>110719842.4303044</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -3465,13 +3465,13 @@
         <v>4102590.51490509</v>
       </c>
       <c r="C183">
-        <v>3558128.695857654</v>
+        <v>3559402.101962859</v>
       </c>
       <c r="D183">
-        <v>3697053.281270059</v>
+        <v>3712976.655314891</v>
       </c>
       <c r="E183">
-        <v>3320138.387770094</v>
+        <v>3329915.711405233</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -3482,13 +3482,13 @@
         <v>931508.8653957171</v>
       </c>
       <c r="C184">
-        <v>991582.8448461657</v>
+        <v>991984.368722008</v>
       </c>
       <c r="D184">
-        <v>1018308.766877749</v>
+        <v>1021577.754983264</v>
       </c>
       <c r="E184">
-        <v>823733.958595094</v>
+        <v>825180.2732705283</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -3499,13 +3499,13 @@
         <v>12016464.36360475</v>
       </c>
       <c r="C185">
-        <v>15369534.09511557</v>
+        <v>15375757.71519112</v>
       </c>
       <c r="D185">
-        <v>21675429.46639781</v>
+        <v>21745012.21321519</v>
       </c>
       <c r="E185">
-        <v>30020526.49102121</v>
+        <v>30073236.62585925</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -3516,13 +3516,13 @@
         <v>5290982.148470853</v>
       </c>
       <c r="C186">
-        <v>7303083.203018934</v>
+        <v>7306946.775860892</v>
       </c>
       <c r="D186">
-        <v>11103458.99434138</v>
+        <v>11151205.59234898</v>
       </c>
       <c r="E186">
-        <v>16407380.0977666</v>
+        <v>16453789.83125154</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -3533,13 +3533,13 @@
         <v>2217147.614115603</v>
       </c>
       <c r="C187">
-        <v>2935207.245654609</v>
+        <v>2936835.013661614</v>
       </c>
       <c r="D187">
-        <v>4567366.689579921</v>
+        <v>4588084.214670089</v>
       </c>
       <c r="E187">
-        <v>6777495.266866478</v>
+        <v>6798182.727567766</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -3547,16 +3547,16 @@
         <v>187</v>
       </c>
       <c r="B188">
-        <v>5876701.112545554</v>
+        <v>5876788.715123114</v>
       </c>
       <c r="C188">
-        <v>6234928.090870484</v>
+        <v>6256626.457668474</v>
       </c>
       <c r="D188">
-        <v>7616752.380637189</v>
+        <v>7669398.967537306</v>
       </c>
       <c r="E188">
-        <v>8570261.005570523</v>
+        <v>8592906.880234441</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -3564,16 +3564,16 @@
         <v>188</v>
       </c>
       <c r="B189">
-        <v>81132298.09334473</v>
+        <v>81133507.51310256</v>
       </c>
       <c r="C189">
-        <v>96007754.50494875</v>
+        <v>96341874.07174057</v>
       </c>
       <c r="D189">
-        <v>133223923.4576905</v>
+        <v>134144760.1231071</v>
       </c>
       <c r="E189">
-        <v>176225991.9270439</v>
+        <v>176691647.7248207</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -3581,16 +3581,16 @@
         <v>189</v>
       </c>
       <c r="B190">
-        <v>25916674.69057859</v>
+        <v>25917061.02424798</v>
       </c>
       <c r="C190">
-        <v>35483330.59844991</v>
+        <v>35606817.23876368</v>
       </c>
       <c r="D190">
-        <v>49993592.8983641</v>
+        <v>50339145.95056305</v>
       </c>
       <c r="E190">
-        <v>68383540.94028147</v>
+        <v>68564236.14853731</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -3601,13 +3601,13 @@
         <v>1206018.52719274</v>
       </c>
       <c r="C191">
-        <v>1654129.612912052</v>
+        <v>1655661.229658643</v>
       </c>
       <c r="D191">
-        <v>2482435.031659257</v>
+        <v>2492238.570003004</v>
       </c>
       <c r="E191">
-        <v>3484811.987703665</v>
+        <v>3491953.834194975</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -3618,13 +3618,13 @@
         <v>5605618.496065863</v>
       </c>
       <c r="C192">
-        <v>6915149.273660858</v>
+        <v>6918984.184728209</v>
       </c>
       <c r="D192">
-        <v>9680090.595826101</v>
+        <v>9723999.380345561</v>
       </c>
       <c r="E192">
-        <v>12498757.50513039</v>
+        <v>12536908.40668341</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -3632,16 +3632,16 @@
         <v>192</v>
       </c>
       <c r="B193">
-        <v>14104115.39813704</v>
+        <v>14104120.13250116</v>
       </c>
       <c r="C193">
-        <v>18383293.88713438</v>
+        <v>18398356.6642464</v>
       </c>
       <c r="D193">
-        <v>26928748.10851563</v>
+        <v>27008901.71043079</v>
       </c>
       <c r="E193">
-        <v>37033444.3738219</v>
+        <v>37073422.43860062</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -3649,16 +3649,16 @@
         <v>193</v>
       </c>
       <c r="B194">
-        <v>8613584.761005122</v>
+        <v>8613587.652348923</v>
       </c>
       <c r="C194">
-        <v>11430637.86571817</v>
+        <v>11440003.82328142</v>
       </c>
       <c r="D194">
-        <v>17648219.09936617</v>
+        <v>17700749.14355916</v>
       </c>
       <c r="E194">
-        <v>26278782.49758574</v>
+        <v>26307150.77082518</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -3666,16 +3666,16 @@
         <v>194</v>
       </c>
       <c r="B195">
-        <v>23270830.18466752</v>
+        <v>23271369.50667339</v>
       </c>
       <c r="C195">
-        <v>37371917.57904465</v>
+        <v>37404070.57097231</v>
       </c>
       <c r="D195">
-        <v>56719834.06004491</v>
+        <v>56881840.26059957</v>
       </c>
       <c r="E195">
-        <v>81398946.31335302</v>
+        <v>81478808.29620956</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -3683,16 +3683,16 @@
         <v>195</v>
       </c>
       <c r="B196">
-        <v>5500932.59573652</v>
+        <v>5500932.707725095</v>
       </c>
       <c r="C196">
-        <v>7432728.491996872</v>
+        <v>7436076.907788171</v>
       </c>
       <c r="D196">
-        <v>11882364.55837869</v>
+        <v>11917674.62812853</v>
       </c>
       <c r="E196">
-        <v>18188232.73766043</v>
+        <v>18211401.52717752</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -3703,13 +3703,13 @@
         <v>11085636.15081904</v>
       </c>
       <c r="C197">
-        <v>13767054.00615747</v>
+        <v>13778297.9225395</v>
       </c>
       <c r="D197">
-        <v>18316249.0739631</v>
+        <v>18373144.19592568</v>
       </c>
       <c r="E197">
-        <v>22581237.60431477</v>
+        <v>22610190.56105336</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -3720,13 +3720,13 @@
         <v>3631501.497682097</v>
       </c>
       <c r="C198">
-        <v>4644981.636223863</v>
+        <v>4648775.31532837</v>
       </c>
       <c r="D198">
-        <v>6399653.290902771</v>
+        <v>6419532.309419815</v>
       </c>
       <c r="E198">
-        <v>8261428.391822479</v>
+        <v>8272020.936970741</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -3737,13 +3737,13 @@
         <v>8937507.384451251</v>
       </c>
       <c r="C199">
-        <v>10538729.91134842</v>
+        <v>10546978.22328544</v>
       </c>
       <c r="D199">
-        <v>13762549.57829245</v>
+        <v>13802708.70212366</v>
       </c>
       <c r="E199">
-        <v>16711308.80098455</v>
+        <v>16730695.60626389</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -3754,13 +3754,13 @@
         <v>7005073.35538071</v>
       </c>
       <c r="C200">
-        <v>10139967.15794605</v>
+        <v>10147903.37159356</v>
       </c>
       <c r="D200">
-        <v>15108885.95008193</v>
+        <v>15152973.68385315</v>
       </c>
       <c r="E200">
-        <v>21353339.02348026</v>
+        <v>21378111.0524483</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -3771,13 +3771,13 @@
         <v>7747761.050143554</v>
       </c>
       <c r="C201">
-        <v>11255447.86169207</v>
+        <v>11259602.5376001</v>
       </c>
       <c r="D201">
-        <v>15968298.52488014</v>
+        <v>16012441.20897695</v>
       </c>
       <c r="E201">
-        <v>20930384.28433491</v>
+        <v>20953935.02190509</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -3788,13 +3788,13 @@
         <v>56890792.24794281</v>
       </c>
       <c r="C202">
-        <v>96581683.48461835</v>
+        <v>96667801.36134361</v>
       </c>
       <c r="D202">
-        <v>182840376.2453138</v>
+        <v>183489295.1949681</v>
       </c>
       <c r="E202">
-        <v>304349211.9201192</v>
+        <v>304737677.0133431</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -3802,16 +3802,16 @@
         <v>202</v>
       </c>
       <c r="B203">
-        <v>20709906.27398192</v>
+        <v>20709906.69104282</v>
       </c>
       <c r="C203">
-        <v>26013166.35931859</v>
+        <v>26024245.12122768</v>
       </c>
       <c r="D203">
-        <v>37550096.4256288</v>
+        <v>37655514.03590745</v>
       </c>
       <c r="E203">
-        <v>52219582.64989788</v>
+        <v>52279912.07504851</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -3822,13 +3822,13 @@
         <v>7507825.189811196</v>
       </c>
       <c r="C204">
-        <v>9303334.714907834</v>
+        <v>9309035.000159962</v>
       </c>
       <c r="D204">
-        <v>12431479.56122883</v>
+        <v>12478065.59570503</v>
       </c>
       <c r="E204">
-        <v>15646415.69371753</v>
+        <v>15671011.38682383</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -3839,13 +3839,13 @@
         <v>926427.2737366462</v>
       </c>
       <c r="C205">
-        <v>1274144.212120293</v>
+        <v>1274882.528289204</v>
       </c>
       <c r="D205">
-        <v>1847281.160865521</v>
+        <v>1853781.160111502</v>
       </c>
       <c r="E205">
-        <v>2590669.429770134</v>
+        <v>2594369.488309676</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -3853,16 +3853,16 @@
         <v>205</v>
       </c>
       <c r="B206">
-        <v>23401571.04318075</v>
+        <v>23408784.37507167</v>
       </c>
       <c r="C206">
-        <v>31147013.93980544</v>
+        <v>31277811.08167784</v>
       </c>
       <c r="D206">
-        <v>40408371.12360096</v>
+        <v>40940662.61365282</v>
       </c>
       <c r="E206">
-        <v>45505593.95666641</v>
+        <v>46016894.59538384</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -3870,16 +3870,16 @@
         <v>206</v>
       </c>
       <c r="B207">
-        <v>3253607.376395306</v>
+        <v>3253787.808213247</v>
       </c>
       <c r="C207">
-        <v>4304910.419639485</v>
+        <v>4315802.989597981</v>
       </c>
       <c r="D207">
-        <v>5818213.62918985</v>
+        <v>5879284.536151118</v>
       </c>
       <c r="E207">
-        <v>7008022.624360841</v>
+        <v>7086214.676931417</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -3887,16 +3887,16 @@
         <v>207</v>
       </c>
       <c r="B208">
-        <v>2965677.520077137</v>
+        <v>2965841.984477561</v>
       </c>
       <c r="C208">
-        <v>4112726.918762722</v>
+        <v>4123133.213276642</v>
       </c>
       <c r="D208">
-        <v>5929036.745936323</v>
+        <v>5991270.908268281</v>
       </c>
       <c r="E208">
-        <v>7665024.745394669</v>
+        <v>7750547.302893736</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -3904,16 +3904,16 @@
         <v>208</v>
       </c>
       <c r="B209">
-        <v>19521517.81322332</v>
+        <v>19527535.15226186</v>
       </c>
       <c r="C209">
-        <v>27900821.19410012</v>
+        <v>28017986.44387764</v>
       </c>
       <c r="D209">
-        <v>42005773.7888092</v>
+        <v>42559107.54859956</v>
       </c>
       <c r="E209">
-        <v>57480750.26105231</v>
+        <v>58126603.69943222</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -3921,16 +3921,16 @@
         <v>209</v>
       </c>
       <c r="B210">
-        <v>2361024.821808983</v>
+        <v>2361155.754632621</v>
       </c>
       <c r="C210">
-        <v>3843670.017535254</v>
+        <v>3853395.526426769</v>
       </c>
       <c r="D210">
-        <v>6206094.537802506</v>
+        <v>6271236.838561192</v>
       </c>
       <c r="E210">
-        <v>9125029.458803177</v>
+        <v>9226842.027254447</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -3941,13 +3941,13 @@
         <v>42480996.84738921</v>
       </c>
       <c r="C211">
-        <v>48699019.46416945</v>
+        <v>48785763.24998769</v>
       </c>
       <c r="D211">
-        <v>63375273.52023341</v>
+        <v>63879388.85987044</v>
       </c>
       <c r="E211">
-        <v>74726578.49850032</v>
+        <v>75454346.30551712</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -3955,16 +3955,16 @@
         <v>211</v>
       </c>
       <c r="B212">
-        <v>15866044.30129685</v>
+        <v>15866923.27582248</v>
       </c>
       <c r="C212">
-        <v>20117034.91147138</v>
+        <v>20199148.72842393</v>
       </c>
       <c r="D212">
-        <v>28554450.43996481</v>
+        <v>28907313.00079059</v>
       </c>
       <c r="E212">
-        <v>37211059.49366374</v>
+        <v>37587957.77760053</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -3972,16 +3972,16 @@
         <v>212</v>
       </c>
       <c r="B213">
-        <v>2677747.663758968</v>
+        <v>2677896.160741875</v>
       </c>
       <c r="C213">
-        <v>3805233.317359901</v>
+        <v>3814861.571162501</v>
       </c>
       <c r="D213">
-        <v>5984448.30430956</v>
+        <v>6047264.094326863</v>
       </c>
       <c r="E213">
-        <v>8760028.28045105</v>
+        <v>8857768.346164269</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -3992,13 +3992,13 @@
         <v>1955235.904596207</v>
       </c>
       <c r="C214">
-        <v>2642176.2891134</v>
+        <v>2644082.728633884</v>
       </c>
       <c r="D214">
-        <v>3784441.211258159</v>
+        <v>3805294.804629079</v>
       </c>
       <c r="E214">
-        <v>4839693.878913077</v>
+        <v>4883385.092417363</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -4009,13 +4009,13 @@
         <v>1629363.253830172</v>
       </c>
       <c r="C215">
-        <v>2356535.609209249</v>
+        <v>2358235.94715995</v>
       </c>
       <c r="D215">
-        <v>3888124.532114547</v>
+        <v>3909549.456810697</v>
       </c>
       <c r="E215">
-        <v>5945909.622664637</v>
+        <v>5999587.399255618</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -4026,13 +4026,13 @@
         <v>6052394.534102605</v>
       </c>
       <c r="C216">
-        <v>8331134.448457182</v>
+        <v>8336264.469306136</v>
       </c>
       <c r="D216">
-        <v>11816687.9368835</v>
+        <v>11869975.44959665</v>
       </c>
       <c r="E216">
-        <v>15307764.7171241</v>
+        <v>15435364.52904336</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -4043,13 +4043,13 @@
         <v>2402423.414912544</v>
       </c>
       <c r="C217">
-        <v>4279846.988373216</v>
+        <v>4284887.682726764</v>
       </c>
       <c r="D217">
-        <v>9446304.831024382</v>
+        <v>9506743.646919722</v>
       </c>
       <c r="E217">
-        <v>17819719.10210495</v>
+        <v>17986817.9144358</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -4060,13 +4060,13 @@
         <v>4820855.437459574</v>
       </c>
       <c r="C218">
-        <v>6236645.955403957</v>
+        <v>6243596.123155566</v>
       </c>
       <c r="D218">
-        <v>8761749.346642749</v>
+        <v>8814076.073197309</v>
       </c>
       <c r="E218">
-        <v>10933814.76044679</v>
+        <v>11028706.96472531</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -4077,13 +4077,13 @@
         <v>4699993.1226864</v>
       </c>
       <c r="C219">
-        <v>6475585.831661187</v>
+        <v>6486153.077820544</v>
       </c>
       <c r="D219">
-        <v>9152143.976060348</v>
+        <v>9246070.280306498</v>
       </c>
       <c r="E219">
-        <v>11452870.89695527</v>
+        <v>11555041.87023383</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -4091,16 +4091,16 @@
         <v>219</v>
       </c>
       <c r="B220">
-        <v>4936841.131990717</v>
+        <v>4937997.086857333</v>
       </c>
       <c r="C220">
-        <v>6812107.013405396</v>
+        <v>6853458.519977287</v>
       </c>
       <c r="D220">
-        <v>10112966.5895181</v>
+        <v>10258673.60558966</v>
       </c>
       <c r="E220">
-        <v>13621687.49348129</v>
+        <v>13755290.74401297</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -4111,13 +4111,13 @@
         <v>3662360.144289937</v>
       </c>
       <c r="C221">
-        <v>4661373.239504302</v>
+        <v>4668432.532440327</v>
       </c>
       <c r="D221">
-        <v>6323909.77872322</v>
+        <v>6388023.927553639</v>
       </c>
       <c r="E221">
-        <v>7679015.910728305</v>
+        <v>7737159.890160749</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -4128,13 +4128,13 @@
         <v>3588508.262591643</v>
       </c>
       <c r="C222">
-        <v>5459807.661988843</v>
+        <v>5468717.300907517</v>
       </c>
       <c r="D222">
-        <v>9515805.32610248</v>
+        <v>9613463.801378278</v>
       </c>
       <c r="E222">
-        <v>15165180.77389939</v>
+        <v>15300469.23506824</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -4145,13 +4145,13 @@
         <v>4508126.854549608</v>
       </c>
       <c r="C223">
-        <v>5055843.11436033</v>
+        <v>5063256.445272559</v>
       </c>
       <c r="D223">
-        <v>6081894.624263878</v>
+        <v>6138919.825422148</v>
       </c>
       <c r="E223">
-        <v>6238323.851401776</v>
+        <v>6281341.871673228</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -4162,13 +4162,13 @@
         <v>2575130.474381785</v>
       </c>
       <c r="C224">
-        <v>3517155.718911564</v>
+        <v>3517918.450533992</v>
       </c>
       <c r="D224">
-        <v>5283248.579676273</v>
+        <v>5295704.851705083</v>
       </c>
       <c r="E224">
-        <v>7198503.202081776</v>
+        <v>7241303.9029931</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -4179,13 +4179,13 @@
         <v>2859912.013247489</v>
       </c>
       <c r="C225">
-        <v>3574311.409134146</v>
+        <v>3575198.51305846</v>
       </c>
       <c r="D225">
-        <v>4885899.150245333</v>
+        <v>4899617.296222013</v>
       </c>
       <c r="E225">
-        <v>5922330.095153394</v>
+        <v>5962972.108035904</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -4196,13 +4196,13 @@
         <v>2408859.831264515</v>
       </c>
       <c r="C226">
-        <v>3410410.538547452</v>
+        <v>3411210.60742781</v>
       </c>
       <c r="D226">
-        <v>5207553.624361007</v>
+        <v>5221012.486469435</v>
       </c>
       <c r="E226">
-        <v>7224584.607532723</v>
+        <v>7270965.629430339</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -4213,13 +4213,13 @@
         <v>2639789.626592918</v>
       </c>
       <c r="C227">
-        <v>3528324.835510531</v>
+        <v>3530096.246523825</v>
       </c>
       <c r="D227">
-        <v>5653052.616954701</v>
+        <v>5672983.08893989</v>
       </c>
       <c r="E227">
-        <v>8521305.594847323</v>
+        <v>8585843.926285205</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -4230,13 +4230,13 @@
         <v>25706409.37632059</v>
       </c>
       <c r="C228">
-        <v>28719573.96137501</v>
+        <v>28726056.60880807</v>
       </c>
       <c r="D228">
-        <v>35274720.14377181</v>
+        <v>35344404.19065611</v>
       </c>
       <c r="E228">
-        <v>36119931.6090927</v>
+        <v>36305835.83111719</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -4244,16 +4244,16 @@
         <v>228</v>
       </c>
       <c r="B229">
-        <v>4775506.45447468</v>
+        <v>4776624.633038466</v>
       </c>
       <c r="C229">
-        <v>7033279.319035441</v>
+        <v>7075973.406989537</v>
       </c>
       <c r="D229">
-        <v>10239378.67188708</v>
+        <v>10386907.02565954</v>
       </c>
       <c r="E229">
-        <v>13213852.53858664</v>
+        <v>13343455.69179702</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -4264,13 +4264,13 @@
         <v>3663709.85618259</v>
       </c>
       <c r="C230">
-        <v>4500075.645533074</v>
+        <v>4507094.486908769</v>
       </c>
       <c r="D230">
-        <v>6113634.688209115</v>
+        <v>6180088.862665898</v>
       </c>
       <c r="E230">
-        <v>7613595.968173592</v>
+        <v>7676456.759542128</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -4278,16 +4278,16 @@
         <v>230</v>
       </c>
       <c r="B231">
-        <v>10873960.24955614</v>
+        <v>10874552.75667565</v>
       </c>
       <c r="C231">
-        <v>19994060.39796816</v>
+        <v>20071729.61686984</v>
       </c>
       <c r="D231">
-        <v>32044618.43290432</v>
+        <v>32414449.01368411</v>
       </c>
       <c r="E231">
-        <v>45405620.79797546</v>
+        <v>45825093.45814928</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -4298,13 +4298,13 @@
         <v>2158288.867782658</v>
       </c>
       <c r="C232">
-        <v>3319119.198447624</v>
+        <v>3324379.373064269</v>
       </c>
       <c r="D232">
-        <v>5762602.087756248</v>
+        <v>5809072.788912687</v>
       </c>
       <c r="E232">
-        <v>9061049.943088965</v>
+        <v>9146096.106990844</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -4315,13 +4315,13 @@
         <v>2191509.016282172</v>
       </c>
       <c r="C233">
-        <v>3401429.807681611</v>
+        <v>3406614.071473978</v>
       </c>
       <c r="D233">
-        <v>5904481.902472368</v>
+        <v>5948619.26204186</v>
       </c>
       <c r="E233">
-        <v>9251130.405866679</v>
+        <v>9330616.403683638</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -4332,13 +4332,13 @@
         <v>14570261.49345191</v>
       </c>
       <c r="C234">
-        <v>19226799.87650294</v>
+        <v>19256108.56655527</v>
       </c>
       <c r="D234">
-        <v>26821299.88091439</v>
+        <v>27048065.0498714</v>
       </c>
       <c r="E234">
-        <v>34237835.50613046</v>
+        <v>34496473.26607503</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -4349,13 +4349,13 @@
         <v>13018798.46405657</v>
       </c>
       <c r="C235">
-        <v>18200775.75316288</v>
+        <v>18228520.40639107</v>
       </c>
       <c r="D235">
-        <v>27450907.85933961</v>
+        <v>27682996.15432848</v>
       </c>
       <c r="E235">
-        <v>38222761.72893424</v>
+        <v>38511502.22103388</v>
       </c>
     </row>
     <row r="236" spans="1:5">
@@ -4366,13 +4366,13 @@
         <v>18685011.26706565</v>
       </c>
       <c r="C236">
-        <v>21412677.35666221</v>
+        <v>21445318.12516597</v>
       </c>
       <c r="D236">
-        <v>25058397.54132378</v>
+        <v>25270257.95739159</v>
       </c>
       <c r="E236">
-        <v>24722807.58637449</v>
+        <v>24909567.39403042</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -4383,13 +4383,13 @@
         <v>2674683.561742621</v>
       </c>
       <c r="C237">
-        <v>3838034.685061884</v>
+        <v>3839810.76994961</v>
       </c>
       <c r="D237">
-        <v>5891810.118099018</v>
+        <v>5910998.675191729</v>
       </c>
       <c r="E237">
-        <v>8205238.333795613</v>
+        <v>8263047.270392531</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -4400,13 +4400,13 @@
         <v>2795071.369333678</v>
       </c>
       <c r="C238">
-        <v>3696340.303868175</v>
+        <v>3698196.067786864</v>
       </c>
       <c r="D238">
-        <v>5604319.404739575</v>
+        <v>5624078.062311098</v>
       </c>
       <c r="E238">
-        <v>7931369.053665585</v>
+        <v>7991439.346773152</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -4417,13 +4417,13 @@
         <v>4118334.90967961</v>
       </c>
       <c r="C239">
-        <v>4369355.096871062</v>
+        <v>4371170.690507013</v>
       </c>
       <c r="D239">
-        <v>5319185.06228467</v>
+        <v>5335047.761425962</v>
       </c>
       <c r="E239">
-        <v>5584322.517614431</v>
+        <v>5620685.922141952</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -4434,13 +4434,13 @@
         <v>3796297.096782906</v>
       </c>
       <c r="C240">
-        <v>5411322.669822449</v>
+        <v>5413921.355242837</v>
       </c>
       <c r="D240">
-        <v>8625585.16922562</v>
+        <v>8654038.939612964</v>
       </c>
       <c r="E240">
-        <v>12637258.5380528</v>
+        <v>12717845.13768118</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -4451,13 +4451,13 @@
         <v>984590.9844680181</v>
       </c>
       <c r="C241">
-        <v>1228205.283081375</v>
+        <v>1228633.728967457</v>
       </c>
       <c r="D241">
-        <v>1544146.383913565</v>
+        <v>1548441.523774155</v>
       </c>
       <c r="E241">
-        <v>1740188.926430673</v>
+        <v>1750454.552435907</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -4468,13 +4468,13 @@
         <v>2696828.83352259</v>
       </c>
       <c r="C242">
-        <v>4084250.838422817</v>
+        <v>4090436.123662001</v>
       </c>
       <c r="D242">
-        <v>6766583.463233846</v>
+        <v>6835185.602482393</v>
       </c>
       <c r="E242">
-        <v>10211457.32809615</v>
+        <v>10288776.44968185</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -4485,13 +4485,13 @@
         <v>4248716.313808059</v>
       </c>
       <c r="C243">
-        <v>6020836.19688035</v>
+        <v>6039221.903384772</v>
       </c>
       <c r="D243">
-        <v>8706843.062320149</v>
+        <v>8809060.838609505</v>
       </c>
       <c r="E243">
-        <v>11552387.38200393</v>
+        <v>11628057.54176358</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -4502,13 +4502,13 @@
         <v>3462595.045510486</v>
       </c>
       <c r="C244">
-        <v>4439403.085242192</v>
+        <v>4446126.22137174</v>
       </c>
       <c r="D244">
-        <v>6387148.876510452</v>
+        <v>6451904.166829175</v>
       </c>
       <c r="E244">
-        <v>8414240.838351227</v>
+        <v>8477951.794537842</v>
       </c>
     </row>
     <row r="245" spans="1:5">
@@ -4519,13 +4519,13 @@
         <v>3570374.367282415</v>
       </c>
       <c r="C245">
-        <v>5507703.72975538</v>
+        <v>5523994.543445176</v>
       </c>
       <c r="D245">
-        <v>9240036.475168394</v>
+        <v>9340059.294998031</v>
       </c>
       <c r="E245">
-        <v>14046502.85302196</v>
+        <v>14129095.61100162</v>
       </c>
     </row>
     <row r="246" spans="1:5">
@@ -4533,16 +4533,16 @@
         <v>245</v>
       </c>
       <c r="B246">
-        <v>973394.9242809396</v>
+        <v>973404.5858437989</v>
       </c>
       <c r="C246">
-        <v>1953834.319570184</v>
+        <v>1964760.013879124</v>
       </c>
       <c r="D246">
-        <v>4859659.431564932</v>
+        <v>4915907.820962297</v>
       </c>
       <c r="E246">
-        <v>9442837.0764369</v>
+        <v>9501909.913618295</v>
       </c>
     </row>
     <row r="247" spans="1:5">
@@ -4550,16 +4550,16 @@
         <v>246</v>
       </c>
       <c r="B247">
-        <v>973394.9242809396</v>
+        <v>973404.5858437989</v>
       </c>
       <c r="C247">
-        <v>1953834.319570184</v>
+        <v>1964760.013879124</v>
       </c>
       <c r="D247">
-        <v>4859659.431564932</v>
+        <v>4915907.820962297</v>
       </c>
       <c r="E247">
-        <v>9442837.0764369</v>
+        <v>9501909.913618295</v>
       </c>
     </row>
     <row r="248" spans="1:5">
@@ -4570,13 +4570,13 @@
         <v>45182625.7586931</v>
       </c>
       <c r="C248">
-        <v>52777954.1830837</v>
+        <v>52860930.65929924</v>
       </c>
       <c r="D248">
-        <v>65969041.23424903</v>
+        <v>66420301.14208609</v>
       </c>
       <c r="E248">
-        <v>72109532.34257941</v>
+        <v>72712229.63936828</v>
       </c>
     </row>
     <row r="249" spans="1:5">
@@ -4587,13 +4587,13 @@
         <v>24478715.36127214</v>
       </c>
       <c r="C249">
-        <v>27808377.13768861</v>
+        <v>27814654.10770605</v>
       </c>
       <c r="D249">
-        <v>35836256.93332534</v>
+        <v>35907050.27762748</v>
       </c>
       <c r="E249">
-        <v>39969924.31936421</v>
+        <v>40175643.91389131</v>
       </c>
     </row>
     <row r="250" spans="1:5">
@@ -4604,13 +4604,13 @@
         <v>21282672.90454493</v>
       </c>
       <c r="C250">
-        <v>27805088.12736786</v>
+        <v>27868058.28429809</v>
       </c>
       <c r="D250">
-        <v>36395234.92717655</v>
+        <v>36710391.99624317</v>
       </c>
       <c r="E250">
-        <v>44126851.20396274</v>
+        <v>44295023.90552013</v>
       </c>
     </row>
     <row r="251" spans="1:5">
@@ -4618,16 +4618,16 @@
         <v>250</v>
       </c>
       <c r="B251">
-        <v>11823788.81179969</v>
+        <v>11823920.07137934</v>
       </c>
       <c r="C251">
-        <v>15829700.57804597</v>
+        <v>15901704.61769504</v>
       </c>
       <c r="D251">
-        <v>22353845.1504395</v>
+        <v>22512162.74724635</v>
       </c>
       <c r="E251">
-        <v>29636798.91024524</v>
+        <v>29733375.389869</v>
       </c>
     </row>
     <row r="252" spans="1:5">
@@ -4638,13 +4638,13 @@
         <v>5249730.734673366</v>
       </c>
       <c r="C252">
-        <v>7972425.718574058</v>
+        <v>7975325.403040226</v>
       </c>
       <c r="D252">
-        <v>13657210.11023537</v>
+        <v>13780476.02192736</v>
       </c>
       <c r="E252">
-        <v>21741519.95967561</v>
+        <v>21849937.63670103</v>
       </c>
     </row>
     <row r="253" spans="1:5">
@@ -4655,13 +4655,13 @@
         <v>657287.403338177</v>
       </c>
       <c r="C253">
-        <v>707006.637633083</v>
+        <v>708288.3857885485</v>
       </c>
       <c r="D253">
-        <v>872125.5750174881</v>
+        <v>877617.2652298819</v>
       </c>
       <c r="E253">
-        <v>991432.7256269415</v>
+        <v>994975.017230648</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -4672,13 +4672,13 @@
         <v>12901631.41951654</v>
       </c>
       <c r="C254">
-        <v>14697339.41292366</v>
+        <v>14736791.87522008</v>
       </c>
       <c r="D254">
-        <v>16616910.28865262</v>
+        <v>16704707.32824558</v>
       </c>
       <c r="E254">
-        <v>16653320.17112549</v>
+        <v>16692532.31082301</v>
       </c>
     </row>
     <row r="255" spans="1:5">
@@ -4689,13 +4689,13 @@
         <v>701106.5635607222</v>
       </c>
       <c r="C255">
-        <v>761391.7636048587</v>
+        <v>762772.107772283</v>
       </c>
       <c r="D255">
-        <v>872125.5750174881</v>
+        <v>877617.2652298819</v>
       </c>
       <c r="E255">
-        <v>811172.2300584067</v>
+        <v>814070.4686432574</v>
       </c>
     </row>
     <row r="256" spans="1:5">
@@ -4706,13 +4706,13 @@
         <v>4013888.639248461</v>
       </c>
       <c r="C256">
-        <v>4704793.97864719</v>
+        <v>4705305.739429966</v>
       </c>
       <c r="D256">
-        <v>6071006.856744707</v>
+        <v>6125632.538474821</v>
       </c>
       <c r="E256">
-        <v>7182777.880674766</v>
+        <v>7220920.077036312</v>
       </c>
     </row>
     <row r="257" spans="1:5">
@@ -4723,13 +4723,13 @@
         <v>1570349.932253553</v>
       </c>
       <c r="C257">
-        <v>1724656.8033293</v>
+        <v>1724659.093076291</v>
       </c>
       <c r="D257">
-        <v>2152221.807928465</v>
+        <v>2168290.497050614</v>
       </c>
       <c r="E257">
-        <v>2413999.078163751</v>
+        <v>2428582.310441622</v>
       </c>
     </row>
     <row r="258" spans="1:5">
@@ -4743,10 +4743,10 @@
         <v>1832703.374952017</v>
       </c>
       <c r="D258">
-        <v>2641045.148809507</v>
+        <v>2646310.346881429</v>
       </c>
       <c r="E258">
-        <v>3576517.003739466</v>
+        <v>3588010.263760014</v>
       </c>
     </row>
     <row r="259" spans="1:5">
@@ -4760,10 +4760,10 @@
         <v>1924338.543699618</v>
       </c>
       <c r="D259">
-        <v>2578163.121456899</v>
+        <v>2583302.957669966</v>
       </c>
       <c r="E259">
-        <v>3332663.571666321</v>
+        <v>3343373.200321832</v>
       </c>
     </row>
     <row r="260" spans="1:5">
@@ -4771,16 +4771,16 @@
         <v>259</v>
       </c>
       <c r="B260">
-        <v>6624415.860577866</v>
+        <v>6624433.280604076</v>
       </c>
       <c r="C260">
-        <v>11111597.26287873</v>
+        <v>11115858.69717004</v>
       </c>
       <c r="D260">
-        <v>23016425.5147307</v>
+        <v>23213780.76834716</v>
       </c>
       <c r="E260">
-        <v>35869286.52840722</v>
+        <v>36203270.25208295</v>
       </c>
     </row>
     <row r="261" spans="1:5">
@@ -4791,13 +4791,13 @@
         <v>1493523.970941249</v>
       </c>
       <c r="C261">
-        <v>1919871.297627723</v>
+        <v>1919871.29883982</v>
       </c>
       <c r="D261">
-        <v>4253314.572573808</v>
+        <v>4262259.706582415</v>
       </c>
       <c r="E261">
-        <v>6113549.72654097</v>
+        <v>6144631.870341593</v>
       </c>
     </row>
     <row r="262" spans="1:5">
@@ -4808,13 +4808,13 @@
         <v>1192212.741411128</v>
       </c>
       <c r="C262">
-        <v>1967077.928264445</v>
+        <v>1967324.697040993</v>
       </c>
       <c r="D262">
-        <v>4651592.451026085</v>
+        <v>4684148.726189171</v>
       </c>
       <c r="E262">
-        <v>8507444.260706514</v>
+        <v>8581991.551229231</v>
       </c>
     </row>
     <row r="263" spans="1:5">
@@ -4825,13 +4825,13 @@
         <v>1770252.329917683</v>
       </c>
       <c r="C263">
-        <v>2371357.911679312</v>
+        <v>2371643.607122465</v>
       </c>
       <c r="D263">
-        <v>4369376.601329013</v>
+        <v>4397738.358804128</v>
       </c>
       <c r="E263">
-        <v>6044251.994751688</v>
+        <v>6093273.869651672</v>
       </c>
     </row>
     <row r="264" spans="1:5">
@@ -4839,16 +4839,16 @@
         <v>263</v>
       </c>
       <c r="B264">
-        <v>763428.841209177</v>
+        <v>763444.9151274187</v>
       </c>
       <c r="C264">
-        <v>1040408.467462827</v>
+        <v>1040469.855037951</v>
       </c>
       <c r="D264">
-        <v>2122557.445689893</v>
+        <v>2132012.353105086</v>
       </c>
       <c r="E264">
-        <v>3279253.907788156</v>
+        <v>3303214.41445076</v>
       </c>
     </row>
     <row r="265" spans="1:5">
@@ -4856,16 +4856,16 @@
         <v>264</v>
       </c>
       <c r="B265">
-        <v>751310.9230947457</v>
+        <v>751326.7418714279</v>
       </c>
       <c r="C265">
-        <v>1040408.467462827</v>
+        <v>1040469.855037951</v>
       </c>
       <c r="D265">
-        <v>2122557.445689893</v>
+        <v>2132012.353105086</v>
       </c>
       <c r="E265">
-        <v>3343553.004019296</v>
+        <v>3367983.324538029</v>
       </c>
     </row>
     <row r="266" spans="1:5">
@@ -4876,13 +4876,13 @@
         <v>653499.9753340245</v>
       </c>
       <c r="C266">
-        <v>1196177.998734206</v>
+        <v>1198337.71068126</v>
       </c>
       <c r="D266">
-        <v>2558780.973335118</v>
+        <v>2587086.10772438</v>
       </c>
       <c r="E266">
-        <v>4381099.697650587</v>
+        <v>4418703.697958883</v>
       </c>
     </row>
     <row r="267" spans="1:5">
@@ -4890,16 +4890,16 @@
         <v>266</v>
       </c>
       <c r="B267">
-        <v>884608.0223534909</v>
+        <v>884626.6476873264</v>
       </c>
       <c r="C267">
-        <v>1148036.929614154</v>
+        <v>1148104.667628084</v>
       </c>
       <c r="D267">
-        <v>2043944.206960638</v>
+        <v>2053048.932619713</v>
       </c>
       <c r="E267">
-        <v>2507664.753014472</v>
+        <v>2525987.493403522</v>
       </c>
     </row>
     <row r="268" spans="1:5">
@@ -4910,13 +4910,13 @@
         <v>1201685.95363089</v>
       </c>
       <c r="C268">
-        <v>1799879.341525991</v>
+        <v>1799879.342662331</v>
       </c>
       <c r="D268">
-        <v>4525526.705218531</v>
+        <v>4535044.327803689</v>
       </c>
       <c r="E268">
-        <v>7700721.290162182</v>
+        <v>7739872.836680276</v>
       </c>
     </row>
     <row r="269" spans="1:5">
@@ -4927,13 +4927,13 @@
         <v>1450606.615454432</v>
       </c>
       <c r="C269">
-        <v>1919871.297627723</v>
+        <v>1919871.29883982</v>
       </c>
       <c r="D269">
-        <v>4287341.089154398</v>
+        <v>4296357.784235074</v>
       </c>
       <c r="E269">
-        <v>6231117.990512911</v>
+        <v>6262797.867848163</v>
       </c>
     </row>
     <row r="270" spans="1:5">
@@ -4944,13 +4944,13 @@
         <v>922557.2759467394</v>
       </c>
       <c r="C270">
-        <v>1635032.265587688</v>
+        <v>1635764.362021916</v>
       </c>
       <c r="D270">
-        <v>3886555.382944603</v>
+        <v>3900794.393129885</v>
       </c>
       <c r="E270">
-        <v>6443678.524596959</v>
+        <v>6487815.030839915</v>
       </c>
     </row>
     <row r="271" spans="1:5">
@@ -4961,13 +4961,13 @@
         <v>317319.9278064335</v>
       </c>
       <c r="C271">
-        <v>473352.9835489461</v>
+        <v>473410.3973404538</v>
       </c>
       <c r="D271">
-        <v>929001.5764155086</v>
+        <v>930250.7666330149</v>
       </c>
       <c r="E271">
-        <v>1141014.363432657</v>
+        <v>1145102.971711913</v>
       </c>
     </row>
     <row r="272" spans="1:5">
@@ -4978,13 +4978,13 @@
         <v>228765.5293488241</v>
       </c>
       <c r="C272">
-        <v>396593.0402707386</v>
+        <v>396641.1437176775</v>
       </c>
       <c r="D272">
-        <v>1025105.187768837</v>
+        <v>1026483.604560568</v>
       </c>
       <c r="E272">
-        <v>1793022.571108461</v>
+        <v>1799447.526975863</v>
       </c>
     </row>
     <row r="273" spans="1:5">
@@ -4995,13 +4995,13 @@
         <v>750537.3873984986</v>
       </c>
       <c r="C273">
-        <v>1236060.964652876</v>
+        <v>1237278.861711113</v>
       </c>
       <c r="D273">
-        <v>2718483.988595892</v>
+        <v>2733451.830473818</v>
       </c>
       <c r="E273">
-        <v>4221121.304658691</v>
+        <v>4254852.381452688</v>
       </c>
     </row>
     <row r="274" spans="1:5">
@@ -5012,13 +5012,13 @@
         <v>909101.6241728292</v>
       </c>
       <c r="C274">
-        <v>1346752.991338208</v>
+        <v>1348079.953804646</v>
       </c>
       <c r="D274">
-        <v>2593015.496814543</v>
+        <v>2607292.515221181</v>
       </c>
       <c r="E274">
-        <v>3216092.422597098</v>
+        <v>3241792.290630619</v>
       </c>
     </row>
     <row r="275" spans="1:5">
@@ -5029,13 +5029,13 @@
         <v>1789985.340328698</v>
       </c>
       <c r="C275">
-        <v>2898370.086309937</v>
+        <v>2898424.48884576</v>
       </c>
       <c r="D275">
-        <v>5976824.729537856</v>
+        <v>5986425.873801965</v>
       </c>
       <c r="E275">
-        <v>9247786.289406786</v>
+        <v>9269643.925044864</v>
       </c>
     </row>
     <row r="276" spans="1:5">
@@ -5049,10 +5049,10 @@
         <v>682309.9968793716</v>
       </c>
       <c r="D276">
-        <v>1558375.800081054</v>
+        <v>1559345.564814231</v>
       </c>
       <c r="E276">
-        <v>2388050.357315942</v>
+        <v>2390380.913178618</v>
       </c>
     </row>
     <row r="277" spans="1:5">
@@ -5063,13 +5063,13 @@
         <v>3111999.904986183</v>
       </c>
       <c r="C277">
-        <v>3986145.439735518</v>
+        <v>3986190.743392994</v>
       </c>
       <c r="D277">
-        <v>6184968.978157099</v>
+        <v>6200758.293299627</v>
       </c>
       <c r="E277">
-        <v>7424736.311097709</v>
+        <v>7450589.597379093</v>
       </c>
     </row>
     <row r="278" spans="1:5">
@@ -5080,13 +5080,13 @@
         <v>2164602.395904915</v>
       </c>
       <c r="C278">
-        <v>3024312.824294422</v>
+        <v>3025170.534384864</v>
       </c>
       <c r="D278">
-        <v>4828034.219590036</v>
+        <v>4846367.203270343</v>
       </c>
       <c r="E278">
-        <v>6640072.339670904</v>
+        <v>6679305.090106717</v>
       </c>
     </row>
     <row r="279" spans="1:5">
@@ -5100,10 +5100,10 @@
         <v>1107797.706479552</v>
       </c>
       <c r="D279">
-        <v>1473262.05472577</v>
+        <v>1476027.524968997</v>
       </c>
       <c r="E279">
-        <v>1731473.227797089</v>
+        <v>1738248.348830358</v>
       </c>
     </row>
     <row r="280" spans="1:5">
@@ -5117,10 +5117,10 @@
         <v>1107797.706479552</v>
       </c>
       <c r="D280">
-        <v>1473262.05472577</v>
+        <v>1476027.524968997</v>
       </c>
       <c r="E280">
-        <v>1731473.227797089</v>
+        <v>1738248.348830358</v>
       </c>
     </row>
     <row r="281" spans="1:5">
@@ -5131,13 +5131,13 @@
         <v>2457727.822762271</v>
       </c>
       <c r="C281">
-        <v>3667818.664179621</v>
+        <v>3667911.951318318</v>
       </c>
       <c r="D281">
-        <v>7273230.667902962</v>
+        <v>7280933.315443281</v>
       </c>
       <c r="E281">
-        <v>9708580.609963499</v>
+        <v>9725139.192824921</v>
       </c>
     </row>
     <row r="282" spans="1:5">
@@ -5148,13 +5148,13 @@
         <v>849445.4812557147</v>
       </c>
       <c r="C282">
-        <v>1180168.806092751</v>
+        <v>1180588.96427869</v>
       </c>
       <c r="D282">
-        <v>2161939.81416461</v>
+        <v>2163477.28478698</v>
       </c>
       <c r="E282">
-        <v>2312865.709395416</v>
+        <v>2315715.531276916</v>
       </c>
     </row>
     <row r="283" spans="1:5">
@@ -5165,13 +5165,13 @@
         <v>810834.3230168186</v>
       </c>
       <c r="C283">
-        <v>1153648.158764824</v>
+        <v>1154058.875193776</v>
       </c>
       <c r="D283">
-        <v>2224604.736314308</v>
+        <v>2226186.771302544</v>
       </c>
       <c r="E283">
-        <v>2608125.161658661</v>
+        <v>2611338.790588863</v>
       </c>
     </row>
     <row r="284" spans="1:5">
@@ -5182,13 +5182,13 @@
         <v>664111.9217090133</v>
       </c>
       <c r="C284">
-        <v>1074086.216781043</v>
+        <v>1074468.607939032</v>
       </c>
       <c r="D284">
-        <v>2349934.580613706</v>
+        <v>2351605.744333673</v>
       </c>
       <c r="E284">
-        <v>3346273.792316772</v>
+        <v>3350396.93886873</v>
       </c>
     </row>
     <row r="285" spans="1:5">
@@ -5202,10 +5202,10 @@
         <v>751933.4659486952</v>
       </c>
       <c r="D285">
-        <v>1399357.861297273</v>
+        <v>1400228.670445432</v>
       </c>
       <c r="E285">
-        <v>1592033.571543961</v>
+        <v>1593587.275452412</v>
       </c>
     </row>
     <row r="286" spans="1:5">
@@ -5219,10 +5219,10 @@
         <v>1142416.384807038</v>
       </c>
       <c r="D286">
-        <v>1473262.05472577</v>
+        <v>1476027.524968997</v>
       </c>
       <c r="E286">
-        <v>1515039.074322453</v>
+        <v>1520967.305226563</v>
       </c>
     </row>
     <row r="287" spans="1:5">
@@ -5230,16 +5230,16 @@
         <v>286</v>
       </c>
       <c r="B287">
-        <v>7238014.185598485</v>
+        <v>7238017.275580065</v>
       </c>
       <c r="C287">
-        <v>10176206.38085392</v>
+        <v>10235500.34463082</v>
       </c>
       <c r="D287">
-        <v>15583201.2899291</v>
+        <v>15755220.32107158</v>
       </c>
       <c r="E287">
-        <v>21468695.75902898</v>
+        <v>21564680.91400349</v>
       </c>
     </row>
     <row r="288" spans="1:5">
@@ -5247,16 +5247,16 @@
         <v>287</v>
       </c>
       <c r="B288">
-        <v>3007360.897768991</v>
+        <v>3007361.592662852</v>
       </c>
       <c r="C288">
-        <v>4654129.683185597</v>
+        <v>4688235.90987768</v>
       </c>
       <c r="D288">
-        <v>8507036.014580958</v>
+        <v>8617114.193652172</v>
       </c>
       <c r="E288">
-        <v>13535453.91988315</v>
+        <v>13629144.49899271</v>
       </c>
     </row>
     <row r="289" spans="1:5">
@@ -5267,13 +5267,13 @@
         <v>103071850.6977032</v>
       </c>
       <c r="C289">
-        <v>115107229.10228</v>
+        <v>115487947.2699934</v>
       </c>
       <c r="D289">
-        <v>148854886.4776165</v>
+        <v>150084008.3543171</v>
       </c>
       <c r="E289">
-        <v>174884878.9129837</v>
+        <v>175619871.6048388</v>
       </c>
     </row>
     <row r="290" spans="1:5">
@@ -5281,16 +5281,16 @@
         <v>289</v>
       </c>
       <c r="B290">
-        <v>6003882.734597822</v>
+        <v>6003885.297716184</v>
       </c>
       <c r="C290">
-        <v>9036133.46681634</v>
+        <v>9088784.538385877</v>
       </c>
       <c r="D290">
-        <v>16019530.92604712</v>
+        <v>16196366.49006159</v>
       </c>
       <c r="E290">
-        <v>25846625.87459567</v>
+        <v>25962184.47293754</v>
       </c>
     </row>
     <row r="291" spans="1:5">
@@ -5301,13 +5301,13 @@
         <v>4936899.905665361</v>
       </c>
       <c r="C291">
-        <v>5731982.461389092</v>
+        <v>5763867.726087809</v>
       </c>
       <c r="D291">
-        <v>8101426.49584252</v>
+        <v>8204729.660445969</v>
       </c>
       <c r="E291">
-        <v>9406214.344292277</v>
+        <v>9479195.153977914</v>
       </c>
     </row>
     <row r="292" spans="1:5">
@@ -5318,13 +5318,13 @@
         <v>769378.385332216</v>
       </c>
       <c r="C292">
-        <v>1006850.746232379</v>
+        <v>1008227.522880836</v>
       </c>
       <c r="D292">
-        <v>1536118.214885887</v>
+        <v>1552596.230218955</v>
       </c>
       <c r="E292">
-        <v>2020783.928774023</v>
+        <v>2034668.472289015</v>
       </c>
     </row>
     <row r="293" spans="1:5">
@@ -5335,13 +5335,13 @@
         <v>3429717.833534627</v>
       </c>
       <c r="C293">
-        <v>4773330.42551854</v>
+        <v>4777823.687902723</v>
       </c>
       <c r="D293">
-        <v>7754984.608099351</v>
+        <v>7837643.658451213</v>
       </c>
       <c r="E293">
-        <v>11375289.12455302</v>
+        <v>11452643.13750837</v>
       </c>
     </row>
     <row r="294" spans="1:5">
@@ -5352,13 +5352,13 @@
         <v>997342.3513565763</v>
       </c>
       <c r="C294">
-        <v>1118723.05136931</v>
+        <v>1120252.803200929</v>
       </c>
       <c r="D294">
-        <v>1422331.680449895</v>
+        <v>1437589.102054588</v>
       </c>
       <c r="E294">
-        <v>1476726.717181017</v>
+        <v>1486873.114365049</v>
       </c>
     </row>
     <row r="295" spans="1:5">
@@ -5369,13 +5369,13 @@
         <v>8096498.28333783</v>
       </c>
       <c r="C295">
-        <v>10905351.42075777</v>
+        <v>10908661.61131831</v>
       </c>
       <c r="D295">
-        <v>18092111.11711847</v>
+        <v>18256199.02246605</v>
       </c>
       <c r="E295">
-        <v>25794737.08996687</v>
+        <v>25984242.42139046</v>
       </c>
     </row>
     <row r="296" spans="1:5">
@@ -5386,13 +5386,13 @@
         <v>3457267.888116678</v>
       </c>
       <c r="C296">
-        <v>4540685.187941087</v>
+        <v>4554772.102716813</v>
       </c>
       <c r="D296">
-        <v>7501363.735772902</v>
+        <v>7586326.68248458</v>
       </c>
       <c r="E296">
-        <v>10769378.25193655</v>
+        <v>10843883.99859296</v>
       </c>
     </row>
     <row r="297" spans="1:5">
@@ -5403,13 +5403,13 @@
         <v>2086585.314919782</v>
       </c>
       <c r="C297">
-        <v>3476635.743433479</v>
+        <v>3492540.431525757</v>
       </c>
       <c r="D297">
-        <v>8264034.276419563</v>
+        <v>8358166.663087226</v>
       </c>
       <c r="E297">
-        <v>16073798.72262773</v>
+        <v>16177003.61924569</v>
       </c>
     </row>
     <row r="298" spans="1:5">
@@ -5420,13 +5420,13 @@
         <v>7833151.785728016</v>
       </c>
       <c r="C298">
-        <v>12116563.75377209</v>
+        <v>12158168.74602269</v>
       </c>
       <c r="D298">
-        <v>22185159.19980913</v>
+        <v>22448297.23885363</v>
       </c>
       <c r="E298">
-        <v>34283620.43953913</v>
+        <v>34560096.45960825</v>
       </c>
     </row>
     <row r="299" spans="1:5">
@@ -5437,13 +5437,13 @@
         <v>8841005.817689089</v>
       </c>
       <c r="C299">
-        <v>14969945.28154012</v>
+        <v>15022303.31861715</v>
       </c>
       <c r="D299">
-        <v>28644227.51917635</v>
+        <v>28948428.62323004</v>
       </c>
       <c r="E299">
-        <v>45287202.50154644</v>
+        <v>45628901.81067784</v>
       </c>
     </row>
     <row r="300" spans="1:5">
@@ -5454,13 +5454,13 @@
         <v>9405512.975853527</v>
       </c>
       <c r="C300">
-        <v>11495669.58883298</v>
+        <v>11499158.96349793</v>
       </c>
       <c r="D300">
-        <v>17374576.96516476</v>
+        <v>17532157.13488949</v>
       </c>
       <c r="E300">
-        <v>22183473.89737151</v>
+        <v>22346448.48239579</v>
       </c>
     </row>
     <row r="301" spans="1:5">
@@ -5471,13 +5471,13 @@
         <v>3305791.487896641</v>
       </c>
       <c r="C301">
-        <v>4532710.857228618</v>
+        <v>4546337.323734359</v>
       </c>
       <c r="D301">
-        <v>7764998.37748294</v>
+        <v>7846808.580667539</v>
       </c>
       <c r="E301">
-        <v>11471230.51419158</v>
+        <v>11543043.78528174</v>
       </c>
     </row>
     <row r="302" spans="1:5">
@@ -5488,13 +5488,13 @@
         <v>11903510.92532227</v>
       </c>
       <c r="C302">
-        <v>14391430.74810839</v>
+        <v>14436566.94863439</v>
       </c>
       <c r="D302">
-        <v>21246953.34504363</v>
+        <v>21461412.37308395</v>
       </c>
       <c r="E302">
-        <v>25550598.59687828</v>
+        <v>25719541.69855179</v>
       </c>
     </row>
     <row r="303" spans="1:5">
@@ -5505,13 +5505,13 @@
         <v>11903510.92532227</v>
       </c>
       <c r="C303">
-        <v>14391430.74810839</v>
+        <v>14436566.94863439</v>
       </c>
       <c r="D303">
-        <v>21246953.34504363</v>
+        <v>21461412.37308395</v>
       </c>
       <c r="E303">
-        <v>25550598.59687828</v>
+        <v>25719541.69855179</v>
       </c>
     </row>
     <row r="304" spans="1:5">
@@ -5522,13 +5522,13 @@
         <v>1586099.945301365</v>
       </c>
       <c r="C304">
-        <v>2092651.668063986</v>
+        <v>2095309.228825251</v>
       </c>
       <c r="D304">
-        <v>3332549.428756221</v>
+        <v>3360220.249326613</v>
       </c>
       <c r="E304">
-        <v>4346907.862324429</v>
+        <v>4379624.447773936</v>
       </c>
     </row>
     <row r="305" spans="1:5">
@@ -5539,13 +5539,13 @@
         <v>1277691.622603878</v>
       </c>
       <c r="C305">
-        <v>1831070.209555988</v>
+        <v>1833395.575222095</v>
       </c>
       <c r="D305">
-        <v>3481768.059894559</v>
+        <v>3510677.87243079</v>
       </c>
       <c r="E305">
-        <v>5650980.221021757</v>
+        <v>5693511.782106117</v>
       </c>
     </row>
     <row r="306" spans="1:5">
@@ -5556,13 +5556,13 @@
         <v>529974.5071737122</v>
       </c>
       <c r="C306">
-        <v>701753.7827296387</v>
+        <v>701828.6652494756</v>
       </c>
       <c r="D306">
-        <v>1281208.256096246</v>
+        <v>1285596.279501262</v>
       </c>
       <c r="E306">
-        <v>2001436.059259066</v>
+        <v>2013704.942681095</v>
       </c>
     </row>
     <row r="307" spans="1:5">
@@ -5573,13 +5573,13 @@
         <v>1431895.783952622</v>
       </c>
       <c r="C307">
-        <v>1976393.242060432</v>
+        <v>1978903.160557182</v>
       </c>
       <c r="D307">
-        <v>3382288.972469001</v>
+        <v>3410372.790361339</v>
       </c>
       <c r="E307">
-        <v>4998944.041673093</v>
+        <v>5036568.114940027</v>
       </c>
     </row>
     <row r="308" spans="1:5">
@@ -5590,13 +5590,13 @@
         <v>389862.0022783046</v>
       </c>
       <c r="C308">
-        <v>658274.1492676992</v>
+        <v>658329.0413034159</v>
       </c>
       <c r="D308">
-        <v>1365861.825548877</v>
+        <v>1370320.936307345</v>
       </c>
       <c r="E308">
-        <v>2405674.576962376</v>
+        <v>2419211.181036407</v>
       </c>
     </row>
     <row r="309" spans="1:5">
@@ -5607,13 +5607,13 @@
         <v>505884.7568476344</v>
       </c>
       <c r="C309">
-        <v>701753.7827296387</v>
+        <v>701828.6652494756</v>
       </c>
       <c r="D309">
-        <v>1281208.256096246</v>
+        <v>1285596.279501262</v>
       </c>
       <c r="E309">
-        <v>2070451.09578524</v>
+        <v>2083143.044152857</v>
       </c>
     </row>
     <row r="310" spans="1:5">
@@ -5624,13 +5624,13 @@
         <v>1725601.620688541</v>
       </c>
       <c r="C310">
-        <v>2066074.513114541</v>
+        <v>2068585.390549743</v>
       </c>
       <c r="D310">
-        <v>3328618.924585038</v>
+        <v>3354199.41550402</v>
       </c>
       <c r="E310">
-        <v>4526342.027558978</v>
+        <v>4557404.718115072</v>
       </c>
     </row>
     <row r="311" spans="1:5">
@@ -5641,13 +5641,13 @@
         <v>376470.2908146561</v>
       </c>
       <c r="C311">
-        <v>491574.1065105886</v>
+        <v>491593.1831690118</v>
       </c>
       <c r="D311">
-        <v>962875.5351699267</v>
+        <v>964494.634977345</v>
       </c>
       <c r="E311">
-        <v>1410868.340428283</v>
+        <v>1417705.581823981</v>
       </c>
     </row>
     <row r="312" spans="1:5">
@@ -5658,13 +5658,13 @@
         <v>439215.3392837655</v>
       </c>
       <c r="C312">
-        <v>522297.4881675004</v>
+        <v>522317.757117075</v>
       </c>
       <c r="D312">
-        <v>929672.9305088947</v>
+        <v>931236.199288471</v>
       </c>
       <c r="E312">
-        <v>1139547.505730537</v>
+        <v>1145069.893011677</v>
       </c>
     </row>
     <row r="313" spans="1:5">
@@ -5675,13 +5675,13 @@
         <v>428757.8312055806</v>
       </c>
       <c r="C313">
-        <v>522297.4881675004</v>
+        <v>522317.757117075</v>
       </c>
       <c r="D313">
-        <v>929672.9305088947</v>
+        <v>931236.199288471</v>
       </c>
       <c r="E313">
-        <v>1139547.505730537</v>
+        <v>1145069.893011677</v>
       </c>
     </row>
     <row r="314" spans="1:5">
@@ -5692,13 +5692,13 @@
         <v>355555.2746582863</v>
       </c>
       <c r="C314">
-        <v>491574.1065105886</v>
+        <v>491593.1831690118</v>
       </c>
       <c r="D314">
-        <v>996078.1398309586</v>
+        <v>997753.0706662189</v>
       </c>
       <c r="E314">
-        <v>1519396.674307382</v>
+        <v>1526759.857348903</v>
       </c>
     </row>
     <row r="315" spans="1:5">
@@ -5709,13 +5709,13 @@
         <v>22241980.69050792</v>
       </c>
       <c r="C315">
-        <v>26175496.58662353</v>
+        <v>26249303.42920355</v>
       </c>
       <c r="D315">
-        <v>35679548.84754582</v>
+        <v>36024639.93873565</v>
       </c>
       <c r="E315">
-        <v>44470232.5257965</v>
+        <v>44656226.33830338</v>
       </c>
     </row>
     <row r="316" spans="1:5">
@@ -5726,13 +5726,13 @@
         <v>37216465.80367549</v>
       </c>
       <c r="C316">
-        <v>43647565.32969307</v>
+        <v>43727069.05122137</v>
       </c>
       <c r="D316">
-        <v>59089664.76348213</v>
+        <v>59445689.48326743</v>
       </c>
       <c r="E316">
-        <v>75558388.39043495</v>
+        <v>75754831.03006069</v>
       </c>
     </row>
     <row r="317" spans="1:5">
@@ -5743,13 +5743,13 @@
         <v>10749142.90809297</v>
       </c>
       <c r="C317">
-        <v>13554588.24330338</v>
+        <v>13570500.915573</v>
       </c>
       <c r="D317">
-        <v>19436337.08273406</v>
+        <v>19525821.665316</v>
       </c>
       <c r="E317">
-        <v>26597834.73551836</v>
+        <v>26659282.53515793</v>
       </c>
     </row>
     <row r="318" spans="1:5">
@@ -5760,13 +5760,13 @@
         <v>5242838.298379415</v>
       </c>
       <c r="C318">
-        <v>6969809.108526704</v>
+        <v>6990107.407046652</v>
       </c>
       <c r="D318">
-        <v>10141283.18022974</v>
+        <v>10217497.94194955</v>
       </c>
       <c r="E318">
-        <v>13667199.10571822</v>
+        <v>13712790.49953498</v>
       </c>
     </row>
     <row r="319" spans="1:5">
@@ -5777,13 +5777,13 @@
         <v>3758942.190705794</v>
       </c>
       <c r="C319">
-        <v>4904220.569962705</v>
+        <v>4913833.65331187</v>
       </c>
       <c r="D319">
-        <v>7134191.126429058</v>
+        <v>7201172.921523824</v>
       </c>
       <c r="E319">
-        <v>9464687.155239644</v>
+        <v>9513071.764630074</v>
       </c>
     </row>
     <row r="320" spans="1:5">
@@ -5794,13 +5794,13 @@
         <v>3688179.884916785</v>
       </c>
       <c r="C320">
-        <v>4765490.193048464</v>
+        <v>4784605.062496969</v>
       </c>
       <c r="D320">
-        <v>6771684.787925534</v>
+        <v>6840203.786997265</v>
       </c>
       <c r="E320">
-        <v>8834748.128106266</v>
+        <v>8873582.054440541</v>
       </c>
     </row>
     <row r="321" spans="1:5">
@@ -5811,13 +5811,13 @@
         <v>17704676.2739092</v>
       </c>
       <c r="C321">
-        <v>22768028.40576769</v>
+        <v>22825672.56592058</v>
       </c>
       <c r="D321">
-        <v>31665971.80494697</v>
+        <v>31896055.9906889</v>
       </c>
       <c r="E321">
-        <v>40786446.2800355</v>
+        <v>40928079.82836211</v>
       </c>
     </row>
     <row r="322" spans="1:5">
@@ -5828,13 +5828,13 @@
         <v>11669173.02632643</v>
       </c>
       <c r="C322">
-        <v>12824098.53953964</v>
+        <v>12858414.69205218</v>
       </c>
       <c r="D322">
-        <v>16447334.38320009</v>
+        <v>16617284.91630486</v>
       </c>
       <c r="E322">
-        <v>18670617.76951562</v>
+        <v>18751168.53674114</v>
       </c>
     </row>
     <row r="323" spans="1:5">
@@ -5845,13 +5845,13 @@
         <v>2924194.29256588</v>
       </c>
       <c r="C323">
-        <v>4062029.770964161</v>
+        <v>4070945.477575012</v>
       </c>
       <c r="D323">
-        <v>6486771.323247252</v>
+        <v>6545139.791686069</v>
       </c>
       <c r="E323">
-        <v>9601083.255238615</v>
+        <v>9644107.495377447</v>
       </c>
     </row>
     <row r="324" spans="1:5">
@@ -5862,13 +5862,13 @@
         <v>3220315.233585209</v>
       </c>
       <c r="C324">
-        <v>4197430.763329633</v>
+        <v>4206643.660160846</v>
       </c>
       <c r="D324">
-        <v>6358320.405955227</v>
+        <v>6415533.06313783</v>
       </c>
       <c r="E324">
-        <v>8921360.546903137</v>
+        <v>8961338.823138338</v>
       </c>
     </row>
     <row r="325" spans="1:5">
@@ -5879,13 +5879,13 @@
         <v>2702103.586801383</v>
       </c>
       <c r="C325">
-        <v>3881495.114476865</v>
+        <v>3890014.567460567</v>
       </c>
       <c r="D325">
-        <v>6550996.781893265</v>
+        <v>6609943.155960189</v>
       </c>
       <c r="E325">
-        <v>10280805.96357409</v>
+        <v>10326876.16761656</v>
       </c>
     </row>
     <row r="326" spans="1:5">
@@ -5896,13 +5896,13 @@
         <v>6080129.899419076</v>
       </c>
       <c r="C326">
-        <v>9177281.862643536</v>
+        <v>9196777.457106175</v>
       </c>
       <c r="D326">
-        <v>14589860.28316117</v>
+        <v>14681026.64745574</v>
       </c>
       <c r="E326">
-        <v>21609785.11115396</v>
+        <v>21674256.09783939</v>
       </c>
     </row>
     <row r="327" spans="1:5">
@@ -5913,13 +5913,13 @@
         <v>3075462.464283084</v>
       </c>
       <c r="C327">
-        <v>4772851.102198107</v>
+        <v>4776307.981491067</v>
       </c>
       <c r="D327">
-        <v>7636918.67636547</v>
+        <v>7711279.52560074</v>
       </c>
       <c r="E327">
-        <v>11038227.82049396</v>
+        <v>11092974.77299123</v>
       </c>
     </row>
     <row r="328" spans="1:5">
@@ -5930,13 +5930,13 @@
         <v>3510038.682062215</v>
       </c>
       <c r="C328">
-        <v>4772851.102198107</v>
+        <v>4776307.981491067</v>
       </c>
       <c r="D328">
-        <v>7386527.900091192</v>
+        <v>7458450.688695798</v>
       </c>
       <c r="E328">
-        <v>10536490.19228969</v>
+        <v>10588748.64694617</v>
       </c>
     </row>
     <row r="329" spans="1:5">
@@ -5947,13 +5947,13 @@
         <v>30857.80694630789</v>
       </c>
       <c r="C329">
-        <v>39760.82091214301</v>
+        <v>39779.35833085136</v>
       </c>
       <c r="D329">
-        <v>60226.790135864</v>
+        <v>60776.34945103007</v>
       </c>
       <c r="E329">
-        <v>81851.59608689816</v>
+        <v>82299.03399403226</v>
       </c>
     </row>
     <row r="330" spans="1:5">
@@ -5964,13 +5964,13 @@
         <v>4713480.515912117</v>
       </c>
       <c r="C330">
-        <v>5326842.747988959</v>
+        <v>5330700.872199851</v>
       </c>
       <c r="D330">
-        <v>6823148.653474066</v>
+        <v>6889585.805659678</v>
       </c>
       <c r="E330">
-        <v>7693310.299132157</v>
+        <v>7731467.266024187</v>
       </c>
     </row>
     <row r="331" spans="1:5">
@@ -5981,13 +5981,13 @@
         <v>4011614.580727433</v>
       </c>
       <c r="C331">
-        <v>4948181.964816547</v>
+        <v>4951892.896747412</v>
       </c>
       <c r="D331">
-        <v>7046174.293870091</v>
+        <v>7118465.08129864</v>
       </c>
       <c r="E331">
-        <v>8967106.406605566</v>
+        <v>9016807.230427666</v>
       </c>
     </row>
     <row r="332" spans="1:5">
@@ -5998,13 +5998,13 @@
         <v>8760029.282033943</v>
       </c>
       <c r="C332">
-        <v>11263081.28591549</v>
+        <v>11266512.50812723</v>
       </c>
       <c r="D332">
-        <v>16958561.5165482</v>
+        <v>17057430.78227288</v>
       </c>
       <c r="E332">
-        <v>23391793.11977059</v>
+        <v>23475549.73401621</v>
       </c>
     </row>
     <row r="333" spans="1:5">
@@ -6015,13 +6015,13 @@
         <v>7151560.505745417</v>
       </c>
       <c r="C333">
-        <v>9756129.033231078</v>
+        <v>9765594.529209875</v>
       </c>
       <c r="D333">
-        <v>14814835.85213187</v>
+        <v>14899449.93906644</v>
       </c>
       <c r="E333">
-        <v>20425983.66732866</v>
+        <v>20488627.96388303</v>
       </c>
     </row>
     <row r="334" spans="1:5">
@@ -6032,13 +6032,13 @@
         <v>14880882.00987505</v>
       </c>
       <c r="C334">
-        <v>19178479.55688273</v>
+        <v>19187933.73760702</v>
       </c>
       <c r="D334">
-        <v>27654793.25995259</v>
+        <v>27775044.70658478</v>
       </c>
       <c r="E334">
-        <v>36256990.92509255</v>
+        <v>36334783.31405218</v>
       </c>
     </row>
     <row r="335" spans="1:5">
@@ -6049,13 +6049,13 @@
         <v>6213659.54084129</v>
       </c>
       <c r="C335">
-        <v>9042921.286243578</v>
+        <v>9051685.132429319</v>
       </c>
       <c r="D335">
-        <v>15679492.37306201</v>
+        <v>15775494.45104252</v>
       </c>
       <c r="E335">
-        <v>24097940.93522306</v>
+        <v>24161123.26990259</v>
       </c>
     </row>
     <row r="336" spans="1:5">
@@ -6066,13 +6066,13 @@
         <v>6116072.865570005</v>
       </c>
       <c r="C336">
-        <v>6917520.367536344</v>
+        <v>6918453.088448353</v>
       </c>
       <c r="D336">
-        <v>9372561.800758388</v>
+        <v>9428870.577999683</v>
       </c>
       <c r="E336">
-        <v>11585139.88379347</v>
+        <v>11635434.25065472</v>
       </c>
     </row>
     <row r="337" spans="1:5">
@@ -6083,13 +6083,13 @@
         <v>4996931.996845973</v>
       </c>
       <c r="C337">
-        <v>7316035.264348892</v>
+        <v>7316581.682379633</v>
       </c>
       <c r="D337">
-        <v>11940663.67991652</v>
+        <v>11981813.30880827</v>
       </c>
       <c r="E337">
-        <v>16600873.19180316</v>
+        <v>16634382.57597484</v>
       </c>
     </row>
     <row r="338" spans="1:5">
@@ -6100,13 +6100,13 @@
         <v>3832728.332395494</v>
       </c>
       <c r="C338">
-        <v>6172623.245606463</v>
+        <v>6173052.42552239</v>
       </c>
       <c r="D338">
-        <v>12059163.04175285</v>
+        <v>12100000.34965263</v>
       </c>
       <c r="E338">
-        <v>19638202.16865508</v>
+        <v>19673517.73899334</v>
       </c>
     </row>
     <row r="339" spans="1:5">
@@ -6117,13 +6117,13 @@
         <v>5059393.646806547</v>
       </c>
       <c r="C339">
-        <v>7250322.372752945</v>
+        <v>7250863.882837301</v>
       </c>
       <c r="D339">
-        <v>11905440.4832206</v>
+        <v>11946468.72677639</v>
       </c>
       <c r="E339">
-        <v>16649272.23900958</v>
+        <v>16682879.31817885</v>
       </c>
     </row>
     <row r="340" spans="1:5">
@@ -6137,10 +6137,10 @@
         <v>3079182.620393323</v>
       </c>
       <c r="D340">
-        <v>4697536.13704358</v>
+        <v>4709844.358569789</v>
       </c>
       <c r="E340">
-        <v>5707088.763094282</v>
+        <v>5714706.566270299</v>
       </c>
     </row>
     <row r="341" spans="1:5">
@@ -6154,10 +6154,10 @@
         <v>2722448.048518486</v>
       </c>
       <c r="D341">
-        <v>5151091.350275375</v>
+        <v>5164587.95181101</v>
       </c>
       <c r="E341">
-        <v>7926512.17096428</v>
+        <v>7937092.453153193</v>
       </c>
     </row>
     <row r="342" spans="1:5">
@@ -6168,13 +6168,13 @@
         <v>532145.9930062327</v>
       </c>
       <c r="C342">
-        <v>679554.1922377355</v>
+        <v>681751.0104205951</v>
       </c>
       <c r="D342">
-        <v>1008088.478250072</v>
+        <v>1011296.656958139</v>
       </c>
       <c r="E342">
-        <v>1110598.706430805</v>
+        <v>1112758.788699198</v>
       </c>
     </row>
     <row r="343" spans="1:5">
@@ -6185,13 +6185,13 @@
         <v>517763.668870929</v>
       </c>
       <c r="C343">
-        <v>658318.1237303063</v>
+        <v>660446.2913449515</v>
       </c>
       <c r="D343">
-        <v>1008088.478250072</v>
+        <v>1011296.656958139</v>
       </c>
       <c r="E343">
-        <v>1211562.225197241</v>
+        <v>1213918.678580943</v>
       </c>
     </row>
     <row r="344" spans="1:5">
@@ -6205,10 +6205,10 @@
         <v>3210611.146873525</v>
       </c>
       <c r="D344">
-        <v>4567948.933263068</v>
+        <v>4579917.617643726</v>
       </c>
       <c r="E344">
-        <v>4982379.078891833</v>
+        <v>4989029.541982007</v>
       </c>
     </row>
     <row r="345" spans="1:5">
@@ -6222,10 +6222,10 @@
         <v>960146.058492024</v>
       </c>
       <c r="D345">
-        <v>1621158.563024948</v>
+        <v>1623854.051904541</v>
       </c>
       <c r="E345">
-        <v>1932480.386984873</v>
+        <v>1934378.151804717</v>
       </c>
     </row>
     <row r="346" spans="1:5">
@@ -6239,10 +6239,10 @@
         <v>945815.5203055758</v>
       </c>
       <c r="D346">
-        <v>1593207.553317621</v>
+        <v>1595856.568251014</v>
       </c>
       <c r="E346">
-        <v>1892220.378922688</v>
+        <v>1894078.606975452</v>
       </c>
     </row>
     <row r="347" spans="1:5">
@@ -6256,10 +6256,10 @@
         <v>945815.5203055758</v>
       </c>
       <c r="D347">
-        <v>1593207.553317621</v>
+        <v>1595856.568251014</v>
       </c>
       <c r="E347">
-        <v>1892220.378922688</v>
+        <v>1894078.606975452</v>
       </c>
     </row>
     <row r="348" spans="1:5">
@@ -6270,13 +6270,13 @@
         <v>683305.3939318368</v>
       </c>
       <c r="C348">
-        <v>884173.4199332974</v>
+        <v>884199.6936510631</v>
       </c>
       <c r="D348">
-        <v>1331878.193151871</v>
+        <v>1333341.769118865</v>
       </c>
       <c r="E348">
-        <v>1647720.147537994</v>
+        <v>1650032.846438604</v>
       </c>
     </row>
     <row r="349" spans="1:5">
@@ -6287,13 +6287,13 @@
         <v>802883.8378699083</v>
       </c>
       <c r="C349">
-        <v>953976.5846648735</v>
+        <v>954004.9326235155</v>
       </c>
       <c r="D349">
-        <v>1259884.777305824</v>
+        <v>1261269.241058386</v>
       </c>
       <c r="E349">
-        <v>1356946.003854819</v>
+        <v>1358850.579420027</v>
       </c>
     </row>
     <row r="350" spans="1:5">
@@ -6304,13 +6304,13 @@
         <v>802883.8378699083</v>
       </c>
       <c r="C350">
-        <v>953976.5846648735</v>
+        <v>954004.9326235155</v>
       </c>
       <c r="D350">
-        <v>1259884.777305824</v>
+        <v>1261269.241058386</v>
       </c>
       <c r="E350">
-        <v>1356946.003854819</v>
+        <v>1358850.579420027</v>
       </c>
     </row>
     <row r="351" spans="1:5">
@@ -6321,13 +6321,13 @@
         <v>823259.7252521839</v>
       </c>
       <c r="C351">
-        <v>1336718.794439075</v>
+        <v>1337161.018253002</v>
       </c>
       <c r="D351">
-        <v>2543794.096840793</v>
+        <v>2546358.236861063</v>
       </c>
       <c r="E351">
-        <v>3276871.483803953</v>
+        <v>3279561.36622321</v>
       </c>
     </row>
     <row r="352" spans="1:5">
@@ -6338,13 +6338,13 @@
         <v>984971.4569981486</v>
       </c>
       <c r="C352">
-        <v>1426690.25175709</v>
+        <v>1427162.240635416</v>
       </c>
       <c r="D352">
-        <v>2411304.820963668</v>
+        <v>2413735.412024549</v>
       </c>
       <c r="E352">
-        <v>2561232.883892745</v>
+        <v>2563335.320726187</v>
       </c>
     </row>
     <row r="353" spans="1:5">
@@ -6355,13 +6355,13 @@
         <v>4671433.844320204</v>
       </c>
       <c r="C353">
-        <v>6286599.7086367</v>
+        <v>6288072.665228025</v>
       </c>
       <c r="D353">
-        <v>9181424.156435205</v>
+        <v>9195593.057243779</v>
       </c>
       <c r="E353">
-        <v>12200572.81782144</v>
+        <v>12238754.52639167</v>
       </c>
     </row>
     <row r="354" spans="1:5">
@@ -6372,13 +6372,13 @@
         <v>6400794.741927771</v>
       </c>
       <c r="C354">
-        <v>6927960.201856918</v>
+        <v>6928056.513486216</v>
       </c>
       <c r="D354">
-        <v>8269963.095927685</v>
+        <v>8273090.288218707</v>
       </c>
       <c r="E354">
-        <v>8560633.922146004</v>
+        <v>8573294.777190471</v>
       </c>
     </row>
     <row r="355" spans="1:5">
@@ -6389,13 +6389,13 @@
         <v>6205337.494694003</v>
       </c>
       <c r="C355">
-        <v>6891080.449851767</v>
+        <v>6892695.036884566</v>
       </c>
       <c r="D355">
-        <v>8431019.29749579</v>
+        <v>8444030.163142124</v>
       </c>
       <c r="E355">
-        <v>8911202.695369579</v>
+        <v>8939090.315844895</v>
       </c>
     </row>
     <row r="356" spans="1:5">
@@ -6406,13 +6406,13 @@
         <v>1129016.795465454</v>
       </c>
       <c r="C356">
-        <v>1464743.159016459</v>
+        <v>1464772.504762368</v>
       </c>
       <c r="D356">
-        <v>2105376.315756403</v>
+        <v>2109039.578636752</v>
       </c>
       <c r="E356">
-        <v>2551810.563788859</v>
+        <v>2554618.548744314</v>
       </c>
     </row>
     <row r="357" spans="1:5">
@@ -6423,13 +6423,13 @@
         <v>1311651.86532016</v>
       </c>
       <c r="C357">
-        <v>1556289.606454988</v>
+        <v>1556320.786310016</v>
       </c>
       <c r="D357">
-        <v>1998323.28275184</v>
+        <v>2001800.278028103</v>
       </c>
       <c r="E357">
-        <v>2070336.872507942</v>
+        <v>2072615.048981236</v>
       </c>
     </row>
     <row r="358" spans="1:5">
@@ -6440,13 +6440,13 @@
         <v>1295048.67715155</v>
       </c>
       <c r="C358">
-        <v>1556289.606454988</v>
+        <v>1556320.786310016</v>
       </c>
       <c r="D358">
-        <v>1998323.28275184</v>
+        <v>2001800.278028103</v>
       </c>
       <c r="E358">
-        <v>2118484.241636034</v>
+        <v>2120815.398957544</v>
       </c>
     </row>
     <row r="359" spans="1:5">
@@ -6457,13 +6457,13 @@
         <v>417864.8037264797</v>
       </c>
       <c r="C359">
-        <v>691240.2398869602</v>
+        <v>691533.7260253791</v>
       </c>
       <c r="D359">
-        <v>1341843.712518356</v>
+        <v>1343027.63739927</v>
       </c>
       <c r="E359">
-        <v>1790349.460478938</v>
+        <v>1791520.877042226</v>
       </c>
     </row>
     <row r="360" spans="1:5">
@@ -6474,13 +6474,13 @@
         <v>546438.5894884735</v>
       </c>
       <c r="C360">
-        <v>745455.1606624081</v>
+        <v>745771.6653214874</v>
       </c>
       <c r="D360">
-        <v>1232305.450271959</v>
+        <v>1233392.728223819</v>
       </c>
       <c r="E360">
-        <v>1245460.494246218</v>
+        <v>1246275.392725027</v>
       </c>
     </row>
     <row r="361" spans="1:5">
@@ -6491,13 +6491,13 @@
         <v>10297581.28394632</v>
       </c>
       <c r="C361">
-        <v>15189279.89736909</v>
+        <v>15189557.77957208</v>
       </c>
       <c r="D361">
-        <v>27470515.09468839</v>
+        <v>27634727.97461389</v>
       </c>
       <c r="E361">
-        <v>40051318.15218556</v>
+        <v>40294405.93781947</v>
       </c>
     </row>
     <row r="362" spans="1:5">
@@ -6508,13 +6508,13 @@
         <v>12795255.83150032</v>
       </c>
       <c r="C362">
-        <v>16255614.59309088</v>
+        <v>16259362.97386235</v>
       </c>
       <c r="D362">
-        <v>26410645.65948457</v>
+        <v>26613757.85305084</v>
       </c>
       <c r="E362">
-        <v>32205471.51774957</v>
+        <v>32432401.75588967</v>
       </c>
     </row>
     <row r="363" spans="1:5">
@@ -6528,10 +6528,10 @@
         <v>1163476.75745592</v>
       </c>
       <c r="D363">
-        <v>2245751.870949796</v>
+        <v>2250574.667020818</v>
       </c>
       <c r="E363">
-        <v>3416448.930905918</v>
+        <v>3435170.170069399</v>
       </c>
     </row>
     <row r="364" spans="1:5">
@@ -6542,13 +6542,13 @@
         <v>2081301.623481127</v>
       </c>
       <c r="C364">
-        <v>3148001.274726113</v>
+        <v>3158845.420722006</v>
       </c>
       <c r="D364">
-        <v>5968325.733768006</v>
+        <v>6029576.820795115</v>
       </c>
       <c r="E364">
-        <v>8668584.460594801</v>
+        <v>8740532.908224834</v>
       </c>
     </row>
     <row r="365" spans="1:5">
@@ -6559,13 +6559,13 @@
         <v>1992357.109657147</v>
       </c>
       <c r="C365">
-        <v>3040377.299521802</v>
+        <v>3050850.705483647</v>
       </c>
       <c r="D365">
-        <v>6020224.218409467</v>
+        <v>6082007.923584637</v>
       </c>
       <c r="E365">
-        <v>9210370.989381976</v>
+        <v>9286816.214988885</v>
       </c>
     </row>
     <row r="366" spans="1:5">
@@ -6576,13 +6576,13 @@
         <v>573436.6617520605</v>
       </c>
       <c r="C366">
-        <v>861931.9815324791</v>
+        <v>864997.8836631525</v>
       </c>
       <c r="D366">
-        <v>1636462.031474377</v>
+        <v>1651984.303608983</v>
       </c>
       <c r="E366">
-        <v>2142487.655160278</v>
+        <v>2161848.603940274</v>
       </c>
     </row>
     <row r="367" spans="1:5">
@@ -6593,13 +6593,13 @@
         <v>637151.8463911783</v>
       </c>
       <c r="C367">
-        <v>882954.7127893688</v>
+        <v>886095.3930207903</v>
       </c>
       <c r="D367">
-        <v>1591004.752822312</v>
+        <v>1606095.850730955</v>
       </c>
       <c r="E367">
-        <v>1928238.88964425</v>
+        <v>1945663.743546246</v>
       </c>
     </row>
     <row r="368" spans="1:5">
@@ -6610,13 +6610,13 @@
         <v>626481.4857543097</v>
       </c>
       <c r="C368">
-        <v>895537.2629840927</v>
+        <v>898737.9773919581</v>
       </c>
       <c r="D368">
-        <v>1753117.987072058</v>
+        <v>1769345.378191492</v>
       </c>
       <c r="E368">
-        <v>2377058.637790032</v>
+        <v>2398340.462955242</v>
       </c>
     </row>
     <row r="369" spans="1:5">
@@ -6627,13 +6627,13 @@
         <v>700867.0310302961</v>
       </c>
       <c r="C369">
-        <v>903977.4440462585</v>
+        <v>907192.9023784281</v>
       </c>
       <c r="D369">
-        <v>1545547.474170245</v>
+        <v>1560207.397852928</v>
       </c>
       <c r="E369">
-        <v>1642573.868956213</v>
+        <v>1657417.263020876</v>
       </c>
     </row>
     <row r="370" spans="1:5">
@@ -6644,13 +6644,13 @@
         <v>374484.1796276189</v>
       </c>
       <c r="C370">
-        <v>579249.585697463</v>
+        <v>579408.9076436061</v>
       </c>
       <c r="D370">
-        <v>1206879.842964574</v>
+        <v>1211984.780722564</v>
       </c>
       <c r="E370">
-        <v>1797877.326653671</v>
+        <v>1810971.65106807</v>
       </c>
     </row>
     <row r="371" spans="1:5">
@@ -6661,13 +6661,13 @@
         <v>468105.2245345237</v>
       </c>
       <c r="C371">
-        <v>616620.5267102025</v>
+        <v>616790.1274915807</v>
       </c>
       <c r="D371">
-        <v>1123646.750346328</v>
+        <v>1128399.623431353</v>
       </c>
       <c r="E371">
-        <v>1331760.982706423</v>
+        <v>1341460.482272645</v>
       </c>
     </row>
     <row r="372" spans="1:5">
@@ -6678,13 +6678,13 @@
         <v>432997.3326944344</v>
       </c>
       <c r="C372">
-        <v>597935.0562038327</v>
+        <v>598099.5175675934</v>
       </c>
       <c r="D372">
-        <v>1165263.296655451</v>
+        <v>1170192.202076959</v>
       </c>
       <c r="E372">
-        <v>1464937.080977066</v>
+        <v>1475606.530499909</v>
       </c>
     </row>
     <row r="373" spans="1:5">
@@ -6695,13 +6695,13 @@
         <v>4450406.952548334</v>
       </c>
       <c r="C373">
-        <v>6171119.134777244</v>
+        <v>6171150.659813534</v>
       </c>
       <c r="D373">
-        <v>9930738.323039064</v>
+        <v>9957331.512563888</v>
       </c>
       <c r="E373">
-        <v>14223066.52396266</v>
+        <v>14294829.67526488</v>
       </c>
     </row>
     <row r="374" spans="1:5">
@@ -6712,13 +6712,13 @@
         <v>3223987.163584713</v>
       </c>
       <c r="C374">
-        <v>4743641.33300726</v>
+        <v>4743647.59656344</v>
       </c>
       <c r="D374">
-        <v>7833226.000998185</v>
+        <v>7851107.625368848</v>
       </c>
       <c r="E374">
-        <v>11535834.70335517</v>
+        <v>11567735.7566575</v>
       </c>
     </row>
     <row r="375" spans="1:5">
@@ -6729,13 +6729,13 @@
         <v>6149218.208628613</v>
       </c>
       <c r="C375">
-        <v>7084192.884310612</v>
+        <v>7084229.073765536</v>
       </c>
       <c r="D375">
-        <v>9067195.860166103</v>
+        <v>9091476.598427897</v>
       </c>
       <c r="E375">
-        <v>9766068.719218602</v>
+        <v>9815343.878407685</v>
       </c>
     </row>
     <row r="376" spans="1:5">
@@ -6746,13 +6746,13 @@
         <v>4187891.990237252</v>
       </c>
       <c r="C376">
-        <v>4805159.026950098</v>
+        <v>4805552.576767019</v>
       </c>
       <c r="D376">
-        <v>6518617.096037805</v>
+        <v>6535696.874135306</v>
       </c>
       <c r="E376">
-        <v>7534357.981488294</v>
+        <v>7560839.662732282</v>
       </c>
     </row>
     <row r="377" spans="1:5">
@@ -6763,13 +6763,13 @@
         <v>4187891.990237252</v>
       </c>
       <c r="C377">
-        <v>4805159.026950098</v>
+        <v>4805552.576767019</v>
       </c>
       <c r="D377">
-        <v>6518617.096037805</v>
+        <v>6535696.874135306</v>
       </c>
       <c r="E377">
-        <v>7534357.981488294</v>
+        <v>7560839.662732282</v>
       </c>
     </row>
     <row r="378" spans="1:5">
@@ -6780,13 +6780,13 @@
         <v>2678260.157370931</v>
       </c>
       <c r="C378">
-        <v>3568445.709756522</v>
+        <v>3568691.729558086</v>
       </c>
       <c r="D378">
-        <v>5340601.606654178</v>
+        <v>5358221.244191712</v>
       </c>
       <c r="E378">
-        <v>7222445.125901391</v>
+        <v>7269814.897656182</v>
       </c>
     </row>
     <row r="379" spans="1:5">
@@ -6797,13 +6797,13 @@
         <v>2594564.52745309</v>
       </c>
       <c r="C379">
-        <v>3677683.843728661</v>
+        <v>3677937.394748639</v>
       </c>
       <c r="D379">
-        <v>5394007.622720719</v>
+        <v>5411803.456633628</v>
       </c>
       <c r="E379">
-        <v>7150935.768219198</v>
+        <v>7197836.532332852</v>
       </c>
     </row>
     <row r="380" spans="1:5">
@@ -6814,13 +6814,13 @@
         <v>3598912.086467189</v>
       </c>
       <c r="C380">
-        <v>3859747.400348892</v>
+        <v>3860013.503399562</v>
       </c>
       <c r="D380">
-        <v>4859947.462055302</v>
+        <v>4875981.332214458</v>
       </c>
       <c r="E380">
-        <v>5363201.826164399</v>
+        <v>5398377.399249639</v>
       </c>
     </row>
     <row r="381" spans="1:5">
@@ -6831,13 +6831,13 @@
         <v>2678260.157370931</v>
       </c>
       <c r="C381">
-        <v>3568445.709756522</v>
+        <v>3568691.729558086</v>
       </c>
       <c r="D381">
-        <v>5340601.606654178</v>
+        <v>5358221.244191712</v>
       </c>
       <c r="E381">
-        <v>7222445.125901391</v>
+        <v>7269814.897656182</v>
       </c>
     </row>
     <row r="382" spans="1:5">
@@ -6848,13 +6848,13 @@
         <v>1807478.57607511</v>
       </c>
       <c r="C382">
-        <v>2082798.694212917</v>
+        <v>2083202.75058193</v>
       </c>
       <c r="D382">
-        <v>2669275.365724786</v>
+        <v>2675945.150415601</v>
       </c>
       <c r="E382">
-        <v>2960651.053276714</v>
+        <v>2978277.917501087</v>
       </c>
     </row>
     <row r="383" spans="1:5">
@@ -6865,13 +6865,13 @@
         <v>4973655.881042176</v>
       </c>
       <c r="C383">
-        <v>6876975.980176813</v>
+        <v>6876976.093609273</v>
       </c>
       <c r="D383">
-        <v>10695245.93989477</v>
+        <v>10745260.96896996</v>
       </c>
       <c r="E383">
-        <v>14824205.98829103</v>
+        <v>14916417.82200489</v>
       </c>
     </row>
     <row r="384" spans="1:5">
@@ -6882,13 +6882,13 @@
         <v>7676034.769816656</v>
       </c>
       <c r="C384">
-        <v>8375665.600201556</v>
+        <v>8375673.459697052</v>
       </c>
       <c r="D384">
-        <v>11147650.64997257</v>
+        <v>11185876.22336449</v>
       </c>
       <c r="E384">
-        <v>12764761.48775015</v>
+        <v>12837095.81598021</v>
       </c>
     </row>
     <row r="385" spans="1:5">
@@ -6899,13 +6899,13 @@
         <v>1165257.955339782</v>
       </c>
       <c r="C385">
-        <v>1607205.347027826</v>
+        <v>1607527.837034822</v>
       </c>
       <c r="D385">
-        <v>2378469.718101219</v>
+        <v>2400387.483395725</v>
       </c>
       <c r="E385">
-        <v>3201282.677821255</v>
+        <v>3222986.524775687</v>
       </c>
     </row>
     <row r="386" spans="1:5">
@@ -6916,13 +6916,13 @@
         <v>1523258.770591925</v>
       </c>
       <c r="C386">
-        <v>2102947.168733657</v>
+        <v>2102949.395320105</v>
       </c>
       <c r="D386">
-        <v>3400213.542260866</v>
+        <v>3411367.367203911</v>
       </c>
       <c r="E386">
-        <v>4509561.287941951</v>
+        <v>4528184.195811195</v>
       </c>
     </row>
     <row r="387" spans="1:5">
@@ -6933,13 +6933,13 @@
         <v>1746174.688239524</v>
       </c>
       <c r="C387">
-        <v>2181807.68756117</v>
+        <v>2181809.997644609</v>
       </c>
       <c r="D387">
-        <v>3309541.181133909</v>
+        <v>3320397.57074514</v>
       </c>
       <c r="E387">
-        <v>3921357.641688654</v>
+        <v>3937551.474618431</v>
       </c>
     </row>
     <row r="388" spans="1:5">
@@ -6950,13 +6950,13 @@
         <v>1986757.066690547</v>
       </c>
       <c r="C388">
-        <v>2925693.74672394</v>
+        <v>2926163.359114004</v>
       </c>
       <c r="D388">
-        <v>6975453.334767713</v>
+        <v>6976214.754166878</v>
       </c>
       <c r="E388">
-        <v>11147779.03103783</v>
+        <v>11155325.8053625</v>
       </c>
     </row>
     <row r="389" spans="1:5">
@@ -6967,13 +6967,13 @@
         <v>194695.9053862769</v>
       </c>
       <c r="C389">
-        <v>277318.757933689</v>
+        <v>277320.613407361</v>
       </c>
       <c r="D389">
-        <v>699100.1545079711</v>
+        <v>699254.0640358707</v>
       </c>
       <c r="E389">
-        <v>993153.7898135068</v>
+        <v>994176.3357809549</v>
       </c>
     </row>
     <row r="390" spans="1:5">
@@ -6984,13 +6984,13 @@
         <v>194695.9053862769</v>
       </c>
       <c r="C390">
-        <v>285984.9691191168</v>
+        <v>285986.882576341</v>
       </c>
       <c r="D390">
-        <v>699100.1545079711</v>
+        <v>699254.0640358707</v>
       </c>
       <c r="E390">
-        <v>948010.4357310747</v>
+        <v>948986.5023363661</v>
       </c>
     </row>
     <row r="391" spans="1:5">
@@ -7001,13 +7001,13 @@
         <v>1986757.066690547</v>
       </c>
       <c r="C391">
-        <v>2925693.74672394</v>
+        <v>2926163.359114004</v>
       </c>
       <c r="D391">
-        <v>6975453.334767713</v>
+        <v>6976214.754166878</v>
       </c>
       <c r="E391">
-        <v>11147779.03103783</v>
+        <v>11155325.8053625</v>
       </c>
     </row>
     <row r="392" spans="1:5">
@@ -7018,13 +7018,13 @@
         <v>220313.7876739449</v>
       </c>
       <c r="C392">
-        <v>294651.1803045446</v>
+        <v>294653.1517453211</v>
       </c>
       <c r="D392">
-        <v>674132.2918469722</v>
+        <v>674280.7046060181</v>
       </c>
       <c r="E392">
-        <v>812580.3734837782</v>
+        <v>813417.0020025995</v>
       </c>
     </row>
     <row r="393" spans="1:5">
@@ -7035,13 +7035,13 @@
         <v>466516.15568665</v>
       </c>
       <c r="C393">
-        <v>633440.6160834894</v>
+        <v>633453.37841426</v>
       </c>
       <c r="D393">
-        <v>1410129.200915673</v>
+        <v>1410323.077255549</v>
       </c>
       <c r="E393">
-        <v>2003518.404558005</v>
+        <v>2004278.048206984</v>
       </c>
     </row>
     <row r="394" spans="1:5">
@@ -7052,13 +7052,13 @@
         <v>443647.7166824024</v>
       </c>
       <c r="C394">
-        <v>618878.7628401908</v>
+        <v>618891.2317840471</v>
       </c>
       <c r="D394">
-        <v>1429185.000928047</v>
+        <v>1429381.497218462</v>
       </c>
       <c r="E394">
-        <v>2102052.096585448</v>
+        <v>2102849.099758147</v>
       </c>
     </row>
     <row r="395" spans="1:5">
@@ -7069,13 +7069,13 @@
         <v>345087.5707089988</v>
       </c>
       <c r="C395">
-        <v>538603.2126685628</v>
+        <v>538617.2316171284</v>
       </c>
       <c r="D395">
-        <v>1324377.181500908</v>
+        <v>1324547.839611738</v>
       </c>
       <c r="E395">
-        <v>2224317.252392716</v>
+        <v>2225374.135088466</v>
       </c>
     </row>
     <row r="396" spans="1:5">
@@ -7086,13 +7086,13 @@
         <v>433973.763164347</v>
       </c>
       <c r="C396">
-        <v>587567.1410929775</v>
+        <v>587582.4344914127</v>
       </c>
       <c r="D396">
-        <v>1242877.047254698</v>
+        <v>1243037.203327938</v>
       </c>
       <c r="E396">
-        <v>1702992.896363173</v>
+        <v>1703802.072177107</v>
       </c>
     </row>
     <row r="397" spans="1:5">
@@ -7106,10 +7106,10 @@
         <v>215735.9292017858</v>
       </c>
       <c r="D397">
-        <v>473559.940424461</v>
+        <v>473619.7370921614</v>
       </c>
       <c r="E397">
-        <v>737824.8332271423</v>
+        <v>738345.1065326458</v>
       </c>
     </row>
     <row r="398" spans="1:5">
@@ -7123,10 +7123,10 @@
         <v>215735.9292017858</v>
       </c>
       <c r="D398">
-        <v>473559.940424461</v>
+        <v>473619.7370921614</v>
       </c>
       <c r="E398">
-        <v>737824.8332271423</v>
+        <v>738345.1065326458</v>
       </c>
     </row>
     <row r="399" spans="1:5">
@@ -7140,10 +7140,10 @@
         <v>2058288.126894574</v>
       </c>
       <c r="D399">
-        <v>6356930.294625834</v>
+        <v>6360731.639796957</v>
       </c>
       <c r="E399">
-        <v>11220281.03311489</v>
+        <v>11249096.62495249</v>
       </c>
     </row>
     <row r="400" spans="1:5">
@@ -7157,10 +7157,10 @@
         <v>1846699.608755172</v>
       </c>
       <c r="D400">
-        <v>5159186.543177562</v>
+        <v>5162230.115585829</v>
       </c>
       <c r="E400">
-        <v>7656108.471069327</v>
+        <v>7674502.761477103</v>
       </c>
     </row>
     <row r="401" spans="1:5">
@@ -7174,10 +7174,10 @@
         <v>2139005.30834142</v>
       </c>
       <c r="D401">
-        <v>6150200.854150197</v>
+        <v>6153878.578340146</v>
       </c>
       <c r="E401">
-        <v>9925633.221601635</v>
+        <v>9951123.937457969</v>
       </c>
     </row>
     <row r="402" spans="1:5">
@@ -7191,10 +7191,10 @@
         <v>172439.494177336</v>
       </c>
       <c r="D402">
-        <v>499097.1640800636</v>
+        <v>499263.5775522914</v>
       </c>
       <c r="E402">
-        <v>838611.4023506788</v>
+        <v>840226.8893574629</v>
       </c>
     </row>
     <row r="403" spans="1:5">
@@ -7208,10 +7208,10 @@
         <v>1823615.863645732</v>
       </c>
       <c r="D403">
-        <v>5261348.652943454</v>
+        <v>5264452.494112281</v>
       </c>
       <c r="E403">
-        <v>8182465.928455343</v>
+        <v>8202124.826328654</v>
       </c>
     </row>
     <row r="404" spans="1:5">
@@ -7225,10 +7225,10 @@
         <v>402559.898889713</v>
       </c>
       <c r="D404">
-        <v>1284152.276137727</v>
+        <v>1284594.385898406</v>
       </c>
       <c r="E404">
-        <v>2118737.350307971</v>
+        <v>2122201.463264057</v>
       </c>
     </row>
     <row r="405" spans="1:5">
@@ -7242,10 +7242,10 @@
         <v>415758.5840992118</v>
       </c>
       <c r="D405">
-        <v>1238289.694847094</v>
+        <v>1238716.014973463</v>
       </c>
       <c r="E405">
-        <v>1902539.661501035</v>
+        <v>1905650.293543235</v>
       </c>
     </row>
     <row r="406" spans="1:5">
@@ -7259,10 +7259,10 @@
         <v>402559.898889713</v>
       </c>
       <c r="D406">
-        <v>1284152.276137727</v>
+        <v>1284594.385898406</v>
       </c>
       <c r="E406">
-        <v>2118737.350307971</v>
+        <v>2122201.463264057</v>
       </c>
     </row>
     <row r="407" spans="1:5">
@@ -7276,10 +7276,10 @@
         <v>358210.6227658093</v>
       </c>
       <c r="D407">
-        <v>1316444.10205756</v>
+        <v>1316736.350437545</v>
       </c>
       <c r="E407">
-        <v>2545289.405669775</v>
+        <v>2548328.546574458</v>
       </c>
     </row>
     <row r="408" spans="1:5">
@@ -7293,10 +7293,10 @@
         <v>392876.166904436</v>
       </c>
       <c r="D408">
-        <v>1231512.224505459</v>
+        <v>1231785.618151252</v>
       </c>
       <c r="E408">
-        <v>1939268.118605542</v>
+        <v>1941583.654532921</v>
       </c>
     </row>
     <row r="409" spans="1:5">
@@ -7310,10 +7310,10 @@
         <v>363988.2134555804</v>
       </c>
       <c r="D409">
-        <v>1295211.132669534</v>
+        <v>1295498.667365971</v>
       </c>
       <c r="E409">
-        <v>2424085.148256928</v>
+        <v>2426979.568166151</v>
       </c>
     </row>
     <row r="410" spans="1:5">
@@ -7321,16 +7321,16 @@
         <v>409</v>
       </c>
       <c r="B410">
-        <v>1658734.855119521</v>
+        <v>1658910.82710113</v>
       </c>
       <c r="C410">
-        <v>2982869.333008354</v>
+        <v>2988482.677180957</v>
       </c>
       <c r="D410">
-        <v>7168358.785558079</v>
+        <v>7218777.333480528</v>
       </c>
       <c r="E410">
-        <v>11645961.5041622</v>
+        <v>11741356.73806893</v>
       </c>
     </row>
     <row r="411" spans="1:5">
@@ -7341,13 +7341,13 @@
         <v>317984.9493369432</v>
       </c>
       <c r="C411">
-        <v>716193.7097033152</v>
+        <v>716450.9580272381</v>
       </c>
       <c r="D411">
-        <v>2376121.265229072</v>
+        <v>2382985.345553311</v>
       </c>
       <c r="E411">
-        <v>5084089.94045392</v>
+        <v>5113754.453245793</v>
       </c>
     </row>
     <row r="412" spans="1:5">
@@ -7358,13 +7358,13 @@
         <v>545117.0560061884</v>
       </c>
       <c r="C412">
-        <v>878350.7760512356</v>
+        <v>878666.2692786882</v>
       </c>
       <c r="D412">
-        <v>2127869.789757378</v>
+        <v>2134016.727361174</v>
       </c>
       <c r="E412">
-        <v>3307721.166078453</v>
+        <v>3327020.9695816</v>
       </c>
     </row>
     <row r="413" spans="1:5">
@@ -7375,13 +7375,13 @@
         <v>1404781.298513178</v>
       </c>
       <c r="C413">
-        <v>2212391.965742142</v>
+        <v>2213439.217471783</v>
       </c>
       <c r="D413">
-        <v>4876027.559565932</v>
+        <v>4890634.82840247</v>
       </c>
       <c r="E413">
-        <v>6708630.866496376</v>
+        <v>6747054.399143803</v>
       </c>
     </row>
     <row r="414" spans="1:5">
@@ -7389,16 +7389,16 @@
         <v>413</v>
       </c>
       <c r="B414">
-        <v>1658734.855119521</v>
+        <v>1658910.82710113</v>
       </c>
       <c r="C414">
-        <v>2982869.333008354</v>
+        <v>2988482.677180957</v>
       </c>
       <c r="D414">
-        <v>7168358.785558079</v>
+        <v>7218777.333480528</v>
       </c>
       <c r="E414">
-        <v>11645961.5041622</v>
+        <v>11741356.73806893</v>
       </c>
     </row>
     <row r="415" spans="1:5">
@@ -7409,13 +7409,13 @@
         <v>617897.4504561016</v>
       </c>
       <c r="C415">
-        <v>1018667.178257893</v>
+        <v>1019441.660043348</v>
       </c>
       <c r="D415">
-        <v>2401034.545461476</v>
+        <v>2412443.056456515</v>
       </c>
       <c r="E415">
-        <v>3667117.606016176</v>
+        <v>3693894.147292169</v>
       </c>
     </row>
     <row r="416" spans="1:5">
@@ -7426,13 +7426,13 @@
         <v>698143.8725932576</v>
       </c>
       <c r="C416">
-        <v>1090404.303487322</v>
+        <v>1091233.326243583</v>
       </c>
       <c r="D416">
-        <v>2326002.215915805</v>
+        <v>2337054.210942249</v>
       </c>
       <c r="E416">
-        <v>3023763.640048426</v>
+        <v>3045842.542504069</v>
       </c>
     </row>
     <row r="417" spans="1:5">
@@ -7443,13 +7443,13 @@
         <v>156836.2856825288</v>
       </c>
       <c r="C417">
-        <v>234612.9909009759</v>
+        <v>234664.0436497215</v>
       </c>
       <c r="D417">
-        <v>610962.9380774819</v>
+        <v>612079.3446249004</v>
       </c>
       <c r="E417">
-        <v>1043023.535102143</v>
+        <v>1047998.588154001</v>
       </c>
     </row>
     <row r="418" spans="1:5">
@@ -7460,13 +7460,13 @@
         <v>188203.5428190345</v>
       </c>
       <c r="C418">
-        <v>255941.4446192464</v>
+        <v>255997.1385269688</v>
       </c>
       <c r="D418">
-        <v>580414.7911736078</v>
+        <v>581475.3773936554</v>
       </c>
       <c r="E418">
-        <v>768543.6574436842</v>
+        <v>772209.4860082114</v>
       </c>
     </row>
     <row r="419" spans="1:5">
@@ -7480,10 +7480,10 @@
         <v>687629.0835711417</v>
       </c>
       <c r="D419">
-        <v>1388435.087641645</v>
+        <v>1390168.344937745</v>
       </c>
       <c r="E419">
-        <v>2273949.929668717</v>
+        <v>2281066.56704077</v>
       </c>
     </row>
     <row r="420" spans="1:5">
@@ -7497,10 +7497,10 @@
         <v>687629.0835711417</v>
       </c>
       <c r="D420">
-        <v>1388435.087641645</v>
+        <v>1390168.344937745</v>
       </c>
       <c r="E420">
-        <v>2273949.929668717</v>
+        <v>2281066.56704077</v>
       </c>
     </row>
     <row r="421" spans="1:5">
@@ -7514,10 +7514,10 @@
         <v>668114.2226479377</v>
       </c>
       <c r="D421">
-        <v>1344597.93669863</v>
+        <v>1346467.711601018</v>
       </c>
       <c r="E421">
-        <v>2203788.607272876</v>
+        <v>2211230.670796098</v>
       </c>
     </row>
     <row r="422" spans="1:5">
@@ -7531,10 +7531,10 @@
         <v>668114.2226479377</v>
       </c>
       <c r="D422">
-        <v>1344597.93669863</v>
+        <v>1346467.711601018</v>
       </c>
       <c r="E422">
-        <v>2203788.607272876</v>
+        <v>2211230.670796098</v>
       </c>
     </row>
     <row r="423" spans="1:5">
@@ -7548,10 +7548,10 @@
         <v>687629.0835711417</v>
       </c>
       <c r="D423">
-        <v>1388435.087641645</v>
+        <v>1390168.344937745</v>
       </c>
       <c r="E423">
-        <v>2273949.929668717</v>
+        <v>2281066.56704077</v>
       </c>
     </row>
     <row r="424" spans="1:5">
@@ -7565,10 +7565,10 @@
         <v>687629.0835711417</v>
       </c>
       <c r="D424">
-        <v>1388435.087641645</v>
+        <v>1390168.344937745</v>
       </c>
       <c r="E424">
-        <v>2273949.929668717</v>
+        <v>2281066.56704077</v>
       </c>
     </row>
     <row r="425" spans="1:5">
@@ -7582,10 +7582,10 @@
         <v>668114.2226479377</v>
       </c>
       <c r="D425">
-        <v>1344597.93669863</v>
+        <v>1346467.711601018</v>
       </c>
       <c r="E425">
-        <v>2203788.607272876</v>
+        <v>2211230.670796098</v>
       </c>
     </row>
     <row r="426" spans="1:5">
@@ -7599,10 +7599,10 @@
         <v>687629.0835711417</v>
       </c>
       <c r="D426">
-        <v>1388435.087641645</v>
+        <v>1390168.344937745</v>
       </c>
       <c r="E426">
-        <v>2273949.929668717</v>
+        <v>2281066.56704077</v>
       </c>
     </row>
     <row r="427" spans="1:5">
@@ -7616,10 +7616,10 @@
         <v>687629.0835711417</v>
       </c>
       <c r="D427">
-        <v>1388435.087641645</v>
+        <v>1390168.344937745</v>
       </c>
       <c r="E427">
-        <v>2273949.929668717</v>
+        <v>2281066.56704077</v>
       </c>
     </row>
     <row r="428" spans="1:5">
@@ -7633,10 +7633,10 @@
         <v>687629.0835711417</v>
       </c>
       <c r="D428">
-        <v>1388435.087641645</v>
+        <v>1390168.344937745</v>
       </c>
       <c r="E428">
-        <v>2273949.929668717</v>
+        <v>2281066.56704077</v>
       </c>
     </row>
     <row r="429" spans="1:5">
@@ -7650,10 +7650,10 @@
         <v>687629.0835711417</v>
       </c>
       <c r="D429">
-        <v>1388435.087641645</v>
+        <v>1390168.344937745</v>
       </c>
       <c r="E429">
-        <v>2273949.929668717</v>
+        <v>2281066.56704077</v>
       </c>
     </row>
     <row r="430" spans="1:5">
@@ -7667,10 +7667,10 @@
         <v>687629.0835711417</v>
       </c>
       <c r="D430">
-        <v>1388435.087641645</v>
+        <v>1390168.344937745</v>
       </c>
       <c r="E430">
-        <v>2273949.929668717</v>
+        <v>2281066.56704077</v>
       </c>
     </row>
     <row r="431" spans="1:5">
@@ -7684,10 +7684,10 @@
         <v>668114.2226479377</v>
       </c>
       <c r="D431">
-        <v>1344597.93669863</v>
+        <v>1346467.711601018</v>
       </c>
       <c r="E431">
-        <v>2203788.607272876</v>
+        <v>2211230.670796098</v>
       </c>
     </row>
     <row r="432" spans="1:5">
@@ -7701,10 +7701,10 @@
         <v>687629.0835711417</v>
       </c>
       <c r="D432">
-        <v>1388435.087641645</v>
+        <v>1390168.344937745</v>
       </c>
       <c r="E432">
-        <v>2273949.929668717</v>
+        <v>2281066.56704077</v>
       </c>
     </row>
     <row r="433" spans="1:5">
@@ -7718,10 +7718,10 @@
         <v>687629.0835711417</v>
       </c>
       <c r="D433">
-        <v>1388435.087641645</v>
+        <v>1390168.344937745</v>
       </c>
       <c r="E433">
-        <v>2273949.929668717</v>
+        <v>2281066.56704077</v>
       </c>
     </row>
     <row r="434" spans="1:5">
@@ -7735,10 +7735,10 @@
         <v>800077.8113214457</v>
       </c>
       <c r="D434">
-        <v>1797745.895372753</v>
+        <v>1798917.127378558</v>
       </c>
       <c r="E434">
-        <v>2923222.456746255</v>
+        <v>2928012.298926823</v>
       </c>
     </row>
     <row r="435" spans="1:5">
@@ -7752,10 +7752,10 @@
         <v>720373.325645958</v>
       </c>
       <c r="D435">
-        <v>1319013.333259563</v>
+        <v>1320659.927690858</v>
       </c>
       <c r="E435">
-        <v>1648613.699009819</v>
+        <v>1653773.261104558</v>
       </c>
     </row>
     <row r="436" spans="1:5">
@@ -7769,10 +7769,10 @@
         <v>313698.9716674015</v>
       </c>
       <c r="D436">
-        <v>678622.0371470493</v>
+        <v>678995.7296201834</v>
       </c>
       <c r="E436">
-        <v>1006133.140513601</v>
+        <v>1008090.917471538</v>
       </c>
     </row>
     <row r="437" spans="1:5">
@@ -7786,10 +7786,10 @@
         <v>212124.6239835651</v>
       </c>
       <c r="D437">
-        <v>486262.0313994261</v>
+        <v>486367.0757828717</v>
       </c>
       <c r="E437">
-        <v>747112.0086343527</v>
+        <v>747721.3484346576</v>
       </c>
     </row>
     <row r="438" spans="1:5">
@@ -7803,10 +7803,10 @@
         <v>212124.6239835651</v>
       </c>
       <c r="D438">
-        <v>486262.0313994261</v>
+        <v>486367.0757828717</v>
       </c>
       <c r="E438">
-        <v>747112.0086343527</v>
+        <v>747721.3484346576</v>
       </c>
     </row>
     <row r="439" spans="1:5">
@@ -7820,10 +7820,10 @@
         <v>212124.6239835651</v>
       </c>
       <c r="D439">
-        <v>486262.0313994261</v>
+        <v>486367.0757828717</v>
       </c>
       <c r="E439">
-        <v>747112.0086343527</v>
+        <v>747721.3484346576</v>
       </c>
     </row>
     <row r="440" spans="1:5">
@@ -7837,10 +7837,10 @@
         <v>212124.6239835651</v>
       </c>
       <c r="D440">
-        <v>486262.0313994261</v>
+        <v>486367.0757828717</v>
       </c>
       <c r="E440">
-        <v>747112.0086343527</v>
+        <v>747721.3484346576</v>
       </c>
     </row>
     <row r="441" spans="1:5">
@@ -7854,10 +7854,10 @@
         <v>212124.6239835651</v>
       </c>
       <c r="D441">
-        <v>486262.0313994261</v>
+        <v>486367.0757828717</v>
       </c>
       <c r="E441">
-        <v>747112.0086343527</v>
+        <v>747721.3484346576</v>
       </c>
     </row>
     <row r="442" spans="1:5">
@@ -7871,10 +7871,10 @@
         <v>212124.6239835651</v>
       </c>
       <c r="D442">
-        <v>486262.0313994261</v>
+        <v>486367.0757828717</v>
       </c>
       <c r="E442">
-        <v>747112.0086343527</v>
+        <v>747721.3484346576</v>
       </c>
     </row>
     <row r="443" spans="1:5">
@@ -7888,10 +7888,10 @@
         <v>212124.6239835651</v>
       </c>
       <c r="D443">
-        <v>486262.0313994261</v>
+        <v>486367.0757828717</v>
       </c>
       <c r="E443">
-        <v>747112.0086343527</v>
+        <v>747721.3484346576</v>
       </c>
     </row>
     <row r="444" spans="1:5">
@@ -7905,10 +7905,10 @@
         <v>212124.6239835651</v>
       </c>
       <c r="D444">
-        <v>486262.0313994261</v>
+        <v>486367.0757828717</v>
       </c>
       <c r="E444">
-        <v>747112.0086343527</v>
+        <v>747721.3484346576</v>
       </c>
     </row>
     <row r="445" spans="1:5">
@@ -7922,10 +7922,10 @@
         <v>212124.6239835651</v>
       </c>
       <c r="D445">
-        <v>486262.0313994261</v>
+        <v>486367.0757828717</v>
       </c>
       <c r="E445">
-        <v>747112.0086343527</v>
+        <v>747721.3484346576</v>
       </c>
     </row>
     <row r="446" spans="1:5">
@@ -7939,10 +7939,10 @@
         <v>212124.6239835651</v>
       </c>
       <c r="D446">
-        <v>486262.0313994261</v>
+        <v>486367.0757828717</v>
       </c>
       <c r="E446">
-        <v>747112.0086343527</v>
+        <v>747721.3484346576</v>
       </c>
     </row>
     <row r="447" spans="1:5">
@@ -7956,10 +7956,10 @@
         <v>212124.6239835651</v>
       </c>
       <c r="D447">
-        <v>486262.0313994261</v>
+        <v>486367.0757828717</v>
       </c>
       <c r="E447">
-        <v>747112.0086343527</v>
+        <v>747721.3484346576</v>
       </c>
     </row>
     <row r="448" spans="1:5">
@@ -7973,10 +7973,10 @@
         <v>439801.1890355988</v>
       </c>
       <c r="D448">
-        <v>716750.652439054</v>
+        <v>716958.3559739037</v>
       </c>
       <c r="E448">
-        <v>1091613.81750957</v>
+        <v>1095328.318871869</v>
       </c>
     </row>
     <row r="449" spans="1:5">
@@ -7990,10 +7990,10 @@
         <v>439801.1890355988</v>
       </c>
       <c r="D449">
-        <v>716750.652439054</v>
+        <v>716958.3559739037</v>
       </c>
       <c r="E449">
-        <v>1091613.81750957</v>
+        <v>1095328.318871869</v>
       </c>
     </row>
     <row r="450" spans="1:5">
@@ -8007,10 +8007,10 @@
         <v>439801.1890355988</v>
       </c>
       <c r="D450">
-        <v>716750.652439054</v>
+        <v>716958.3559739037</v>
       </c>
       <c r="E450">
-        <v>1091613.81750957</v>
+        <v>1095328.318871869</v>
       </c>
     </row>
     <row r="451" spans="1:5">
@@ -8024,10 +8024,10 @@
         <v>439801.1890355988</v>
       </c>
       <c r="D451">
-        <v>716750.652439054</v>
+        <v>716958.3559739037</v>
       </c>
       <c r="E451">
-        <v>1091613.81750957</v>
+        <v>1095328.318871869</v>
       </c>
     </row>
     <row r="452" spans="1:5">
@@ -8041,10 +8041,10 @@
         <v>439801.1890355988</v>
       </c>
       <c r="D452">
-        <v>716750.652439054</v>
+        <v>716958.3559739037</v>
       </c>
       <c r="E452">
-        <v>1091613.81750957</v>
+        <v>1095328.318871869</v>
       </c>
     </row>
     <row r="453" spans="1:5">
@@ -8058,10 +8058,10 @@
         <v>390934.3902538656</v>
       </c>
       <c r="D453">
-        <v>801074.2586083545</v>
+        <v>801306.3978531865</v>
       </c>
       <c r="E453">
-        <v>1541101.86001351</v>
+        <v>1546345.861936756</v>
       </c>
     </row>
     <row r="454" spans="1:5">
@@ -8072,13 +8072,13 @@
         <v>575655.962514816</v>
       </c>
       <c r="C454">
-        <v>731252.8000488431</v>
+        <v>731374.9426822021</v>
       </c>
       <c r="D454">
-        <v>1396879.531462838</v>
+        <v>1397932.220142571</v>
       </c>
       <c r="E454">
-        <v>2045423.176234433</v>
+        <v>2051352.381964166</v>
       </c>
     </row>
     <row r="455" spans="1:5">
@@ -8089,13 +8089,13 @@
         <v>575655.962514816</v>
       </c>
       <c r="C455">
-        <v>731252.8000488431</v>
+        <v>731374.9426822021</v>
       </c>
       <c r="D455">
-        <v>1396879.531462838</v>
+        <v>1397932.220142571</v>
       </c>
       <c r="E455">
-        <v>2045423.176234433</v>
+        <v>2051352.381964166</v>
       </c>
     </row>
     <row r="456" spans="1:5">
@@ -8106,13 +8106,13 @@
         <v>575655.962514816</v>
       </c>
       <c r="C456">
-        <v>731252.8000488431</v>
+        <v>731374.9426822021</v>
       </c>
       <c r="D456">
-        <v>1396879.531462838</v>
+        <v>1397932.220142571</v>
       </c>
       <c r="E456">
-        <v>2045423.176234433</v>
+        <v>2051352.381964166</v>
       </c>
     </row>
     <row r="457" spans="1:5">
@@ -8123,13 +8123,13 @@
         <v>575655.962514816</v>
       </c>
       <c r="C457">
-        <v>731252.8000488431</v>
+        <v>731374.9426822021</v>
       </c>
       <c r="D457">
-        <v>1396879.531462838</v>
+        <v>1397932.220142571</v>
       </c>
       <c r="E457">
-        <v>2045423.176234433</v>
+        <v>2051352.381964166</v>
       </c>
     </row>
     <row r="458" spans="1:5">
@@ -8140,13 +8140,13 @@
         <v>575655.962514816</v>
       </c>
       <c r="C458">
-        <v>731252.8000488431</v>
+        <v>731374.9426822021</v>
       </c>
       <c r="D458">
-        <v>1396879.531462838</v>
+        <v>1397932.220142571</v>
       </c>
       <c r="E458">
-        <v>2045423.176234433</v>
+        <v>2051352.381964166</v>
       </c>
     </row>
     <row r="459" spans="1:5">
@@ -8157,13 +8157,13 @@
         <v>662004.3568920384</v>
       </c>
       <c r="C459">
-        <v>788983.2842632255</v>
+        <v>789115.0697360601</v>
       </c>
       <c r="D459">
-        <v>1321372.529762144</v>
+        <v>1322368.316351081</v>
       </c>
       <c r="E459">
-        <v>1684466.145134239</v>
+        <v>1689349.020441078</v>
       </c>
     </row>
     <row r="460" spans="1:5">
@@ -8174,13 +8174,13 @@
         <v>575655.962514816</v>
       </c>
       <c r="C460">
-        <v>731252.8000488431</v>
+        <v>731374.9426822021</v>
       </c>
       <c r="D460">
-        <v>1396879.531462838</v>
+        <v>1397932.220142571</v>
       </c>
       <c r="E460">
-        <v>2045423.176234433</v>
+        <v>2051352.381964166</v>
       </c>
     </row>
     <row r="461" spans="1:5">
@@ -8191,13 +8191,13 @@
         <v>575655.962514816</v>
       </c>
       <c r="C461">
-        <v>731252.8000488431</v>
+        <v>731374.9426822021</v>
       </c>
       <c r="D461">
-        <v>1396879.531462838</v>
+        <v>1397932.220142571</v>
       </c>
       <c r="E461">
-        <v>2045423.176234433</v>
+        <v>2051352.381964166</v>
       </c>
     </row>
     <row r="462" spans="1:5">
@@ -8208,13 +8208,13 @@
         <v>662004.3568920384</v>
       </c>
       <c r="C462">
-        <v>788983.2842632255</v>
+        <v>789115.0697360601</v>
       </c>
       <c r="D462">
-        <v>1321372.529762144</v>
+        <v>1322368.316351081</v>
       </c>
       <c r="E462">
-        <v>1684466.145134239</v>
+        <v>1689349.020441078</v>
       </c>
     </row>
     <row r="463" spans="1:5">
@@ -8228,10 +8228,10 @@
         <v>671256.9625337336</v>
       </c>
       <c r="D463">
-        <v>1388435.087641645</v>
+        <v>1390168.344937745</v>
       </c>
       <c r="E463">
-        <v>2330798.677910435</v>
+        <v>2338093.231216789</v>
       </c>
     </row>
     <row r="464" spans="1:5">
@@ -8245,10 +8245,10 @@
         <v>671256.9625337336</v>
       </c>
       <c r="D464">
-        <v>1388435.087641645</v>
+        <v>1390168.344937745</v>
       </c>
       <c r="E464">
-        <v>2330798.677910435</v>
+        <v>2338093.231216789</v>
       </c>
     </row>
     <row r="465" spans="1:5">
@@ -8262,10 +8262,10 @@
         <v>861622.2583461724</v>
       </c>
       <c r="D465">
-        <v>1657296.997296757</v>
+        <v>1658376.726802108</v>
       </c>
       <c r="E465">
-        <v>2215991.217210871</v>
+        <v>2219622.226605818</v>
       </c>
     </row>
     <row r="466" spans="1:5">
@@ -8279,10 +8279,10 @@
         <v>775460.0325115551</v>
       </c>
       <c r="D466">
-        <v>1769656.115757554</v>
+        <v>1770809.047263268</v>
       </c>
       <c r="E466">
-        <v>3017519.955350973</v>
+        <v>3022464.308569624</v>
       </c>
     </row>
     <row r="467" spans="1:5">
@@ -8296,10 +8296,10 @@
         <v>671256.9625337336</v>
       </c>
       <c r="D467">
-        <v>1388435.087641645</v>
+        <v>1390168.344937745</v>
       </c>
       <c r="E467">
-        <v>2330798.677910435</v>
+        <v>2338093.231216789</v>
       </c>
     </row>
     <row r="468" spans="1:5">
@@ -8313,10 +8313,10 @@
         <v>390934.3902538656</v>
       </c>
       <c r="D468">
-        <v>801074.2586083545</v>
+        <v>801306.3978531865</v>
       </c>
       <c r="E468">
-        <v>1541101.86001351</v>
+        <v>1546345.861936756</v>
       </c>
     </row>
     <row r="469" spans="1:5">
@@ -8330,10 +8330,10 @@
         <v>464234.5884264653</v>
       </c>
       <c r="D469">
-        <v>716750.652439054</v>
+        <v>716958.3559739037</v>
       </c>
       <c r="E469">
-        <v>963188.6625084439</v>
+        <v>966466.1637104724</v>
       </c>
     </row>
     <row r="470" spans="1:5">
@@ -8347,10 +8347,10 @@
         <v>464234.5884264653</v>
       </c>
       <c r="D470">
-        <v>716750.652439054</v>
+        <v>716958.3559739037</v>
       </c>
       <c r="E470">
-        <v>963188.6625084439</v>
+        <v>966466.1637104724</v>
       </c>
     </row>
     <row r="471" spans="1:5">
@@ -8364,10 +8364,10 @@
         <v>736745.4466833661</v>
       </c>
       <c r="D471">
-        <v>1319013.333259563</v>
+        <v>1320659.927690858</v>
       </c>
       <c r="E471">
-        <v>1648613.699009819</v>
+        <v>1653773.261104558</v>
       </c>
     </row>
     <row r="472" spans="1:5">
@@ -8378,13 +8378,13 @@
         <v>690787.1550177792</v>
       </c>
       <c r="C472">
-        <v>827470.2737394804</v>
+        <v>827608.4877719654</v>
       </c>
       <c r="D472">
-        <v>1321372.529762144</v>
+        <v>1322368.316351081</v>
       </c>
       <c r="E472">
-        <v>1443828.124400777</v>
+        <v>1448013.446092353</v>
       </c>
     </row>
     <row r="473" spans="1:5">
@@ -8398,10 +8398,10 @@
         <v>873931.1477511177</v>
       </c>
       <c r="D473">
-        <v>1657296.997296757</v>
+        <v>1658376.726802108</v>
       </c>
       <c r="E473">
-        <v>2168842.467908512</v>
+        <v>2172396.221784418</v>
       </c>
     </row>
     <row r="474" spans="1:5">
@@ -8415,10 +8415,10 @@
         <v>873931.1477511177</v>
       </c>
       <c r="D474">
-        <v>1657296.997296757</v>
+        <v>1658376.726802108</v>
       </c>
       <c r="E474">
-        <v>2168842.467908512</v>
+        <v>2172396.221784418</v>
       </c>
     </row>
     <row r="475" spans="1:5">
@@ -8432,10 +8432,10 @@
         <v>325317.4520995275</v>
       </c>
       <c r="D475">
-        <v>678622.0371470493</v>
+        <v>678995.7296201834</v>
       </c>
       <c r="E475">
-        <v>910310.9366551633</v>
+        <v>912082.2586647246</v>
       </c>
     </row>
     <row r="476" spans="1:5">
@@ -8449,10 +8449,10 @@
         <v>469876.7722971776</v>
       </c>
       <c r="D476">
-        <v>912191.5008655832</v>
+        <v>912684.5338167513</v>
       </c>
       <c r="E476">
-        <v>1167787.040958767</v>
+        <v>1169256.587768685</v>
       </c>
     </row>
     <row r="477" spans="1:5">
@@ -8466,10 +8466,10 @@
         <v>458416.3632167587</v>
       </c>
       <c r="D477">
-        <v>939833.6675584796</v>
+        <v>940341.6409021073</v>
       </c>
       <c r="E477">
-        <v>1214498.522597118</v>
+        <v>1216026.851279433</v>
       </c>
     </row>
     <row r="478" spans="1:5">
@@ -8480,13 +8480,13 @@
         <v>1301739.838038603</v>
       </c>
       <c r="C478">
-        <v>2070008.180643173</v>
+        <v>2070433.375106085</v>
       </c>
       <c r="D478">
-        <v>5015665.970767506</v>
+        <v>5020279.406889539</v>
       </c>
       <c r="E478">
-        <v>8762137.97895422</v>
+        <v>8789961.91381317</v>
       </c>
     </row>
     <row r="479" spans="1:5">
@@ -8497,13 +8497,13 @@
         <v>4914091.024654992</v>
       </c>
       <c r="C479">
-        <v>6611233.709393505</v>
+        <v>6611395.595320114</v>
       </c>
       <c r="D479">
-        <v>14241344.69677601</v>
+        <v>14249521.44624039</v>
       </c>
       <c r="E479">
-        <v>20942996.51414172</v>
+        <v>20985507.45041532</v>
       </c>
     </row>
     <row r="480" spans="1:5">
@@ -8514,13 +8514,13 @@
         <v>1323604.682100974</v>
       </c>
       <c r="C480">
-        <v>2132287.377542218</v>
+        <v>2132620.356078169</v>
       </c>
       <c r="D480">
-        <v>5186774.486171505</v>
+        <v>5191011.771383597</v>
       </c>
       <c r="E480">
-        <v>9056776.677907513</v>
+        <v>9083227.473304519</v>
       </c>
     </row>
     <row r="481" spans="1:5">
@@ -8531,13 +8531,13 @@
         <v>1301739.838038603</v>
       </c>
       <c r="C481">
-        <v>2070008.180643173</v>
+        <v>2070433.375106085</v>
       </c>
       <c r="D481">
-        <v>5015665.970767506</v>
+        <v>5020279.406889539</v>
       </c>
       <c r="E481">
-        <v>8762137.97895422</v>
+        <v>8789961.91381317</v>
       </c>
     </row>
     <row r="482" spans="1:5">
@@ -8548,13 +8548,13 @@
         <v>1301739.838038603</v>
       </c>
       <c r="C482">
-        <v>2070008.180643173</v>
+        <v>2070433.375106085</v>
       </c>
       <c r="D482">
-        <v>5015665.970767506</v>
+        <v>5020279.406889539</v>
       </c>
       <c r="E482">
-        <v>8762137.97895422</v>
+        <v>8789961.91381317</v>
       </c>
     </row>
     <row r="483" spans="1:5">
@@ -8565,13 +8565,13 @@
         <v>1301739.838038603</v>
       </c>
       <c r="C483">
-        <v>2070008.180643173</v>
+        <v>2070433.375106085</v>
       </c>
       <c r="D483">
-        <v>5015665.970767506</v>
+        <v>5020279.406889539</v>
       </c>
       <c r="E483">
-        <v>8762137.97895422</v>
+        <v>8789961.91381317</v>
       </c>
     </row>
     <row r="484" spans="1:5">
@@ -8582,13 +8582,13 @@
         <v>1301739.838038603</v>
       </c>
       <c r="C484">
-        <v>2070008.180643173</v>
+        <v>2070433.375106085</v>
       </c>
       <c r="D484">
-        <v>5015665.970767506</v>
+        <v>5020279.406889539</v>
       </c>
       <c r="E484">
-        <v>8762137.97895422</v>
+        <v>8789961.91381317</v>
       </c>
     </row>
     <row r="485" spans="1:5">
@@ -8599,13 +8599,13 @@
         <v>1323604.682100974</v>
       </c>
       <c r="C485">
-        <v>2132287.377542218</v>
+        <v>2132620.356078169</v>
       </c>
       <c r="D485">
-        <v>5186774.486171505</v>
+        <v>5191011.771383597</v>
       </c>
       <c r="E485">
-        <v>9056776.677907513</v>
+        <v>9083227.473304519</v>
       </c>
     </row>
     <row r="486" spans="1:5">
@@ -8616,13 +8616,13 @@
         <v>2283704.349496123</v>
       </c>
       <c r="C486">
-        <v>3742218.342207976</v>
+        <v>3742623.316039231</v>
       </c>
       <c r="D486">
-        <v>9274734.730599115</v>
+        <v>9281699.264286326</v>
       </c>
       <c r="E486">
-        <v>16287086.47812749</v>
+        <v>16328433.29523424</v>
       </c>
     </row>
     <row r="487" spans="1:5">
@@ -8633,13 +8633,13 @@
         <v>733237.8019366825</v>
       </c>
       <c r="C487">
-        <v>953043.7187271412</v>
+        <v>953045.323653459</v>
       </c>
       <c r="D487">
-        <v>1795095.520772929</v>
+        <v>1795852.105541703</v>
       </c>
       <c r="E487">
-        <v>2235976.245577344</v>
+        <v>2239932.036933025</v>
       </c>
     </row>
     <row r="488" spans="1:5">
@@ -8650,13 +8650,13 @@
         <v>212602.5545204221</v>
       </c>
       <c r="C488">
-        <v>294053.5321649725</v>
+        <v>294073.2861387866</v>
       </c>
       <c r="D488">
-        <v>706768.6494529725</v>
+        <v>707104.1327501701</v>
       </c>
       <c r="E488">
-        <v>1142131.293182709</v>
+        <v>1143818.552419232</v>
       </c>
     </row>
     <row r="489" spans="1:5">
@@ -8667,13 +8667,13 @@
         <v>255123.0654245065</v>
       </c>
       <c r="C489">
-        <v>332408.3407082298</v>
+        <v>332430.671287324</v>
       </c>
       <c r="D489">
-        <v>647871.2619985582</v>
+        <v>648178.7883543227</v>
       </c>
       <c r="E489">
-        <v>943499.7639335422</v>
+        <v>944893.5867811046</v>
       </c>
     </row>
     <row r="490" spans="1:5">
@@ -8684,13 +8684,13 @@
         <v>2327555.182210077</v>
       </c>
       <c r="C490">
-        <v>3440775.204600768</v>
+        <v>3441651.81750031</v>
       </c>
       <c r="D490">
-        <v>7124318.197818167</v>
+        <v>7141996.977196638</v>
       </c>
       <c r="E490">
-        <v>10731354.72687631</v>
+        <v>10792491.52513996</v>
       </c>
     </row>
     <row r="491" spans="1:5">
@@ -8701,13 +8701,13 @@
         <v>2673231.694419494</v>
       </c>
       <c r="C491">
-        <v>3566220.133935171</v>
+        <v>3567128.706680009</v>
       </c>
       <c r="D491">
-        <v>6809431.205649409</v>
+        <v>6826328.602513913</v>
       </c>
       <c r="E491">
-        <v>9317643.325730933</v>
+        <v>9370726.174522717</v>
       </c>
     </row>
     <row r="492" spans="1:5">
@@ -8718,13 +8718,13 @@
         <v>2327555.182210077</v>
       </c>
       <c r="C492">
-        <v>3440775.204600768</v>
+        <v>3441651.81750031</v>
       </c>
       <c r="D492">
-        <v>7124318.197818167</v>
+        <v>7141996.977196638</v>
       </c>
       <c r="E492">
-        <v>10731354.72687631</v>
+        <v>10792491.52513996</v>
       </c>
     </row>
     <row r="493" spans="1:5">
@@ -8735,13 +8735,13 @@
         <v>2327555.182210077</v>
       </c>
       <c r="C493">
-        <v>3440775.204600768</v>
+        <v>3441651.81750031</v>
       </c>
       <c r="D493">
-        <v>7124318.197818167</v>
+        <v>7141996.977196638</v>
       </c>
       <c r="E493">
-        <v>10731354.72687631</v>
+        <v>10792491.52513996</v>
       </c>
     </row>
     <row r="494" spans="1:5">
@@ -8752,13 +8752,13 @@
         <v>2327555.182210077</v>
       </c>
       <c r="C494">
-        <v>3440775.204600768</v>
+        <v>3441651.81750031</v>
       </c>
       <c r="D494">
-        <v>7124318.197818167</v>
+        <v>7141996.977196638</v>
       </c>
       <c r="E494">
-        <v>10731354.72687631</v>
+        <v>10792491.52513996</v>
       </c>
     </row>
     <row r="495" spans="1:5">
@@ -8769,13 +8769,13 @@
         <v>447332.2478875362</v>
       </c>
       <c r="C495">
-        <v>666689.3239164271</v>
+        <v>667204.2002718042</v>
       </c>
       <c r="D495">
-        <v>1352152.349208838</v>
+        <v>1357823.489706549</v>
       </c>
       <c r="E495">
-        <v>1863901.955985622</v>
+        <v>1876382.736466181</v>
       </c>
     </row>
     <row r="496" spans="1:5">
@@ -8786,13 +8786,13 @@
         <v>3081861.818300479</v>
       </c>
       <c r="C496">
-        <v>4407721.207239301</v>
+        <v>4411463.725638966</v>
       </c>
       <c r="D496">
-        <v>8482858.075446788</v>
+        <v>8524161.392648807</v>
       </c>
       <c r="E496">
-        <v>11684267.55704926</v>
+        <v>11768940.9619625</v>
       </c>
     </row>
     <row r="497" spans="1:5">
@@ -8803,13 +8803,13 @@
         <v>447332.2478875362</v>
       </c>
       <c r="C497">
-        <v>666689.3239164271</v>
+        <v>667204.2002718042</v>
       </c>
       <c r="D497">
-        <v>1352152.349208838</v>
+        <v>1357823.489706549</v>
       </c>
       <c r="E497">
-        <v>1863901.955985622</v>
+        <v>1876382.736466181</v>
       </c>
     </row>
     <row r="498" spans="1:5">
@@ -8820,13 +8820,13 @@
         <v>1010399.934723795</v>
       </c>
       <c r="C498">
-        <v>1369740.865882519</v>
+        <v>1369891.376177963</v>
       </c>
       <c r="D498">
-        <v>2476197.384132817</v>
+        <v>2484675.991459633</v>
       </c>
       <c r="E498">
-        <v>3521175.317002682</v>
+        <v>3542259.41557666</v>
       </c>
     </row>
     <row r="499" spans="1:5">
@@ -8837,13 +8837,13 @@
         <v>1190334.169674608</v>
       </c>
       <c r="C499">
-        <v>1450313.857993255</v>
+        <v>1450473.22183549</v>
       </c>
       <c r="D499">
-        <v>2356381.381674778</v>
+        <v>2364449.733808361</v>
       </c>
       <c r="E499">
-        <v>2766637.749073536</v>
+        <v>2783203.826524519</v>
       </c>
     </row>
     <row r="500" spans="1:5">
@@ -8854,13 +8854,13 @@
         <v>1204175.264670825</v>
       </c>
       <c r="C500">
-        <v>1450313.857993255</v>
+        <v>1450473.22183549</v>
       </c>
       <c r="D500">
-        <v>2356381.381674778</v>
+        <v>2364449.733808361</v>
       </c>
       <c r="E500">
-        <v>2703759.618412774</v>
+        <v>2719949.194103507</v>
       </c>
     </row>
     <row r="501" spans="1:5">
@@ -8874,10 +8874,10 @@
         <v>521398.7732062784</v>
       </c>
       <c r="D501">
-        <v>1213572.151649218</v>
+        <v>1214301.708002874</v>
       </c>
       <c r="E501">
-        <v>2215793.833077756</v>
+        <v>2219668.557128583</v>
       </c>
     </row>
   </sheetData>
